--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I848"/>
+  <dimension ref="A1:I853"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29123,13 +29123,13 @@
         </is>
       </c>
       <c r="E776" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F776" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G776" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H776" t="n">
         <v>88</v>
@@ -29345,13 +29345,13 @@
         </is>
       </c>
       <c r="E782" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F782" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G782" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H782" t="n">
         <v>169</v>
@@ -29641,13 +29641,13 @@
         </is>
       </c>
       <c r="E790" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F790" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G790" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H790" t="n">
         <v>30</v>
@@ -29715,13 +29715,13 @@
         </is>
       </c>
       <c r="E792" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F792" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G792" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H792" t="n">
         <v>632</v>
@@ -29748,23 +29748,23 @@
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E793" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F793" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G793" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H793" t="n">
-        <v>2050</v>
+        <v>0</v>
       </c>
       <c r="I793" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="794">
@@ -29780,28 +29780,28 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E794" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F794" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G794" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H794" t="n">
-        <v>0</v>
+        <v>2050</v>
       </c>
       <c r="I794" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="795">
@@ -29822,23 +29822,23 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E795" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F795" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G795" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H795" t="n">
-        <v>1389</v>
+        <v>0</v>
       </c>
       <c r="I795" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="796">
@@ -29849,33 +29849,33 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E796" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="F796" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="G796" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="H796" t="n">
-        <v>0</v>
+        <v>1389</v>
       </c>
       <c r="I796" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="797">
@@ -29896,17 +29896,17 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E797" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="F797" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="G797" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="H797" t="n">
         <v>0</v>
@@ -29928,22 +29928,22 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E798" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F798" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G798" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="H798" t="n">
         <v>0</v>
@@ -29970,23 +29970,23 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E799" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="F799" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="G799" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="H799" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="I799" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="800">
@@ -30002,12 +30002,12 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E800" t="n">
@@ -30020,10 +30020,10 @@
         <v>7</v>
       </c>
       <c r="H800" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="I800" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="801">
@@ -30044,17 +30044,17 @@
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E801" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F801" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G801" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H801" t="n">
         <v>0</v>
@@ -30076,22 +30076,22 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E802" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F802" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G802" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H802" t="n">
         <v>0</v>
@@ -30118,23 +30118,23 @@
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E803" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F803" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G803" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H803" t="n">
-        <v>3303</v>
+        <v>0</v>
       </c>
       <c r="I803" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="804">
@@ -30150,28 +30150,28 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E804" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F804" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G804" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H804" t="n">
-        <v>0</v>
+        <v>3303</v>
       </c>
       <c r="I804" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
     </row>
     <row r="805">
@@ -30192,23 +30192,23 @@
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E805" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F805" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G805" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="H805" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="I805" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="806">
@@ -30224,28 +30224,28 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E806" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F806" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="G806" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H806" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="I806" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="807">
@@ -30266,7 +30266,7 @@
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E807" t="n">
@@ -30279,10 +30279,10 @@
         <v>4</v>
       </c>
       <c r="H807" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="I807" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="808">
@@ -30298,7 +30298,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
@@ -30307,16 +30307,16 @@
         </is>
       </c>
       <c r="E808" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F808" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G808" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H808" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I808" t="n">
         <v>2</v>
@@ -30335,28 +30335,28 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E809" t="n">
+        <v>1</v>
+      </c>
+      <c r="F809" t="n">
+        <v>1</v>
+      </c>
+      <c r="G809" t="n">
+        <v>1</v>
+      </c>
+      <c r="H809" t="n">
+        <v>53</v>
+      </c>
+      <c r="I809" t="n">
         <v>2</v>
-      </c>
-      <c r="F809" t="n">
-        <v>2</v>
-      </c>
-      <c r="G809" t="n">
-        <v>2</v>
-      </c>
-      <c r="H809" t="n">
-        <v>0</v>
-      </c>
-      <c r="I809" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="810">
@@ -30377,17 +30377,17 @@
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E810" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F810" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G810" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H810" t="n">
         <v>0</v>
@@ -30409,22 +30409,22 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E811" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F811" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G811" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H811" t="n">
         <v>0</v>
@@ -30451,23 +30451,23 @@
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E812" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F812" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G812" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H812" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="I812" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="813">
@@ -30483,7 +30483,7 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
@@ -30492,19 +30492,19 @@
         </is>
       </c>
       <c r="E813" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F813" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G813" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H813" t="n">
-        <v>173</v>
+        <v>103</v>
       </c>
       <c r="I813" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="814">
@@ -30520,7 +30520,7 @@
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
@@ -30557,7 +30557,7 @@
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
@@ -30566,19 +30566,19 @@
         </is>
       </c>
       <c r="E815" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F815" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G815" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H815" t="n">
-        <v>677</v>
+        <v>173</v>
       </c>
       <c r="I815" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="816">
@@ -30589,12 +30589,12 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
@@ -30626,12 +30626,12 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
@@ -30640,19 +30640,19 @@
         </is>
       </c>
       <c r="E817" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F817" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G817" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H817" t="n">
-        <v>0</v>
+        <v>677</v>
       </c>
       <c r="I817" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="818">
@@ -30668,28 +30668,28 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E818" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F818" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G818" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H818" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I818" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="819">
@@ -30705,7 +30705,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
@@ -30737,12 +30737,12 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -30760,10 +30760,10 @@
         <v>0</v>
       </c>
       <c r="H820" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I820" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="821">
@@ -30774,12 +30774,12 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -30797,10 +30797,10 @@
         <v>0</v>
       </c>
       <c r="H821" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I821" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="822">
@@ -30811,27 +30811,27 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E822" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F822" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G822" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H822" t="n">
         <v>0</v>
@@ -30848,33 +30848,33 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E823" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F823" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G823" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H823" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I823" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="824">
@@ -30890,12 +30890,12 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E824" t="n">
@@ -30927,22 +30927,22 @@
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E825" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F825" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G825" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H825" t="n">
         <v>0</v>
@@ -30959,12 +30959,12 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
@@ -30982,10 +30982,10 @@
         <v>1</v>
       </c>
       <c r="H826" t="n">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="I826" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="827">
@@ -30996,12 +30996,12 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
@@ -31010,13 +31010,13 @@
         </is>
       </c>
       <c r="E827" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F827" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G827" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -31033,27 +31033,27 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E828" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F828" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -31075,7 +31075,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
@@ -31084,19 +31084,19 @@
         </is>
       </c>
       <c r="E829" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F829" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G829" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H829" t="n">
-        <v>226</v>
+        <v>848</v>
       </c>
       <c r="I829" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
     </row>
     <row r="830">
@@ -31112,7 +31112,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -31121,13 +31121,13 @@
         </is>
       </c>
       <c r="E830" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F830" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G830" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -31149,7 +31149,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -31186,7 +31186,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
@@ -31204,10 +31204,10 @@
         <v>0</v>
       </c>
       <c r="H832" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="I832" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="833">
@@ -31223,7 +31223,7 @@
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
@@ -31232,19 +31232,19 @@
         </is>
       </c>
       <c r="E833" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F833" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G833" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H833" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I833" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="834">
@@ -31260,7 +31260,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
@@ -31292,27 +31292,27 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E835" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F835" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G835" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -31329,12 +31329,12 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
@@ -31343,19 +31343,19 @@
         </is>
       </c>
       <c r="E836" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F836" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G836" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H836" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="I836" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="837">
@@ -31366,27 +31366,27 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E837" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F837" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G837" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H837" t="n">
         <v>0</v>
@@ -31408,22 +31408,22 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E838" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F838" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G838" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H838" t="n">
         <v>0</v>
@@ -31445,7 +31445,7 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
@@ -31454,13 +31454,13 @@
         </is>
       </c>
       <c r="E839" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F839" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G839" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -31482,7 +31482,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -31491,13 +31491,13 @@
         </is>
       </c>
       <c r="E840" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F840" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G840" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H840" t="n">
         <v>0</v>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
@@ -31528,19 +31528,19 @@
         </is>
       </c>
       <c r="E841" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F841" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G841" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H841" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I841" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="842">
@@ -31551,12 +31551,12 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -31565,13 +31565,13 @@
         </is>
       </c>
       <c r="E842" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F842" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G842" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H842" t="n">
         <v>0</v>
@@ -31588,27 +31588,27 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E843" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F843" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G843" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -31625,12 +31625,12 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
@@ -31639,19 +31639,19 @@
         </is>
       </c>
       <c r="E844" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F844" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G844" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H844" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="I844" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="845">
@@ -31662,12 +31662,12 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -31676,19 +31676,19 @@
         </is>
       </c>
       <c r="E845" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F845" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G845" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H845" t="n">
-        <v>1087</v>
+        <v>10</v>
       </c>
       <c r="I845" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="846">
@@ -31704,7 +31704,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
@@ -31741,7 +31741,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
@@ -31759,10 +31759,10 @@
         <v>0</v>
       </c>
       <c r="H847" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="I847" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="848">
@@ -31778,27 +31778,212 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E848" t="n">
+        <v>0</v>
+      </c>
+      <c r="F848" t="n">
+        <v>0</v>
+      </c>
+      <c r="G848" t="n">
+        <v>0</v>
+      </c>
+      <c r="H848" t="n">
+        <v>94</v>
+      </c>
+      <c r="I848" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>£25K-£50K</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E849" t="n">
+        <v>0</v>
+      </c>
+      <c r="F849" t="n">
+        <v>0</v>
+      </c>
+      <c r="G849" t="n">
+        <v>0</v>
+      </c>
+      <c r="H849" t="n">
+        <v>1087</v>
+      </c>
+      <c r="I849" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E850" t="n">
+        <v>0</v>
+      </c>
+      <c r="F850" t="n">
+        <v>0</v>
+      </c>
+      <c r="G850" t="n">
+        <v>0</v>
+      </c>
+      <c r="H850" t="n">
+        <v>0</v>
+      </c>
+      <c r="I850" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E851" t="n">
+        <v>1</v>
+      </c>
+      <c r="F851" t="n">
+        <v>1</v>
+      </c>
+      <c r="G851" t="n">
+        <v>1</v>
+      </c>
+      <c r="H851" t="n">
+        <v>0</v>
+      </c>
+      <c r="I851" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E852" t="n">
+        <v>0</v>
+      </c>
+      <c r="F852" t="n">
+        <v>0</v>
+      </c>
+      <c r="G852" t="n">
+        <v>0</v>
+      </c>
+      <c r="H852" t="n">
+        <v>125</v>
+      </c>
+      <c r="I852" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
           <t>£5K-£10K</t>
         </is>
       </c>
-      <c r="D848" t="inlineStr">
-        <is>
-          <t>Old</t>
-        </is>
-      </c>
-      <c r="E848" t="n">
-        <v>1</v>
-      </c>
-      <c r="F848" t="n">
-        <v>1</v>
-      </c>
-      <c r="G848" t="n">
-        <v>1</v>
-      </c>
-      <c r="H848" t="n">
-        <v>0</v>
-      </c>
-      <c r="I848" t="n">
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E853" t="n">
+        <v>1</v>
+      </c>
+      <c r="F853" t="n">
+        <v>1</v>
+      </c>
+      <c r="G853" t="n">
+        <v>1</v>
+      </c>
+      <c r="H853" t="n">
+        <v>0</v>
+      </c>
+      <c r="I853" t="n">
         <v>0</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I867"/>
+  <dimension ref="A1:I870"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18106,10 +18106,10 @@
         <v>308</v>
       </c>
       <c r="H478" t="n">
-        <v>2962</v>
+        <v>2874</v>
       </c>
       <c r="I478" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="479">
@@ -18920,10 +18920,10 @@
         <v>59</v>
       </c>
       <c r="H500" t="n">
-        <v>634</v>
+        <v>722</v>
       </c>
       <c r="I500" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="501">
@@ -20400,10 +20400,10 @@
         <v>21</v>
       </c>
       <c r="H540" t="n">
-        <v>3895</v>
+        <v>4096</v>
       </c>
       <c r="I540" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="541">
@@ -20622,10 +20622,10 @@
         <v>6</v>
       </c>
       <c r="H546" t="n">
-        <v>6841</v>
+        <v>6974</v>
       </c>
       <c r="I546" t="n">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="547">
@@ -20807,10 +20807,10 @@
         <v>6</v>
       </c>
       <c r="H551" t="n">
-        <v>90</v>
+        <v>243</v>
       </c>
       <c r="I551" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="552">
@@ -20881,10 +20881,10 @@
         <v>28</v>
       </c>
       <c r="H553" t="n">
-        <v>1235</v>
+        <v>1264</v>
       </c>
       <c r="I553" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="554">
@@ -23004,12 +23004,12 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -23018,19 +23018,19 @@
         </is>
       </c>
       <c r="E611" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F611" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G611" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H611" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="I611" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="612">
@@ -23046,22 +23046,22 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E612" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F612" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G612" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H612" t="n">
         <v>0</v>
@@ -23083,28 +23083,28 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E613" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F613" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G613" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H613" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="I613" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="614">
@@ -23125,23 +23125,23 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E614" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F614" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G614" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H614" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="I614" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="615">
@@ -23157,12 +23157,12 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E615" t="n">
@@ -23199,17 +23199,17 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E616" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F616" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G616" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H616" t="n">
         <v>0</v>
@@ -23231,22 +23231,22 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E617" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F617" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G617" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -23273,17 +23273,17 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E618" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F618" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G618" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -23305,22 +23305,22 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E619" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F619" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G619" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -23347,7 +23347,7 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E620" t="n">
@@ -23379,12 +23379,12 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E621" t="n">
@@ -23397,10 +23397,10 @@
         <v>2</v>
       </c>
       <c r="H621" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I621" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="622">
@@ -23421,23 +23421,23 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E622" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F622" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G622" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H622" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I622" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="623">
@@ -23453,22 +23453,22 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E623" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F623" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G623" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H623" t="n">
         <v>0</v>
@@ -23495,17 +23495,17 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E624" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F624" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G624" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -23527,22 +23527,22 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E625" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F625" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G625" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H625" t="n">
         <v>0</v>
@@ -23569,17 +23569,17 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E626" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F626" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G626" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H626" t="n">
         <v>0</v>
@@ -23596,12 +23596,12 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -23610,13 +23610,13 @@
         </is>
       </c>
       <c r="E627" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F627" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G627" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H627" t="n">
         <v>0</v>
@@ -23638,7 +23638,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
@@ -23647,13 +23647,13 @@
         </is>
       </c>
       <c r="E628" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F628" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G628" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H628" t="n">
         <v>0</v>
@@ -23675,22 +23675,22 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E629" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F629" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G629" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H629" t="n">
         <v>0</v>
@@ -23717,7 +23717,7 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E630" t="n">
@@ -23749,22 +23749,22 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E631" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F631" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G631" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H631" t="n">
         <v>0</v>
@@ -23791,17 +23791,17 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E632" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F632" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G632" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H632" t="n">
         <v>0</v>
@@ -23823,28 +23823,28 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E633" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F633" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G633" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H633" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I633" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="634">
@@ -23865,23 +23865,23 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E634" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F634" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="G634" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H634" t="n">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="I634" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="635">
@@ -23897,28 +23897,28 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E635" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F635" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G635" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H635" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="I635" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="636">
@@ -23939,17 +23939,17 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E636" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F636" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G636" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H636" t="n">
         <v>0</v>
@@ -23971,22 +23971,22 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E637" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F637" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G637" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H637" t="n">
         <v>0</v>
@@ -24013,23 +24013,23 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E638" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F638" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G638" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H638" t="n">
-        <v>0</v>
+        <v>4933</v>
       </c>
       <c r="I638" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="639">
@@ -24045,12 +24045,12 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E639" t="n">
@@ -24063,10 +24063,10 @@
         <v>1</v>
       </c>
       <c r="H639" t="n">
-        <v>4914</v>
+        <v>0</v>
       </c>
       <c r="I639" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="640">
@@ -24087,23 +24087,23 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E640" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F640" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G640" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H640" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I640" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="641">
@@ -24119,28 +24119,28 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E641" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F641" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G641" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H641" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I641" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="642">
@@ -24161,17 +24161,17 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E642" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F642" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G642" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H642" t="n">
         <v>0</v>
@@ -24193,28 +24193,28 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E643" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F643" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G643" t="n">
+        <v>1</v>
+      </c>
+      <c r="H643" t="n">
+        <v>107</v>
+      </c>
+      <c r="I643" t="n">
         <v>9</v>
-      </c>
-      <c r="H643" t="n">
-        <v>0</v>
-      </c>
-      <c r="I643" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="644">
@@ -24235,23 +24235,23 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E644" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F644" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G644" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H644" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="I644" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="645">
@@ -24267,22 +24267,22 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E645" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F645" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G645" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H645" t="n">
         <v>0</v>
@@ -24309,17 +24309,17 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E646" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F646" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G646" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H646" t="n">
         <v>0</v>
@@ -24331,17 +24331,17 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -24350,13 +24350,13 @@
         </is>
       </c>
       <c r="E647" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F647" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G647" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H647" t="n">
         <v>0</v>
@@ -24373,33 +24373,33 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Ashwagandha</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E648" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F648" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G648" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H648" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I648" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="649">
@@ -24420,23 +24420,23 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E649" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="F649" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="G649" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="H649" t="n">
-        <v>26</v>
+        <v>389</v>
       </c>
       <c r="I649" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="650">
@@ -24452,28 +24452,28 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E650" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="F650" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G650" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="H650" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="I650" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="651">
@@ -24494,23 +24494,23 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E651" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="F651" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="G651" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H651" t="n">
-        <v>80</v>
+        <v>383</v>
       </c>
       <c r="I651" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="652">
@@ -24526,28 +24526,28 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E652" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F652" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G652" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H652" t="n">
-        <v>278</v>
+        <v>61</v>
       </c>
       <c r="I652" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653">
@@ -24568,23 +24568,23 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E653" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F653" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G653" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H653" t="n">
-        <v>61</v>
+        <v>626</v>
       </c>
       <c r="I653" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="654">
@@ -24600,28 +24600,28 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E654" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F654" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G654" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H654" t="n">
-        <v>569</v>
+        <v>348</v>
       </c>
       <c r="I654" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="655">
@@ -24642,23 +24642,23 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E655" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F655" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G655" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="H655" t="n">
-        <v>322</v>
+        <v>13038</v>
       </c>
       <c r="I655" t="n">
-        <v>12</v>
+        <v>521</v>
       </c>
     </row>
     <row r="656">
@@ -24674,28 +24674,28 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E656" t="n">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="F656" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="G656" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="H656" t="n">
-        <v>11336</v>
+        <v>3052</v>
       </c>
       <c r="I656" t="n">
-        <v>459</v>
+        <v>122</v>
       </c>
     </row>
     <row r="657">
@@ -24716,23 +24716,23 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E657" t="n">
-        <v>132</v>
+        <v>241</v>
       </c>
       <c r="F657" t="n">
-        <v>141</v>
+        <v>280</v>
       </c>
       <c r="G657" t="n">
-        <v>141</v>
+        <v>281</v>
       </c>
       <c r="H657" t="n">
-        <v>2887</v>
+        <v>17166</v>
       </c>
       <c r="I657" t="n">
-        <v>116</v>
+        <v>932</v>
       </c>
     </row>
     <row r="658">
@@ -24748,28 +24748,28 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E658" t="n">
-        <v>241</v>
+        <v>67</v>
       </c>
       <c r="F658" t="n">
-        <v>280</v>
+        <v>68</v>
       </c>
       <c r="G658" t="n">
-        <v>281</v>
+        <v>68</v>
       </c>
       <c r="H658" t="n">
-        <v>16375</v>
+        <v>593</v>
       </c>
       <c r="I658" t="n">
-        <v>890</v>
+        <v>26</v>
       </c>
     </row>
     <row r="659">
@@ -24790,23 +24790,23 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E659" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F659" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G659" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="H659" t="n">
-        <v>515</v>
+        <v>1428</v>
       </c>
       <c r="I659" t="n">
-        <v>24</v>
+        <v>57</v>
       </c>
     </row>
     <row r="660">
@@ -24822,28 +24822,28 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E660" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="F660" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="G660" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="H660" t="n">
-        <v>1385</v>
+        <v>950</v>
       </c>
       <c r="I660" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
     </row>
     <row r="661">
@@ -24864,23 +24864,23 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E661" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F661" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G661" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H661" t="n">
-        <v>792</v>
+        <v>17642</v>
       </c>
       <c r="I661" t="n">
-        <v>26</v>
+        <v>802</v>
       </c>
     </row>
     <row r="662">
@@ -24896,28 +24896,28 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E662" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F662" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G662" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H662" t="n">
-        <v>15823</v>
+        <v>0</v>
       </c>
       <c r="I662" t="n">
-        <v>725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="663">
@@ -24938,23 +24938,23 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E663" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F663" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G663" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H663" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I663" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="664">
@@ -24970,28 +24970,28 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E664" t="n">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="F664" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="G664" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="H664" t="n">
+        <v>552</v>
+      </c>
+      <c r="I664" t="n">
         <v>28</v>
-      </c>
-      <c r="I664" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="665">
@@ -25012,23 +25012,23 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E665" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="F665" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="G665" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="H665" t="n">
-        <v>487</v>
+        <v>2729</v>
       </c>
       <c r="I665" t="n">
-        <v>27</v>
+        <v>113</v>
       </c>
     </row>
     <row r="666">
@@ -25044,28 +25044,28 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E666" t="n">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="F666" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="G666" t="n">
-        <v>82</v>
+        <v>3</v>
       </c>
       <c r="H666" t="n">
-        <v>2653</v>
+        <v>0</v>
       </c>
       <c r="I666" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="667">
@@ -25086,23 +25086,23 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E667" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F667" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G667" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H667" t="n">
-        <v>0</v>
+        <v>5191</v>
       </c>
       <c r="I667" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="668">
@@ -25118,28 +25118,28 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E668" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F668" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G668" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H668" t="n">
-        <v>4523</v>
+        <v>266</v>
       </c>
       <c r="I668" t="n">
-        <v>196</v>
+        <v>10</v>
       </c>
     </row>
     <row r="669">
@@ -25160,23 +25160,23 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E669" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="F669" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G669" t="n">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="H669" t="n">
-        <v>217</v>
+        <v>37897</v>
       </c>
       <c r="I669" t="n">
-        <v>8</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="670">
@@ -25187,12 +25187,12 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>GUTSHIFT</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -25201,19 +25201,19 @@
         </is>
       </c>
       <c r="E670" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F670" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="G670" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H670" t="n">
-        <v>34614</v>
+        <v>0</v>
       </c>
       <c r="I670" t="n">
-        <v>1387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="671">
@@ -25224,27 +25224,27 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>GUTSHIFT</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E671" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="F671" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="G671" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -25271,17 +25271,17 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E672" t="n">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="F672" t="n">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="G672" t="n">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -25303,22 +25303,22 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E673" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="F673" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="G673" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -25345,17 +25345,17 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E674" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="F674" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G674" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -25377,28 +25377,28 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E675" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="F675" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="G675" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="H675" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I675" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="676">
@@ -25419,23 +25419,23 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E676" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F676" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G676" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H676" t="n">
-        <v>15</v>
+        <v>154</v>
       </c>
       <c r="I676" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="677">
@@ -25451,28 +25451,28 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E677" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F677" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G677" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H677" t="n">
-        <v>154</v>
+        <v>53</v>
       </c>
       <c r="I677" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="678">
@@ -25493,23 +25493,23 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E678" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F678" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="G678" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H678" t="n">
-        <v>53</v>
+        <v>6262</v>
       </c>
       <c r="I678" t="n">
-        <v>2</v>
+        <v>269</v>
       </c>
     </row>
     <row r="679">
@@ -25525,28 +25525,28 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E679" t="n">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F679" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="G679" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="H679" t="n">
-        <v>6007</v>
+        <v>144</v>
       </c>
       <c r="I679" t="n">
-        <v>260</v>
+        <v>7</v>
       </c>
     </row>
     <row r="680">
@@ -25567,23 +25567,23 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E680" t="n">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="F680" t="n">
+        <v>154</v>
+      </c>
+      <c r="G680" t="n">
+        <v>154</v>
+      </c>
+      <c r="H680" t="n">
+        <v>1536</v>
+      </c>
+      <c r="I680" t="n">
         <v>70</v>
-      </c>
-      <c r="G680" t="n">
-        <v>70</v>
-      </c>
-      <c r="H680" t="n">
-        <v>144</v>
-      </c>
-      <c r="I680" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="681">
@@ -25599,28 +25599,28 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E681" t="n">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="F681" t="n">
-        <v>154</v>
+        <v>48</v>
       </c>
       <c r="G681" t="n">
-        <v>154</v>
+        <v>48</v>
       </c>
       <c r="H681" t="n">
-        <v>1471</v>
+        <v>39</v>
       </c>
       <c r="I681" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
     </row>
     <row r="682">
@@ -25641,7 +25641,7 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E682" t="n">
@@ -25654,10 +25654,10 @@
         <v>48</v>
       </c>
       <c r="H682" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="I682" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="683">
@@ -25673,28 +25673,28 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E683" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="F683" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="G683" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="H683" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I683" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="684">
@@ -25715,23 +25715,23 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E684" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F684" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G684" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H684" t="n">
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="I684" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="685">
@@ -25747,28 +25747,28 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E685" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F685" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G685" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H685" t="n">
-        <v>296</v>
+        <v>143</v>
       </c>
       <c r="I685" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="686">
@@ -25789,23 +25789,23 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E686" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F686" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G686" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H686" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="I686" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="687">
@@ -25821,28 +25821,28 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E687" t="n">
+        <v>51</v>
+      </c>
+      <c r="F687" t="n">
+        <v>51</v>
+      </c>
+      <c r="G687" t="n">
+        <v>51</v>
+      </c>
+      <c r="H687" t="n">
+        <v>237</v>
+      </c>
+      <c r="I687" t="n">
         <v>8</v>
-      </c>
-      <c r="F687" t="n">
-        <v>8</v>
-      </c>
-      <c r="G687" t="n">
-        <v>8</v>
-      </c>
-      <c r="H687" t="n">
-        <v>0</v>
-      </c>
-      <c r="I687" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="688">
@@ -25863,7 +25863,7 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E688" t="n">
@@ -25876,10 +25876,10 @@
         <v>51</v>
       </c>
       <c r="H688" t="n">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="I688" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="689">
@@ -25895,28 +25895,28 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E689" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="F689" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G689" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="H689" t="n">
-        <v>207</v>
+        <v>437</v>
       </c>
       <c r="I689" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="690">
@@ -25937,23 +25937,23 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E690" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F690" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G690" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H690" t="n">
-        <v>437</v>
+        <v>4131</v>
       </c>
       <c r="I690" t="n">
-        <v>19</v>
+        <v>178</v>
       </c>
     </row>
     <row r="691">
@@ -25969,28 +25969,28 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E691" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F691" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G691" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H691" t="n">
-        <v>4095</v>
+        <v>406</v>
       </c>
       <c r="I691" t="n">
-        <v>176</v>
+        <v>19</v>
       </c>
     </row>
     <row r="692">
@@ -26011,23 +26011,23 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E692" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="F692" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="G692" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="H692" t="n">
-        <v>287</v>
+        <v>802</v>
       </c>
       <c r="I692" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="693">
@@ -26038,33 +26038,33 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E693" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="F693" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="G693" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H693" t="n">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="I693" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="694">
@@ -26085,17 +26085,17 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E694" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F694" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G694" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -26117,22 +26117,22 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E695" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F695" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G695" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -26159,17 +26159,17 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E696" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F696" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G696" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -26191,7 +26191,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -26200,13 +26200,13 @@
         </is>
       </c>
       <c r="E697" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F697" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G697" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H697" t="n">
         <v>0</v>
@@ -26228,28 +26228,28 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E698" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F698" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G698" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H698" t="n">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="I698" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="699">
@@ -26270,23 +26270,23 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E699" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F699" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="G699" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="H699" t="n">
-        <v>247</v>
+        <v>717</v>
       </c>
       <c r="I699" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
     </row>
     <row r="700">
@@ -26302,28 +26302,28 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E700" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="F700" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="G700" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="H700" t="n">
-        <v>707</v>
+        <v>0</v>
       </c>
       <c r="I700" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="701">
@@ -26344,17 +26344,17 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E701" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F701" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G701" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H701" t="n">
         <v>0</v>
@@ -26376,7 +26376,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
@@ -26385,13 +26385,13 @@
         </is>
       </c>
       <c r="E702" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F702" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G702" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H702" t="n">
         <v>0</v>
@@ -26413,28 +26413,28 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E703" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F703" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G703" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H703" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I703" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="704">
@@ -26455,23 +26455,23 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E704" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F704" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G704" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H704" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I704" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="705">
@@ -26487,22 +26487,22 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E705" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F705" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G705" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H705" t="n">
         <v>0</v>
@@ -26529,7 +26529,7 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E706" t="n">
@@ -26561,12 +26561,12 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E707" t="n">
@@ -26603,17 +26603,17 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E708" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F708" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G708" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H708" t="n">
         <v>0</v>
@@ -26630,27 +26630,27 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E709" t="n">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="F709" t="n">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="G709" t="n">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -26677,17 +26677,17 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E710" t="n">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="F710" t="n">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="G710" t="n">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="H710" t="n">
         <v>0</v>
@@ -26709,22 +26709,22 @@
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E711" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F711" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G711" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H711" t="n">
         <v>0</v>
@@ -26746,7 +26746,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -26755,13 +26755,13 @@
         </is>
       </c>
       <c r="E712" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F712" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G712" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H712" t="n">
         <v>0</v>
@@ -26788,17 +26788,17 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E713" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F713" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G713" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H713" t="n">
         <v>0</v>
@@ -26820,22 +26820,22 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E714" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F714" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G714" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H714" t="n">
         <v>0</v>
@@ -26857,22 +26857,22 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E715" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F715" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G715" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H715" t="n">
         <v>0</v>
@@ -26889,27 +26889,27 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E716" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F716" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G716" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H716" t="n">
         <v>0</v>
@@ -26936,17 +26936,17 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E717" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F717" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G717" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -26963,27 +26963,27 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E718" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F718" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G718" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H718" t="n">
         <v>0</v>
@@ -27010,17 +27010,17 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E719" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F719" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G719" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -27042,28 +27042,28 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E720" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F720" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G720" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="H720" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I720" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="721">
@@ -27084,20 +27084,20 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E721" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F721" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G721" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="H721" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I721" t="n">
         <v>2</v>
@@ -27116,28 +27116,28 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E722" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F722" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G722" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="H722" t="n">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="I722" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="723">
@@ -27158,23 +27158,23 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E723" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F723" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G723" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H723" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="I723" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="724">
@@ -27190,28 +27190,28 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E724" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F724" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G724" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H724" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="I724" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="725">
@@ -27232,23 +27232,23 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E725" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F725" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G725" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H725" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I725" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="726">
@@ -27264,28 +27264,28 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E726" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F726" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="G726" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="H726" t="n">
-        <v>0</v>
+        <v>1214</v>
       </c>
       <c r="I726" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="727">
@@ -27306,23 +27306,23 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E727" t="n">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="F727" t="n">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="G727" t="n">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="H727" t="n">
-        <v>1084</v>
+        <v>0</v>
       </c>
       <c r="I727" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="728">
@@ -27338,22 +27338,22 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E728" t="n">
-        <v>121</v>
+        <v>37</v>
       </c>
       <c r="F728" t="n">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="G728" t="n">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="H728" t="n">
         <v>0</v>
@@ -27380,17 +27380,17 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E729" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F729" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G729" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="H729" t="n">
         <v>0</v>
@@ -27412,7 +27412,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -27421,13 +27421,13 @@
         </is>
       </c>
       <c r="E730" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="F730" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="G730" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -27449,22 +27449,22 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E731" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F731" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G731" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H731" t="n">
         <v>0</v>
@@ -27491,17 +27491,17 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E732" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F732" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G732" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H732" t="n">
         <v>0</v>
@@ -27523,28 +27523,28 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E733" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F733" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="G733" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="H733" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I733" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="734">
@@ -27565,23 +27565,23 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E734" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F734" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="G734" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="H734" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I734" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="735">
@@ -27597,22 +27597,22 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E735" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="F735" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="G735" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -27639,17 +27639,17 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E736" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F736" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G736" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -27671,12 +27671,12 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E737" t="n">
@@ -27689,10 +27689,10 @@
         <v>4</v>
       </c>
       <c r="H737" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I737" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="738">
@@ -27713,17 +27713,17 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E738" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F738" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G738" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H738" t="n">
         <v>0</v>
@@ -27740,12 +27740,12 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
@@ -27754,13 +27754,13 @@
         </is>
       </c>
       <c r="E739" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F739" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G739" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -27782,22 +27782,22 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E740" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F740" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G740" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H740" t="n">
         <v>0</v>
@@ -27824,17 +27824,17 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E741" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F741" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G741" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H741" t="n">
         <v>0</v>
@@ -27856,22 +27856,22 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E742" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F742" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G742" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H742" t="n">
         <v>0</v>
@@ -27898,17 +27898,17 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E743" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F743" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G743" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H743" t="n">
         <v>0</v>
@@ -27930,22 +27930,22 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E744" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F744" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G744" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H744" t="n">
         <v>0</v>
@@ -27972,23 +27972,23 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E745" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F745" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G745" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H745" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="I745" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="746">
@@ -28004,28 +28004,28 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E746" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F746" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G746" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H746" t="n">
-        <v>288</v>
+        <v>115</v>
       </c>
       <c r="I746" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="747">
@@ -28046,23 +28046,23 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E747" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="F747" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G747" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="H747" t="n">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="I747" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="748">
@@ -28078,28 +28078,28 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E748" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="F748" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="G748" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="H748" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I748" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="749">
@@ -28120,23 +28120,23 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E749" t="n">
+        <v>8</v>
+      </c>
+      <c r="F749" t="n">
+        <v>8</v>
+      </c>
+      <c r="G749" t="n">
+        <v>8</v>
+      </c>
+      <c r="H749" t="n">
+        <v>80</v>
+      </c>
+      <c r="I749" t="n">
         <v>2</v>
-      </c>
-      <c r="F749" t="n">
-        <v>2</v>
-      </c>
-      <c r="G749" t="n">
-        <v>2</v>
-      </c>
-      <c r="H749" t="n">
-        <v>0</v>
-      </c>
-      <c r="I749" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="750">
@@ -28152,7 +28152,7 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
@@ -28161,19 +28161,19 @@
         </is>
       </c>
       <c r="E750" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F750" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G750" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H750" t="n">
-        <v>80</v>
+        <v>310</v>
       </c>
       <c r="I750" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="751">
@@ -28189,28 +28189,28 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E751" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F751" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G751" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H751" t="n">
-        <v>276</v>
+        <v>54</v>
       </c>
       <c r="I751" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="752">
@@ -28231,23 +28231,23 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E752" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F752" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G752" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H752" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="I752" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="753">
@@ -28263,28 +28263,28 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E753" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F753" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G753" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H753" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I753" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="754">
@@ -28305,17 +28305,17 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E754" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F754" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G754" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H754" t="n">
         <v>0</v>
@@ -28337,12 +28337,12 @@
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E755" t="n">
@@ -28379,17 +28379,17 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E756" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F756" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G756" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H756" t="n">
         <v>0</v>
@@ -28406,12 +28406,12 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
@@ -28420,13 +28420,13 @@
         </is>
       </c>
       <c r="E757" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F757" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G757" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H757" t="n">
         <v>0</v>
@@ -28448,7 +28448,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
@@ -28485,7 +28485,7 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
@@ -28494,13 +28494,13 @@
         </is>
       </c>
       <c r="E759" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F759" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G759" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H759" t="n">
         <v>0</v>
@@ -28522,12 +28522,12 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E760" t="n">
@@ -28559,7 +28559,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
@@ -28568,13 +28568,13 @@
         </is>
       </c>
       <c r="E761" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F761" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G761" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H761" t="n">
         <v>0</v>
@@ -28601,23 +28601,23 @@
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E762" t="n">
+        <v>16</v>
+      </c>
+      <c r="F762" t="n">
+        <v>16</v>
+      </c>
+      <c r="G762" t="n">
+        <v>16</v>
+      </c>
+      <c r="H762" t="n">
+        <v>174</v>
+      </c>
+      <c r="I762" t="n">
         <v>5</v>
-      </c>
-      <c r="F762" t="n">
-        <v>5</v>
-      </c>
-      <c r="G762" t="n">
-        <v>5</v>
-      </c>
-      <c r="H762" t="n">
-        <v>0</v>
-      </c>
-      <c r="I762" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="763">
@@ -28633,28 +28633,28 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E763" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F763" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G763" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H763" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="I763" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="764">
@@ -28675,17 +28675,17 @@
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E764" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F764" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G764" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
@@ -28716,19 +28716,19 @@
         </is>
       </c>
       <c r="E765" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F765" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G765" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H765" t="n">
-        <v>0</v>
+        <v>2495</v>
       </c>
       <c r="I765" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="766">
@@ -28744,7 +28744,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
@@ -28753,19 +28753,19 @@
         </is>
       </c>
       <c r="E766" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F766" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G766" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H766" t="n">
-        <v>2307</v>
+        <v>0</v>
       </c>
       <c r="I766" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="767">
@@ -28781,22 +28781,22 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E767" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F767" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G767" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -28823,17 +28823,17 @@
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E768" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F768" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G768" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H768" t="n">
         <v>0</v>
@@ -28855,7 +28855,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
@@ -28873,10 +28873,10 @@
         <v>3</v>
       </c>
       <c r="H769" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I769" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="770">
@@ -28892,28 +28892,28 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E770" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F770" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G770" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H770" t="n">
-        <v>29</v>
+        <v>364</v>
       </c>
       <c r="I770" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="771">
@@ -28934,60 +28934,60 @@
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E771" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F771" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G771" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H771" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="I771" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E772" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="F772" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="G772" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="H772" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="I772" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="773">
@@ -29008,23 +29008,23 @@
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E773" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="F773" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="G773" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="H773" t="n">
-        <v>88</v>
+        <v>2790</v>
       </c>
       <c r="I773" t="n">
-        <v>3</v>
+        <v>128</v>
       </c>
     </row>
     <row r="774">
@@ -29040,28 +29040,28 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E774" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F774" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="G774" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H774" t="n">
-        <v>372</v>
+        <v>0</v>
       </c>
       <c r="I774" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="775">
@@ -29082,23 +29082,23 @@
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E775" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F775" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G775" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H775" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="I775" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="776">
@@ -29114,12 +29114,12 @@
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E776" t="n">
@@ -29132,10 +29132,10 @@
         <v>4</v>
       </c>
       <c r="H776" t="n">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="I776" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="777">
@@ -29156,23 +29156,23 @@
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E777" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F777" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G777" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H777" t="n">
-        <v>26</v>
+        <v>243</v>
       </c>
       <c r="I777" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="778">
@@ -29188,28 +29188,28 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E778" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F778" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G778" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H778" t="n">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="I778" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="779">
@@ -29230,23 +29230,23 @@
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E779" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F779" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G779" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H779" t="n">
-        <v>169</v>
+        <v>4345</v>
       </c>
       <c r="I779" t="n">
-        <v>7</v>
+        <v>151</v>
       </c>
     </row>
     <row r="780">
@@ -29262,28 +29262,28 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E780" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F780" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G780" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H780" t="n">
-        <v>2490</v>
+        <v>241</v>
       </c>
       <c r="I780" t="n">
-        <v>84</v>
+        <v>7</v>
       </c>
     </row>
     <row r="781">
@@ -29304,23 +29304,23 @@
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E781" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F781" t="n">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="G781" t="n">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="H781" t="n">
-        <v>194</v>
+        <v>4907</v>
       </c>
       <c r="I781" t="n">
-        <v>6</v>
+        <v>209</v>
       </c>
     </row>
     <row r="782">
@@ -29336,28 +29336,28 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E782" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="F782" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="G782" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="H782" t="n">
-        <v>2368</v>
+        <v>27</v>
       </c>
       <c r="I782" t="n">
-        <v>107</v>
+        <v>1</v>
       </c>
     </row>
     <row r="783">
@@ -29378,23 +29378,23 @@
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E783" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F783" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G783" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H783" t="n">
-        <v>27</v>
+        <v>447</v>
       </c>
       <c r="I783" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="784">
@@ -29410,28 +29410,28 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E784" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F784" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G784" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H784" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="I784" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="785">
@@ -29452,23 +29452,23 @@
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E785" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F785" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G785" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H785" t="n">
-        <v>0</v>
+        <v>5520</v>
       </c>
       <c r="I785" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
     </row>
     <row r="786">
@@ -29484,28 +29484,28 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E786" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F786" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G786" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H786" t="n">
-        <v>1923</v>
+        <v>0</v>
       </c>
       <c r="I786" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="787">
@@ -29526,23 +29526,23 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E787" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F787" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G787" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H787" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I787" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="788">
@@ -29558,28 +29558,28 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E788" t="n">
+        <v>11</v>
+      </c>
+      <c r="F788" t="n">
+        <v>11</v>
+      </c>
+      <c r="G788" t="n">
+        <v>11</v>
+      </c>
+      <c r="H788" t="n">
+        <v>26</v>
+      </c>
+      <c r="I788" t="n">
         <v>2</v>
-      </c>
-      <c r="F788" t="n">
-        <v>2</v>
-      </c>
-      <c r="G788" t="n">
-        <v>2</v>
-      </c>
-      <c r="H788" t="n">
-        <v>30</v>
-      </c>
-      <c r="I788" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="789">
@@ -29600,23 +29600,23 @@
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E789" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F789" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G789" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H789" t="n">
-        <v>0</v>
+        <v>1193</v>
       </c>
       <c r="I789" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="790">
@@ -29632,28 +29632,28 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E790" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F790" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G790" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H790" t="n">
-        <v>670</v>
+        <v>0</v>
       </c>
       <c r="I790" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="791">
@@ -29674,23 +29674,23 @@
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E791" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F791" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G791" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H791" t="n">
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="I791" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="792">
@@ -29706,28 +29706,28 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E792" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F792" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G792" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H792" t="n">
-        <v>2067</v>
+        <v>0</v>
       </c>
       <c r="I792" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="793">
@@ -29748,23 +29748,23 @@
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E793" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F793" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G793" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H793" t="n">
-        <v>0</v>
+        <v>4834</v>
       </c>
       <c r="I793" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="794">
@@ -29775,33 +29775,33 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E794" t="n">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="F794" t="n">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="G794" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="H794" t="n">
-        <v>1699</v>
+        <v>51</v>
       </c>
       <c r="I794" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
     </row>
     <row r="795">
@@ -29822,17 +29822,17 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E795" t="n">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="F795" t="n">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="G795" t="n">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="H795" t="n">
         <v>0</v>
@@ -29854,22 +29854,22 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E796" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F796" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="G796" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H796" t="n">
         <v>0</v>
@@ -29896,23 +29896,23 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E797" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F797" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G797" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="H797" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="I797" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="798">
@@ -29928,28 +29928,28 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E798" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F798" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G798" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H798" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="I798" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="799">
@@ -29970,17 +29970,17 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E799" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F799" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G799" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H799" t="n">
         <v>0</v>
@@ -30002,28 +30002,28 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E800" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F800" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G800" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H800" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I800" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="801">
@@ -30044,23 +30044,23 @@
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E801" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F801" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G801" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H801" t="n">
-        <v>0</v>
+        <v>4535</v>
       </c>
       <c r="I801" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
     </row>
     <row r="802">
@@ -30076,28 +30076,28 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E802" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F802" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G802" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H802" t="n">
-        <v>3379</v>
+        <v>0</v>
       </c>
       <c r="I802" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="803">
@@ -30118,23 +30118,23 @@
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E803" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="F803" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="G803" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="H803" t="n">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="I803" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="804">
@@ -30150,28 +30150,28 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E804" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="F804" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="G804" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H804" t="n">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="I804" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="805">
@@ -30192,23 +30192,23 @@
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E805" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F805" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G805" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H805" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I805" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="806">
@@ -30224,7 +30224,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
@@ -30233,19 +30233,19 @@
         </is>
       </c>
       <c r="E806" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F806" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G806" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H806" t="n">
-        <v>61</v>
+        <v>209</v>
       </c>
       <c r="I806" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="807">
@@ -30261,12 +30261,12 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E807" t="n">
@@ -30279,10 +30279,10 @@
         <v>2</v>
       </c>
       <c r="H807" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="I807" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="808">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E808" t="n">
@@ -30316,10 +30316,10 @@
         <v>2</v>
       </c>
       <c r="H808" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I808" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="809">
@@ -30335,22 +30335,22 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E809" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F809" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G809" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -30377,23 +30377,23 @@
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E810" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F810" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="G810" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H810" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="I810" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="811">
@@ -30409,28 +30409,28 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E811" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="F811" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G811" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H811" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="I811" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="812">
@@ -30451,23 +30451,23 @@
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E812" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F812" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G812" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H812" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="I812" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="813">
@@ -30483,28 +30483,28 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E813" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F813" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G813" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H813" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="I813" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="814">
@@ -30525,23 +30525,23 @@
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E814" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F814" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G814" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H814" t="n">
-        <v>0</v>
+        <v>1331</v>
       </c>
       <c r="I814" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
     </row>
     <row r="815">
@@ -30552,33 +30552,33 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E815" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F815" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G815" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H815" t="n">
-        <v>696</v>
+        <v>0</v>
       </c>
       <c r="I815" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="816">
@@ -30636,7 +30636,7 @@
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E817" t="n">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
@@ -30677,13 +30677,13 @@
         </is>
       </c>
       <c r="E818" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F818" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G818" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H818" t="n">
         <v>0</v>
@@ -30705,7 +30705,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
@@ -30714,19 +30714,19 @@
         </is>
       </c>
       <c r="E819" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F819" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G819" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H819" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="I819" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="820">
@@ -30742,7 +30742,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -30751,19 +30751,19 @@
         </is>
       </c>
       <c r="E820" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F820" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G820" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H820" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I820" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="821">
@@ -30779,7 +30779,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -30816,7 +30816,7 @@
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
@@ -30825,13 +30825,13 @@
         </is>
       </c>
       <c r="E822" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F822" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G822" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H822" t="n">
         <v>0</v>
@@ -30848,12 +30848,12 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
@@ -30862,19 +30862,19 @@
         </is>
       </c>
       <c r="E823" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F823" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G823" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H823" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="I823" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="824">
@@ -30890,7 +30890,7 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
@@ -30908,10 +30908,10 @@
         <v>0</v>
       </c>
       <c r="H824" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I824" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="825">
@@ -30922,33 +30922,33 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E825" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F825" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G825" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H825" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I825" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="826">
@@ -30964,7 +30964,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
@@ -30973,13 +30973,13 @@
         </is>
       </c>
       <c r="E826" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F826" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G826" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H826" t="n">
         <v>0</v>
@@ -31001,7 +31001,7 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
@@ -31038,22 +31038,22 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E828" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F828" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G828" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -31075,7 +31075,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
@@ -31084,13 +31084,13 @@
         </is>
       </c>
       <c r="E829" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F829" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G829" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -31112,22 +31112,22 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E830" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F830" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G830" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -31149,7 +31149,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -31158,13 +31158,13 @@
         </is>
       </c>
       <c r="E831" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F831" t="n">
         <v>6</v>
       </c>
       <c r="G831" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -31186,22 +31186,22 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E832" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F832" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G832" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -31223,7 +31223,7 @@
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
@@ -31232,13 +31232,13 @@
         </is>
       </c>
       <c r="E833" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F833" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G833" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -31255,17 +31255,17 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E834" t="n">
@@ -31278,10 +31278,10 @@
         <v>1</v>
       </c>
       <c r="H834" t="n">
-        <v>949</v>
+        <v>0</v>
       </c>
       <c r="I834" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="835">
@@ -31292,12 +31292,12 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
@@ -31306,13 +31306,13 @@
         </is>
       </c>
       <c r="E835" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F835" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G835" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
@@ -31343,19 +31343,19 @@
         </is>
       </c>
       <c r="E836" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F836" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G836" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H836" t="n">
-        <v>40</v>
+        <v>1316</v>
       </c>
       <c r="I836" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
     </row>
     <row r="837">
@@ -31371,7 +31371,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
@@ -31389,10 +31389,10 @@
         <v>0</v>
       </c>
       <c r="H837" t="n">
-        <v>226</v>
+        <v>19</v>
       </c>
       <c r="I837" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="838">
@@ -31408,7 +31408,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
@@ -31417,19 +31417,19 @@
         </is>
       </c>
       <c r="E838" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F838" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G838" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H838" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="I838" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="839">
@@ -31445,7 +31445,7 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
@@ -31463,10 +31463,10 @@
         <v>0</v>
       </c>
       <c r="H839" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="I839" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="840">
@@ -31482,7 +31482,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -31491,19 +31491,19 @@
         </is>
       </c>
       <c r="E840" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F840" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G840" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H840" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I840" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="841">
@@ -31519,7 +31519,7 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
@@ -31537,10 +31537,10 @@
         <v>0</v>
       </c>
       <c r="H841" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I841" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="842">
@@ -31556,7 +31556,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -31574,10 +31574,10 @@
         <v>0</v>
       </c>
       <c r="H842" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I842" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="843">
@@ -31588,33 +31588,33 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E843" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F843" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G843" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H843" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="I843" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="844">
@@ -31635,23 +31635,23 @@
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E844" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F844" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G844" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H844" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I844" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="845">
@@ -31667,22 +31667,22 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E845" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F845" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G845" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H845" t="n">
         <v>0</v>
@@ -31704,22 +31704,22 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E846" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F846" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G846" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H846" t="n">
         <v>0</v>
@@ -31741,7 +31741,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
@@ -31750,13 +31750,13 @@
         </is>
       </c>
       <c r="E847" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F847" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G847" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -31778,22 +31778,22 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E848" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F848" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G848" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H848" t="n">
         <v>0</v>
@@ -31815,7 +31815,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
@@ -31824,13 +31824,13 @@
         </is>
       </c>
       <c r="E849" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F849" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G849" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -31852,7 +31852,7 @@
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
@@ -31861,19 +31861,19 @@
         </is>
       </c>
       <c r="E850" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F850" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G850" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H850" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I850" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="851">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E851" t="n">
@@ -31926,22 +31926,22 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E852" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F852" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G852" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H852" t="n">
         <v>0</v>
@@ -31963,28 +31963,28 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E853" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F853" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G853" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H853" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I853" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="854">
@@ -31995,33 +31995,33 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E854" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F854" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G854" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H854" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I854" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="855">
@@ -32032,33 +32032,33 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E855" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F855" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H855" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I855" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="856">
@@ -32069,12 +32069,12 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
@@ -32083,19 +32083,19 @@
         </is>
       </c>
       <c r="E856" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F856" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G856" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H856" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I856" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="857">
@@ -32111,22 +32111,22 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E857" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F857" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G857" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -32148,7 +32148,7 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -32157,13 +32157,13 @@
         </is>
       </c>
       <c r="E858" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F858" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G858" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -32185,22 +32185,22 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E859" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F859" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G859" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -32222,7 +32222,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -32231,19 +32231,19 @@
         </is>
       </c>
       <c r="E860" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="F860" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G860" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="H860" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="I860" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="861">
@@ -32259,7 +32259,7 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
@@ -32268,13 +32268,13 @@
         </is>
       </c>
       <c r="E861" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F861" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G861" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -32296,28 +32296,28 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E862" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F862" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G862" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H862" t="n">
-        <v>1161</v>
+        <v>0</v>
       </c>
       <c r="I862" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="863">
@@ -32333,7 +32333,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
@@ -32342,19 +32342,19 @@
         </is>
       </c>
       <c r="E863" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F863" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="G863" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="H863" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="I863" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="864">
@@ -32370,22 +32370,22 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E864" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F864" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G864" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H864" t="n">
         <v>0</v>
@@ -32407,7 +32407,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
@@ -32416,19 +32416,19 @@
         </is>
       </c>
       <c r="E865" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F865" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G865" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H865" t="n">
-        <v>125</v>
+        <v>2114</v>
       </c>
       <c r="I865" t="n">
-        <v>4</v>
+        <v>86</v>
       </c>
     </row>
     <row r="866">
@@ -32444,22 +32444,22 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E866" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F866" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G866" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -32481,27 +32481,138 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E867" t="n">
+        <v>1</v>
+      </c>
+      <c r="F867" t="n">
+        <v>1</v>
+      </c>
+      <c r="G867" t="n">
+        <v>1</v>
+      </c>
+      <c r="H867" t="n">
+        <v>0</v>
+      </c>
+      <c r="I867" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E868" t="n">
+        <v>0</v>
+      </c>
+      <c r="F868" t="n">
+        <v>0</v>
+      </c>
+      <c r="G868" t="n">
+        <v>0</v>
+      </c>
+      <c r="H868" t="n">
+        <v>198</v>
+      </c>
+      <c r="I868" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
           <t>£5K-£10K</t>
         </is>
       </c>
-      <c r="D867" t="inlineStr">
-        <is>
-          <t>Old</t>
-        </is>
-      </c>
-      <c r="E867" t="n">
-        <v>2</v>
-      </c>
-      <c r="F867" t="n">
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E869" t="n">
+        <v>1</v>
+      </c>
+      <c r="F869" t="n">
+        <v>1</v>
+      </c>
+      <c r="G869" t="n">
+        <v>1</v>
+      </c>
+      <c r="H869" t="n">
+        <v>0</v>
+      </c>
+      <c r="I869" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E870" t="n">
         <v>3</v>
       </c>
-      <c r="G867" t="n">
-        <v>3</v>
-      </c>
-      <c r="H867" t="n">
+      <c r="F870" t="n">
+        <v>4</v>
+      </c>
+      <c r="G870" t="n">
+        <v>4</v>
+      </c>
+      <c r="H870" t="n">
         <v>30</v>
       </c>
-      <c r="I867" t="n">
+      <c r="I870" t="n">
         <v>1</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -20363,10 +20363,10 @@
         <v>23</v>
       </c>
       <c r="H539" t="n">
-        <v>770</v>
+        <v>807</v>
       </c>
       <c r="I539" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="540">
@@ -20400,10 +20400,10 @@
         <v>21</v>
       </c>
       <c r="H540" t="n">
-        <v>4096</v>
+        <v>4116</v>
       </c>
       <c r="I540" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="541">
@@ -20511,10 +20511,10 @@
         <v>233</v>
       </c>
       <c r="H543" t="n">
-        <v>312</v>
+        <v>244</v>
       </c>
       <c r="I543" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="544">
@@ -20622,10 +20622,10 @@
         <v>6</v>
       </c>
       <c r="H546" t="n">
-        <v>6974</v>
+        <v>6983</v>
       </c>
       <c r="I546" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="547">
@@ -20881,10 +20881,10 @@
         <v>28</v>
       </c>
       <c r="H553" t="n">
-        <v>1264</v>
+        <v>1044</v>
       </c>
       <c r="I553" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="554">
@@ -20918,7 +20918,7 @@
         <v>29</v>
       </c>
       <c r="H554" t="n">
-        <v>7592</v>
+        <v>7613</v>
       </c>
       <c r="I554" t="n">
         <v>254</v>
@@ -21510,10 +21510,10 @@
         <v>0</v>
       </c>
       <c r="H570" t="n">
-        <v>2825</v>
+        <v>2841</v>
       </c>
       <c r="I570" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="571">
@@ -21584,10 +21584,10 @@
         <v>0</v>
       </c>
       <c r="H572" t="n">
-        <v>1130</v>
+        <v>1088</v>
       </c>
       <c r="I572" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="573">
@@ -24618,10 +24618,10 @@
         <v>15</v>
       </c>
       <c r="H654" t="n">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="I654" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="655">
@@ -24655,10 +24655,10 @@
         <v>31</v>
       </c>
       <c r="H655" t="n">
-        <v>13038</v>
+        <v>13281</v>
       </c>
       <c r="I655" t="n">
-        <v>521</v>
+        <v>532</v>
       </c>
     </row>
     <row r="656">
@@ -24729,10 +24729,10 @@
         <v>281</v>
       </c>
       <c r="H657" t="n">
-        <v>17166</v>
+        <v>17296</v>
       </c>
       <c r="I657" t="n">
-        <v>932</v>
+        <v>938</v>
       </c>
     </row>
     <row r="658">
@@ -24877,10 +24877,10 @@
         <v>16</v>
       </c>
       <c r="H661" t="n">
-        <v>17642</v>
+        <v>17888</v>
       </c>
       <c r="I661" t="n">
-        <v>802</v>
+        <v>810</v>
       </c>
     </row>
     <row r="662">
@@ -25025,10 +25025,10 @@
         <v>82</v>
       </c>
       <c r="H665" t="n">
-        <v>2729</v>
+        <v>2755</v>
       </c>
       <c r="I665" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="666">
@@ -25099,10 +25099,10 @@
         <v>6</v>
       </c>
       <c r="H667" t="n">
-        <v>5191</v>
+        <v>5231</v>
       </c>
       <c r="I667" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="668">
@@ -25173,10 +25173,10 @@
         <v>56</v>
       </c>
       <c r="H669" t="n">
-        <v>37897</v>
+        <v>38206</v>
       </c>
       <c r="I669" t="n">
-        <v>1505</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="670">
@@ -28984,10 +28984,10 @@
         <v>85</v>
       </c>
       <c r="H772" t="n">
-        <v>256</v>
+        <v>299</v>
       </c>
       <c r="I772" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="773">
@@ -29021,10 +29021,10 @@
         <v>1</v>
       </c>
       <c r="H773" t="n">
-        <v>2790</v>
+        <v>2809</v>
       </c>
       <c r="I773" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="774">
@@ -29095,10 +29095,10 @@
         <v>4</v>
       </c>
       <c r="H775" t="n">
-        <v>209</v>
+        <v>327</v>
       </c>
       <c r="I775" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="776">
@@ -29206,10 +29206,10 @@
         <v>13</v>
       </c>
       <c r="H778" t="n">
-        <v>214</v>
+        <v>276</v>
       </c>
       <c r="I778" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="779">
@@ -29243,10 +29243,10 @@
         <v>7</v>
       </c>
       <c r="H779" t="n">
-        <v>4345</v>
+        <v>4637</v>
       </c>
       <c r="I779" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
     </row>
     <row r="780">
@@ -29317,10 +29317,10 @@
         <v>62</v>
       </c>
       <c r="H781" t="n">
-        <v>4907</v>
+        <v>5425</v>
       </c>
       <c r="I781" t="n">
-        <v>209</v>
+        <v>222</v>
       </c>
     </row>
     <row r="782">
@@ -29391,10 +29391,10 @@
         <v>13</v>
       </c>
       <c r="H783" t="n">
-        <v>447</v>
+        <v>661</v>
       </c>
       <c r="I783" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="784">
@@ -29465,10 +29465,10 @@
         <v>5</v>
       </c>
       <c r="H785" t="n">
-        <v>5520</v>
+        <v>6314</v>
       </c>
       <c r="I785" t="n">
-        <v>202</v>
+        <v>229</v>
       </c>
     </row>
     <row r="786">
@@ -29576,10 +29576,10 @@
         <v>11</v>
       </c>
       <c r="H788" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="I788" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="789">
@@ -29613,10 +29613,10 @@
         <v>14</v>
       </c>
       <c r="H789" t="n">
-        <v>1193</v>
+        <v>1424</v>
       </c>
       <c r="I789" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="790">
@@ -29687,10 +29687,10 @@
         <v>1</v>
       </c>
       <c r="H791" t="n">
-        <v>2784</v>
+        <v>2836</v>
       </c>
       <c r="I791" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="792">
@@ -29761,10 +29761,10 @@
         <v>20</v>
       </c>
       <c r="H793" t="n">
-        <v>4834</v>
+        <v>5379</v>
       </c>
       <c r="I793" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="794">
@@ -30057,10 +30057,10 @@
         <v>9</v>
       </c>
       <c r="H801" t="n">
-        <v>4535</v>
+        <v>4856</v>
       </c>
       <c r="I801" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="802">
@@ -30131,10 +30131,10 @@
         <v>53</v>
       </c>
       <c r="H803" t="n">
-        <v>483</v>
+        <v>516</v>
       </c>
       <c r="I803" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="804">
@@ -30538,10 +30538,10 @@
         <v>15</v>
       </c>
       <c r="H814" t="n">
-        <v>1331</v>
+        <v>1369</v>
       </c>
       <c r="I814" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="815">
@@ -31648,10 +31648,10 @@
         <v>10</v>
       </c>
       <c r="H844" t="n">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="I844" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="845">
@@ -32018,10 +32018,10 @@
         <v>0</v>
       </c>
       <c r="H854" t="n">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="I854" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="855">
@@ -32351,10 +32351,10 @@
         <v>35</v>
       </c>
       <c r="H863" t="n">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="I863" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="864">
@@ -32425,10 +32425,10 @@
         <v>4</v>
       </c>
       <c r="H865" t="n">
-        <v>2114</v>
+        <v>2184</v>
       </c>
       <c r="I865" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="866">
@@ -32462,10 +32462,10 @@
         <v>4</v>
       </c>
       <c r="H866" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I866" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="867">

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I870"/>
+  <dimension ref="A1:I876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20215,10 +20215,10 @@
         <v>890</v>
       </c>
       <c r="H535" t="n">
-        <v>245</v>
+        <v>183</v>
       </c>
       <c r="I535" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="536">
@@ -20363,10 +20363,10 @@
         <v>23</v>
       </c>
       <c r="H539" t="n">
-        <v>807</v>
+        <v>782</v>
       </c>
       <c r="I539" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="540">
@@ -20400,10 +20400,10 @@
         <v>21</v>
       </c>
       <c r="H540" t="n">
-        <v>4116</v>
+        <v>4150</v>
       </c>
       <c r="I540" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="541">
@@ -20474,10 +20474,10 @@
         <v>127</v>
       </c>
       <c r="H542" t="n">
-        <v>6398</v>
+        <v>6198</v>
       </c>
       <c r="I542" t="n">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="543">
@@ -20548,10 +20548,10 @@
         <v>100</v>
       </c>
       <c r="H544" t="n">
-        <v>1910</v>
+        <v>1885</v>
       </c>
       <c r="I544" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="545">
@@ -20622,10 +20622,10 @@
         <v>6</v>
       </c>
       <c r="H546" t="n">
-        <v>6983</v>
+        <v>6894</v>
       </c>
       <c r="I546" t="n">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="547">
@@ -20844,10 +20844,10 @@
         <v>1</v>
       </c>
       <c r="H552" t="n">
-        <v>924</v>
+        <v>884</v>
       </c>
       <c r="I552" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="553">
@@ -20881,10 +20881,10 @@
         <v>28</v>
       </c>
       <c r="H553" t="n">
-        <v>1044</v>
+        <v>770</v>
       </c>
       <c r="I553" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="554">
@@ -20918,10 +20918,10 @@
         <v>29</v>
       </c>
       <c r="H554" t="n">
-        <v>7613</v>
+        <v>7449</v>
       </c>
       <c r="I554" t="n">
-        <v>254</v>
+        <v>243</v>
       </c>
     </row>
     <row r="555">
@@ -21510,10 +21510,10 @@
         <v>0</v>
       </c>
       <c r="H570" t="n">
-        <v>2841</v>
+        <v>2796</v>
       </c>
       <c r="I570" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="571">
@@ -21584,10 +21584,10 @@
         <v>0</v>
       </c>
       <c r="H572" t="n">
-        <v>1088</v>
+        <v>1050</v>
       </c>
       <c r="I572" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="573">
@@ -21917,10 +21917,10 @@
         <v>0</v>
       </c>
       <c r="H581" t="n">
-        <v>1132</v>
+        <v>1049</v>
       </c>
       <c r="I581" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="582">
@@ -24026,10 +24026,10 @@
         <v>1</v>
       </c>
       <c r="H638" t="n">
-        <v>4933</v>
+        <v>4913</v>
       </c>
       <c r="I638" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="639">
@@ -24433,10 +24433,10 @@
         <v>7</v>
       </c>
       <c r="H649" t="n">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="I649" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="650">
@@ -24655,10 +24655,10 @@
         <v>31</v>
       </c>
       <c r="H655" t="n">
-        <v>13281</v>
+        <v>13724</v>
       </c>
       <c r="I655" t="n">
-        <v>532</v>
+        <v>550</v>
       </c>
     </row>
     <row r="656">
@@ -24729,10 +24729,10 @@
         <v>281</v>
       </c>
       <c r="H657" t="n">
-        <v>17296</v>
+        <v>17483</v>
       </c>
       <c r="I657" t="n">
-        <v>938</v>
+        <v>945</v>
       </c>
     </row>
     <row r="658">
@@ -24766,10 +24766,10 @@
         <v>68</v>
       </c>
       <c r="H658" t="n">
-        <v>593</v>
+        <v>681</v>
       </c>
       <c r="I658" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="659">
@@ -24877,10 +24877,10 @@
         <v>16</v>
       </c>
       <c r="H661" t="n">
-        <v>17888</v>
+        <v>18132</v>
       </c>
       <c r="I661" t="n">
-        <v>810</v>
+        <v>817</v>
       </c>
     </row>
     <row r="662">
@@ -25025,10 +25025,10 @@
         <v>82</v>
       </c>
       <c r="H665" t="n">
-        <v>2755</v>
+        <v>2813</v>
       </c>
       <c r="I665" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="666">
@@ -25099,10 +25099,10 @@
         <v>6</v>
       </c>
       <c r="H667" t="n">
-        <v>5231</v>
+        <v>5251</v>
       </c>
       <c r="I667" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="668">
@@ -25173,10 +25173,10 @@
         <v>56</v>
       </c>
       <c r="H669" t="n">
-        <v>38206</v>
+        <v>38520</v>
       </c>
       <c r="I669" t="n">
-        <v>1519</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="670">
@@ -25506,10 +25506,10 @@
         <v>23</v>
       </c>
       <c r="H678" t="n">
-        <v>6262</v>
+        <v>6434</v>
       </c>
       <c r="I678" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="679">
@@ -25913,10 +25913,10 @@
         <v>2</v>
       </c>
       <c r="H689" t="n">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="I689" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="690">
@@ -25987,10 +25987,10 @@
         <v>13</v>
       </c>
       <c r="H691" t="n">
-        <v>406</v>
+        <v>471</v>
       </c>
       <c r="I691" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="692">
@@ -27282,10 +27282,10 @@
         <v>44</v>
       </c>
       <c r="H726" t="n">
-        <v>1214</v>
+        <v>1250</v>
       </c>
       <c r="I726" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="727">
@@ -27985,10 +27985,10 @@
         <v>5</v>
       </c>
       <c r="H745" t="n">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="I745" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="746">
@@ -28244,10 +28244,10 @@
         <v>10</v>
       </c>
       <c r="H752" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I752" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="753">
@@ -28614,10 +28614,10 @@
         <v>16</v>
       </c>
       <c r="H762" t="n">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="I762" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="763">
@@ -28975,19 +28975,19 @@
         </is>
       </c>
       <c r="E772" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F772" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G772" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H772" t="n">
-        <v>299</v>
+        <v>351</v>
       </c>
       <c r="I772" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="773">
@@ -29021,10 +29021,10 @@
         <v>1</v>
       </c>
       <c r="H773" t="n">
-        <v>2809</v>
+        <v>2958</v>
       </c>
       <c r="I773" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="774">
@@ -29095,10 +29095,10 @@
         <v>4</v>
       </c>
       <c r="H775" t="n">
-        <v>327</v>
+        <v>387</v>
       </c>
       <c r="I775" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="776">
@@ -29169,10 +29169,10 @@
         <v>1</v>
       </c>
       <c r="H777" t="n">
-        <v>243</v>
+        <v>303</v>
       </c>
       <c r="I777" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="778">
@@ -29234,19 +29234,19 @@
         </is>
       </c>
       <c r="E779" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F779" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G779" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H779" t="n">
-        <v>4637</v>
+        <v>5050</v>
       </c>
       <c r="I779" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
     </row>
     <row r="780">
@@ -29308,19 +29308,19 @@
         </is>
       </c>
       <c r="E781" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F781" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G781" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H781" t="n">
-        <v>5425</v>
+        <v>5911</v>
       </c>
       <c r="I781" t="n">
-        <v>222</v>
+        <v>239</v>
       </c>
     </row>
     <row r="782">
@@ -29391,10 +29391,10 @@
         <v>13</v>
       </c>
       <c r="H783" t="n">
-        <v>661</v>
+        <v>782</v>
       </c>
       <c r="I783" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="784">
@@ -29465,10 +29465,10 @@
         <v>5</v>
       </c>
       <c r="H785" t="n">
-        <v>6314</v>
+        <v>7054</v>
       </c>
       <c r="I785" t="n">
-        <v>229</v>
+        <v>255</v>
       </c>
     </row>
     <row r="786">
@@ -29604,19 +29604,19 @@
         </is>
       </c>
       <c r="E789" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F789" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G789" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H789" t="n">
-        <v>1424</v>
+        <v>1483</v>
       </c>
       <c r="I789" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="790">
@@ -29687,10 +29687,10 @@
         <v>1</v>
       </c>
       <c r="H791" t="n">
-        <v>2836</v>
+        <v>2925</v>
       </c>
       <c r="I791" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="792">
@@ -29752,19 +29752,19 @@
         </is>
       </c>
       <c r="E793" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F793" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G793" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H793" t="n">
-        <v>5379</v>
+        <v>6353</v>
       </c>
       <c r="I793" t="n">
-        <v>181</v>
+        <v>205</v>
       </c>
     </row>
     <row r="794">
@@ -29789,19 +29789,19 @@
         </is>
       </c>
       <c r="E794" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F794" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G794" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H794" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="I794" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="795">
@@ -29900,13 +29900,13 @@
         </is>
       </c>
       <c r="E797" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F797" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G797" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H797" t="n">
         <v>136</v>
@@ -30057,10 +30057,10 @@
         <v>9</v>
       </c>
       <c r="H801" t="n">
-        <v>4856</v>
+        <v>5103</v>
       </c>
       <c r="I801" t="n">
-        <v>217</v>
+        <v>231</v>
       </c>
     </row>
     <row r="802">
@@ -30122,19 +30122,19 @@
         </is>
       </c>
       <c r="E803" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F803" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G803" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H803" t="n">
-        <v>516</v>
+        <v>550</v>
       </c>
       <c r="I803" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="804">
@@ -30196,19 +30196,19 @@
         </is>
       </c>
       <c r="E805" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F805" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G805" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H805" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="I805" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="806">
@@ -30229,23 +30229,23 @@
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E806" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F806" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G806" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H806" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="I806" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="807">
@@ -30261,28 +30261,28 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E807" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F807" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G807" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H807" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="I807" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="808">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E808" t="n">
@@ -30316,10 +30316,10 @@
         <v>2</v>
       </c>
       <c r="H808" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I808" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="809">
@@ -30335,28 +30335,28 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E809" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F809" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G809" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H809" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I809" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="810">
@@ -30377,23 +30377,23 @@
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E810" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F810" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="G810" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="H810" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="I810" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="811">
@@ -30409,28 +30409,28 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E811" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F811" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G811" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H811" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="I811" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="812">
@@ -30451,23 +30451,23 @@
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E812" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F812" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G812" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H812" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="I812" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="813">
@@ -30483,28 +30483,28 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E813" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F813" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G813" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H813" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="I813" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="814">
@@ -30525,23 +30525,23 @@
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E814" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F814" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G814" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H814" t="n">
-        <v>1369</v>
+        <v>0</v>
       </c>
       <c r="I814" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="815">
@@ -30552,33 +30552,33 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E815" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F815" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G815" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H815" t="n">
-        <v>0</v>
+        <v>1543</v>
       </c>
       <c r="I815" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="816">
@@ -30594,7 +30594,7 @@
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
@@ -30603,13 +30603,13 @@
         </is>
       </c>
       <c r="E816" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F816" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G816" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H816" t="n">
         <v>0</v>
@@ -30631,7 +30631,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
@@ -30673,7 +30673,7 @@
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E818" t="n">
@@ -30705,7 +30705,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
@@ -30714,19 +30714,19 @@
         </is>
       </c>
       <c r="E819" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F819" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G819" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H819" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="I819" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="820">
@@ -30742,7 +30742,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -30751,19 +30751,19 @@
         </is>
       </c>
       <c r="E820" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F820" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G820" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H820" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="I820" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="821">
@@ -30779,7 +30779,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -30788,19 +30788,19 @@
         </is>
       </c>
       <c r="E821" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F821" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G821" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H821" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I821" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="822">
@@ -30816,12 +30816,12 @@
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E822" t="n">
@@ -30853,7 +30853,7 @@
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
@@ -30862,19 +30862,19 @@
         </is>
       </c>
       <c r="E823" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F823" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G823" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H823" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="I823" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="824">
@@ -30885,12 +30885,12 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
@@ -30899,13 +30899,13 @@
         </is>
       </c>
       <c r="E824" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F824" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G824" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -30922,12 +30922,12 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
@@ -30936,19 +30936,19 @@
         </is>
       </c>
       <c r="E825" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F825" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G825" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H825" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="I825" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="826">
@@ -30959,7 +30959,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -30969,17 +30969,17 @@
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E826" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F826" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G826" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H826" t="n">
         <v>0</v>
@@ -30996,33 +30996,33 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E827" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F827" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G827" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H827" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I827" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="828">
@@ -31033,17 +31033,17 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E828" t="n">
@@ -31070,12 +31070,12 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
@@ -31084,13 +31084,13 @@
         </is>
       </c>
       <c r="E829" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F829" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G829" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -31121,13 +31121,13 @@
         </is>
       </c>
       <c r="E830" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F830" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G830" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -31149,22 +31149,22 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E831" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F831" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G831" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -31186,22 +31186,22 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E832" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F832" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G832" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -31223,7 +31223,7 @@
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
@@ -31232,13 +31232,13 @@
         </is>
       </c>
       <c r="E833" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F833" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G833" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -31260,7 +31260,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
@@ -31297,7 +31297,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
@@ -31306,13 +31306,13 @@
         </is>
       </c>
       <c r="E835" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F835" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G835" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -31329,12 +31329,12 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
@@ -31343,19 +31343,19 @@
         </is>
       </c>
       <c r="E836" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F836" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G836" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H836" t="n">
-        <v>1316</v>
+        <v>0</v>
       </c>
       <c r="I836" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="837">
@@ -31366,12 +31366,12 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
@@ -31380,19 +31380,19 @@
         </is>
       </c>
       <c r="E837" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F837" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G837" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H837" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I837" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="838">
@@ -31403,33 +31403,33 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E838" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F838" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G838" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H838" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="I838" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="839">
@@ -31440,12 +31440,12 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
@@ -31454,19 +31454,19 @@
         </is>
       </c>
       <c r="E839" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F839" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G839" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H839" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="I839" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="840">
@@ -31482,7 +31482,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -31500,10 +31500,10 @@
         <v>1</v>
       </c>
       <c r="H840" t="n">
-        <v>0</v>
+        <v>1379</v>
       </c>
       <c r="I840" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="841">
@@ -31519,7 +31519,7 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
@@ -31537,10 +31537,10 @@
         <v>0</v>
       </c>
       <c r="H841" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I841" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="842">
@@ -31556,7 +31556,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -31574,10 +31574,10 @@
         <v>0</v>
       </c>
       <c r="H842" t="n">
-        <v>19</v>
+        <v>217</v>
       </c>
       <c r="I842" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="843">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
@@ -31611,10 +31611,10 @@
         <v>0</v>
       </c>
       <c r="H843" t="n">
-        <v>132</v>
+        <v>333</v>
       </c>
       <c r="I843" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="844">
@@ -31625,33 +31625,33 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E844" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F844" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G844" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H844" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="I844" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="845">
@@ -31662,12 +31662,12 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -31676,13 +31676,13 @@
         </is>
       </c>
       <c r="E845" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F845" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G845" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H845" t="n">
         <v>0</v>
@@ -31699,33 +31699,33 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E846" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F846" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G846" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H846" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I846" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="847">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
@@ -31759,10 +31759,10 @@
         <v>0</v>
       </c>
       <c r="H847" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="I847" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="848">
@@ -31778,7 +31778,7 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
@@ -31787,19 +31787,19 @@
         </is>
       </c>
       <c r="E848" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F848" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G848" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H848" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="I848" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="849">
@@ -31815,7 +31815,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
@@ -31824,13 +31824,13 @@
         </is>
       </c>
       <c r="E849" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F849" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G849" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -31852,28 +31852,28 @@
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E850" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F850" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G850" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H850" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I850" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="851">
@@ -31889,7 +31889,7 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
@@ -31898,13 +31898,13 @@
         </is>
       </c>
       <c r="E851" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F851" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G851" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H851" t="n">
         <v>0</v>
@@ -31926,22 +31926,22 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E852" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F852" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G852" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H852" t="n">
         <v>0</v>
@@ -31963,22 +31963,22 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E853" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F853" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G853" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H853" t="n">
         <v>0</v>
@@ -32000,7 +32000,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -32009,19 +32009,19 @@
         </is>
       </c>
       <c r="E854" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F854" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G854" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H854" t="n">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="I854" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="855">
@@ -32037,12 +32037,12 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E855" t="n">
@@ -32055,10 +32055,10 @@
         <v>1</v>
       </c>
       <c r="H855" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I855" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="856">
@@ -32074,28 +32074,28 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E856" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F856" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G856" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H856" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I856" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="857">
@@ -32106,27 +32106,27 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E857" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F857" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G857" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -32143,27 +32143,27 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E858" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F858" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G858" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -32180,12 +32180,12 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -32203,10 +32203,10 @@
         <v>0</v>
       </c>
       <c r="H859" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="I859" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="860">
@@ -32217,17 +32217,17 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E860" t="n">
@@ -32240,10 +32240,10 @@
         <v>1</v>
       </c>
       <c r="H860" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I860" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="861">
@@ -32254,12 +32254,12 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
@@ -32268,19 +32268,19 @@
         </is>
       </c>
       <c r="E861" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F861" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G861" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H861" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I861" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="862">
@@ -32296,7 +32296,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
@@ -32305,13 +32305,13 @@
         </is>
       </c>
       <c r="E862" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F862" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G862" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H862" t="n">
         <v>0</v>
@@ -32333,7 +32333,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
@@ -32342,19 +32342,19 @@
         </is>
       </c>
       <c r="E863" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F863" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G863" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H863" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="I863" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="864">
@@ -32370,7 +32370,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
@@ -32379,13 +32379,13 @@
         </is>
       </c>
       <c r="E864" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F864" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G864" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H864" t="n">
         <v>0</v>
@@ -32407,7 +32407,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
@@ -32416,19 +32416,19 @@
         </is>
       </c>
       <c r="E865" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F865" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G865" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H865" t="n">
-        <v>2184</v>
+        <v>0</v>
       </c>
       <c r="I865" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="866">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
@@ -32462,10 +32462,10 @@
         <v>4</v>
       </c>
       <c r="H866" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I866" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="867">
@@ -32481,7 +32481,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -32490,13 +32490,13 @@
         </is>
       </c>
       <c r="E867" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F867" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G867" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -32518,7 +32518,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
@@ -32527,19 +32527,19 @@
         </is>
       </c>
       <c r="E868" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F868" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G868" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H868" t="n">
-        <v>198</v>
+        <v>392</v>
       </c>
       <c r="I868" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="869">
@@ -32555,22 +32555,22 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E869" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F869" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G869" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -32592,27 +32592,249 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
+          <t>£25K-£50K</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E870" t="n">
+        <v>1</v>
+      </c>
+      <c r="F870" t="n">
+        <v>1</v>
+      </c>
+      <c r="G870" t="n">
+        <v>1</v>
+      </c>
+      <c r="H870" t="n">
+        <v>0</v>
+      </c>
+      <c r="I870" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>£25K-£50K</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E871" t="n">
+        <v>4</v>
+      </c>
+      <c r="F871" t="n">
+        <v>4</v>
+      </c>
+      <c r="G871" t="n">
+        <v>4</v>
+      </c>
+      <c r="H871" t="n">
+        <v>2346</v>
+      </c>
+      <c r="I871" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E872" t="n">
+        <v>5</v>
+      </c>
+      <c r="F872" t="n">
+        <v>5</v>
+      </c>
+      <c r="G872" t="n">
+        <v>5</v>
+      </c>
+      <c r="H872" t="n">
+        <v>119</v>
+      </c>
+      <c r="I872" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E873" t="n">
+        <v>1</v>
+      </c>
+      <c r="F873" t="n">
+        <v>1</v>
+      </c>
+      <c r="G873" t="n">
+        <v>1</v>
+      </c>
+      <c r="H873" t="n">
+        <v>0</v>
+      </c>
+      <c r="I873" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E874" t="n">
+        <v>0</v>
+      </c>
+      <c r="F874" t="n">
+        <v>0</v>
+      </c>
+      <c r="G874" t="n">
+        <v>0</v>
+      </c>
+      <c r="H874" t="n">
+        <v>198</v>
+      </c>
+      <c r="I874" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
           <t>£5K-£10K</t>
         </is>
       </c>
-      <c r="D870" t="inlineStr">
-        <is>
-          <t>Old</t>
-        </is>
-      </c>
-      <c r="E870" t="n">
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E875" t="n">
+        <v>1</v>
+      </c>
+      <c r="F875" t="n">
+        <v>1</v>
+      </c>
+      <c r="G875" t="n">
+        <v>1</v>
+      </c>
+      <c r="H875" t="n">
+        <v>0</v>
+      </c>
+      <c r="I875" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E876" t="n">
         <v>3</v>
       </c>
-      <c r="F870" t="n">
+      <c r="F876" t="n">
         <v>4</v>
       </c>
-      <c r="G870" t="n">
+      <c r="G876" t="n">
         <v>4</v>
       </c>
-      <c r="H870" t="n">
+      <c r="H876" t="n">
         <v>30</v>
       </c>
-      <c r="I870" t="n">
+      <c r="I876" t="n">
         <v>1</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I879"/>
+  <dimension ref="A1:I881"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18069,10 +18069,10 @@
         <v>307</v>
       </c>
       <c r="H477" t="n">
-        <v>2874</v>
+        <v>3010</v>
       </c>
       <c r="I477" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="478">
@@ -18883,10 +18883,10 @@
         <v>59</v>
       </c>
       <c r="H499" t="n">
-        <v>722</v>
+        <v>585</v>
       </c>
       <c r="I499" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="500">
@@ -24692,10 +24692,10 @@
         <v>280</v>
       </c>
       <c r="H656" t="n">
-        <v>17702</v>
+        <v>17757</v>
       </c>
       <c r="I656" t="n">
-        <v>952</v>
+        <v>956</v>
       </c>
     </row>
     <row r="657">
@@ -25543,10 +25543,10 @@
         <v>154</v>
       </c>
       <c r="H679" t="n">
-        <v>1610</v>
+        <v>1555</v>
       </c>
       <c r="I679" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="680">
@@ -28975,19 +28975,19 @@
         </is>
       </c>
       <c r="E772" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F772" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G772" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H772" t="n">
-        <v>481</v>
+        <v>4099</v>
       </c>
       <c r="I772" t="n">
-        <v>15</v>
+        <v>180</v>
       </c>
     </row>
     <row r="773">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="E774" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F774" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G774" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H774" t="n">
         <v>0</v>
@@ -29086,13 +29086,13 @@
         </is>
       </c>
       <c r="E775" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F775" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G775" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H775" t="n">
         <v>587</v>
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="E777" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F777" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G777" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H777" t="n">
         <v>303</v>
@@ -29234,13 +29234,13 @@
         </is>
       </c>
       <c r="E779" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F779" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G779" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H779" t="n">
         <v>5589</v>
@@ -29280,10 +29280,10 @@
         <v>16</v>
       </c>
       <c r="H780" t="n">
-        <v>241</v>
+        <v>117</v>
       </c>
       <c r="I780" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="781">
@@ -29308,13 +29308,13 @@
         </is>
       </c>
       <c r="E781" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F781" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G781" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H781" t="n">
         <v>6299</v>
@@ -29382,13 +29382,13 @@
         </is>
       </c>
       <c r="E783" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F783" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G783" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H783" t="n">
         <v>924</v>
@@ -29604,13 +29604,13 @@
         </is>
       </c>
       <c r="E789" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F789" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G789" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H789" t="n">
         <v>1503</v>
@@ -29789,19 +29789,19 @@
         </is>
       </c>
       <c r="E794" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="F794" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G794" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H794" t="n">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="I794" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="795">
@@ -29863,13 +29863,13 @@
         </is>
       </c>
       <c r="E796" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F796" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G796" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H796" t="n">
         <v>0</v>
@@ -29974,13 +29974,13 @@
         </is>
       </c>
       <c r="E799" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F799" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G799" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H799" t="n">
         <v>0</v>
@@ -30048,13 +30048,13 @@
         </is>
       </c>
       <c r="E801" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F801" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G801" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H801" t="n">
         <v>5875</v>
@@ -30088,10 +30088,10 @@
         <v>6</v>
       </c>
       <c r="F802" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G802" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H802" t="n">
         <v>0</v>
@@ -30122,13 +30122,13 @@
         </is>
       </c>
       <c r="E803" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F803" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G803" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H803" t="n">
         <v>1014</v>
@@ -30196,13 +30196,13 @@
         </is>
       </c>
       <c r="E805" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F805" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G805" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H805" t="n">
         <v>124</v>
@@ -30418,13 +30418,13 @@
         </is>
       </c>
       <c r="E811" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F811" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G811" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H811" t="n">
         <v>84</v>
@@ -30529,19 +30529,19 @@
         </is>
       </c>
       <c r="E814" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F814" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G814" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H814" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I814" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="815">
@@ -30566,13 +30566,13 @@
         </is>
       </c>
       <c r="E815" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F815" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G815" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H815" t="n">
         <v>1706</v>
@@ -30603,13 +30603,13 @@
         </is>
       </c>
       <c r="E816" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F816" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G816" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H816" t="n">
         <v>0</v>
@@ -30751,13 +30751,13 @@
         </is>
       </c>
       <c r="E820" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F820" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G820" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H820" t="n">
         <v>59</v>
@@ -30862,13 +30862,13 @@
         </is>
       </c>
       <c r="E823" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F823" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G823" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -31075,12 +31075,12 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E829" t="n">
@@ -31112,7 +31112,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -31144,27 +31144,27 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E831" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F831" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G831" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -31181,17 +31181,17 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E832" t="n">
@@ -31223,7 +31223,7 @@
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
@@ -31232,13 +31232,13 @@
         </is>
       </c>
       <c r="E833" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F833" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G833" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -31260,12 +31260,12 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E834" t="n">
@@ -31297,7 +31297,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
@@ -31334,7 +31334,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
@@ -31343,13 +31343,13 @@
         </is>
       </c>
       <c r="E836" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F836" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G836" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -31371,22 +31371,22 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E837" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F837" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G837" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H837" t="n">
         <v>0</v>
@@ -31408,7 +31408,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
@@ -31417,13 +31417,13 @@
         </is>
       </c>
       <c r="E838" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F838" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G838" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H838" t="n">
         <v>0</v>
@@ -31445,22 +31445,22 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E839" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F839" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G839" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -31482,7 +31482,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -31491,13 +31491,13 @@
         </is>
       </c>
       <c r="E840" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F840" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G840" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H840" t="n">
         <v>0</v>
@@ -31514,17 +31514,17 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E841" t="n">
@@ -31537,10 +31537,10 @@
         <v>1</v>
       </c>
       <c r="H841" t="n">
-        <v>1448</v>
+        <v>0</v>
       </c>
       <c r="I841" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="842">
@@ -31551,12 +31551,12 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -31565,19 +31565,19 @@
         </is>
       </c>
       <c r="E842" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F842" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G842" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H842" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I842" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="843">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
@@ -31602,19 +31602,19 @@
         </is>
       </c>
       <c r="E843" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F843" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G843" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H843" t="n">
-        <v>236</v>
+        <v>1448</v>
       </c>
       <c r="I843" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
     </row>
     <row r="844">
@@ -31630,7 +31630,7 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
@@ -31648,10 +31648,10 @@
         <v>0</v>
       </c>
       <c r="H844" t="n">
-        <v>352</v>
+        <v>19</v>
       </c>
       <c r="I844" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="845">
@@ -31667,7 +31667,7 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -31676,19 +31676,19 @@
         </is>
       </c>
       <c r="E845" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F845" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G845" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H845" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="I845" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="846">
@@ -31704,7 +31704,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
@@ -31722,10 +31722,10 @@
         <v>0</v>
       </c>
       <c r="H846" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="I846" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="847">
@@ -31741,7 +31741,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
@@ -31750,19 +31750,19 @@
         </is>
       </c>
       <c r="E847" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F847" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G847" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H847" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I847" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="848">
@@ -31778,7 +31778,7 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
@@ -31796,10 +31796,10 @@
         <v>0</v>
       </c>
       <c r="H848" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="I848" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="849">
@@ -31810,33 +31810,33 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E849" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F849" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G849" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H849" t="n">
-        <v>301</v>
+        <v>19</v>
       </c>
       <c r="I849" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="850">
@@ -31847,12 +31847,12 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
@@ -31861,19 +31861,19 @@
         </is>
       </c>
       <c r="E850" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F850" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G850" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H850" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="I850" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="851">
@@ -31889,7 +31889,7 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
@@ -31898,19 +31898,19 @@
         </is>
       </c>
       <c r="E851" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F851" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G851" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H851" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="I851" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="852">
@@ -31926,7 +31926,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
@@ -31935,13 +31935,13 @@
         </is>
       </c>
       <c r="E852" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F852" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G852" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H852" t="n">
         <v>0</v>
@@ -31963,7 +31963,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
@@ -31972,13 +31972,13 @@
         </is>
       </c>
       <c r="E853" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F853" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G853" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H853" t="n">
         <v>0</v>
@@ -32000,7 +32000,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -32009,13 +32009,13 @@
         </is>
       </c>
       <c r="E854" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F854" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G854" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H854" t="n">
         <v>0</v>
@@ -32037,28 +32037,28 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E855" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F855" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G855" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H855" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I855" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="856">
@@ -32074,12 +32074,12 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E856" t="n">
@@ -32111,7 +32111,7 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
@@ -32120,19 +32120,19 @@
         </is>
       </c>
       <c r="E857" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F857" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G857" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H857" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I857" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="858">
@@ -32148,7 +32148,7 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -32185,7 +32185,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="E859" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F859" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G859" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H859" t="n">
         <v>0</v>
@@ -32222,7 +32222,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -32259,7 +32259,7 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
@@ -32268,19 +32268,19 @@
         </is>
       </c>
       <c r="E861" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F861" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G861" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H861" t="n">
-        <v>305</v>
+        <v>0</v>
       </c>
       <c r="I861" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="862">
@@ -32296,7 +32296,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
@@ -32314,10 +32314,10 @@
         <v>1</v>
       </c>
       <c r="H862" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I862" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="863">
@@ -32333,7 +32333,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
@@ -32342,19 +32342,19 @@
         </is>
       </c>
       <c r="E863" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F863" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G863" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H863" t="n">
-        <v>40</v>
+        <v>305</v>
       </c>
       <c r="I863" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="864">
@@ -32365,12 +32365,12 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
@@ -32379,13 +32379,13 @@
         </is>
       </c>
       <c r="E864" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F864" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G864" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H864" t="n">
         <v>0</v>
@@ -32402,12 +32402,12 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
@@ -32416,19 +32416,19 @@
         </is>
       </c>
       <c r="E865" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F865" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G865" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H865" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I865" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="866">
@@ -32444,22 +32444,22 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E866" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F866" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G866" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -32481,7 +32481,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -32490,13 +32490,13 @@
         </is>
       </c>
       <c r="E867" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F867" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G867" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -32518,12 +32518,12 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E868" t="n">
@@ -32555,7 +32555,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
@@ -32564,13 +32564,13 @@
         </is>
       </c>
       <c r="E869" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F869" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G869" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
@@ -32601,13 +32601,13 @@
         </is>
       </c>
       <c r="E870" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F870" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G870" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -32629,7 +32629,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
@@ -32638,19 +32638,19 @@
         </is>
       </c>
       <c r="E871" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F871" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="G871" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="H871" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="I871" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="872">
@@ -32666,28 +32666,28 @@
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E872" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F872" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G872" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H872" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="I872" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="873">
@@ -32703,28 +32703,28 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E873" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="F873" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G873" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="H873" t="n">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="I873" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="874">
@@ -32740,7 +32740,7 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
@@ -32749,19 +32749,19 @@
         </is>
       </c>
       <c r="E874" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F874" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G874" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H874" t="n">
-        <v>2440</v>
+        <v>0</v>
       </c>
       <c r="I874" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="875">
@@ -32777,28 +32777,28 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E875" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F875" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G875" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H875" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="I875" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="876">
@@ -32814,28 +32814,28 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E876" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F876" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G876" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H876" t="n">
-        <v>0</v>
+        <v>2440</v>
       </c>
       <c r="I876" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
     </row>
     <row r="877">
@@ -32851,7 +32851,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
@@ -32860,19 +32860,19 @@
         </is>
       </c>
       <c r="E877" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F877" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G877" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H877" t="n">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="I877" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="878">
@@ -32888,7 +32888,7 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
@@ -32925,27 +32925,101 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E879" t="n">
+        <v>0</v>
+      </c>
+      <c r="F879" t="n">
+        <v>0</v>
+      </c>
+      <c r="G879" t="n">
+        <v>0</v>
+      </c>
+      <c r="H879" t="n">
+        <v>198</v>
+      </c>
+      <c r="I879" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
           <t>£5K-£10K</t>
         </is>
       </c>
-      <c r="D879" t="inlineStr">
-        <is>
-          <t>Old</t>
-        </is>
-      </c>
-      <c r="E879" t="n">
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E880" t="n">
+        <v>1</v>
+      </c>
+      <c r="F880" t="n">
+        <v>1</v>
+      </c>
+      <c r="G880" t="n">
+        <v>1</v>
+      </c>
+      <c r="H880" t="n">
+        <v>0</v>
+      </c>
+      <c r="I880" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E881" t="n">
         <v>4</v>
       </c>
-      <c r="F879" t="n">
+      <c r="F881" t="n">
         <v>5</v>
       </c>
-      <c r="G879" t="n">
+      <c r="G881" t="n">
         <v>5</v>
       </c>
-      <c r="H879" t="n">
+      <c r="H881" t="n">
         <v>30</v>
       </c>
-      <c r="I879" t="n">
+      <c r="I881" t="n">
         <v>1</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I881"/>
+  <dimension ref="A1:I888"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18106,10 +18106,10 @@
         <v>149</v>
       </c>
       <c r="H478" t="n">
-        <v>10679</v>
+        <v>10719</v>
       </c>
       <c r="I478" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="479">
@@ -18920,10 +18920,10 @@
         <v>77</v>
       </c>
       <c r="H500" t="n">
-        <v>3440</v>
+        <v>3400</v>
       </c>
       <c r="I500" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="501">
@@ -20095,13 +20095,13 @@
         </is>
       </c>
       <c r="E532" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F532" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G532" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -20178,10 +20178,10 @@
         <v>890</v>
       </c>
       <c r="H534" t="n">
-        <v>183</v>
+        <v>93</v>
       </c>
       <c r="I534" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="535">
@@ -20252,10 +20252,10 @@
         <v>160</v>
       </c>
       <c r="H536" t="n">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="I536" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -20289,10 +20289,10 @@
         <v>24</v>
       </c>
       <c r="H537" t="n">
-        <v>557</v>
+        <v>532</v>
       </c>
       <c r="I537" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="538">
@@ -20326,10 +20326,10 @@
         <v>23</v>
       </c>
       <c r="H538" t="n">
-        <v>782</v>
+        <v>637</v>
       </c>
       <c r="I538" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="539">
@@ -20363,10 +20363,10 @@
         <v>21</v>
       </c>
       <c r="H539" t="n">
-        <v>4210</v>
+        <v>2826</v>
       </c>
       <c r="I539" t="n">
-        <v>151</v>
+        <v>93</v>
       </c>
     </row>
     <row r="540">
@@ -20400,10 +20400,10 @@
         <v>161</v>
       </c>
       <c r="H540" t="n">
-        <v>598</v>
+        <v>547</v>
       </c>
       <c r="I540" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="541">
@@ -20437,10 +20437,10 @@
         <v>127</v>
       </c>
       <c r="H541" t="n">
-        <v>6036</v>
+        <v>5543</v>
       </c>
       <c r="I541" t="n">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="542">
@@ -20474,10 +20474,10 @@
         <v>233</v>
       </c>
       <c r="H542" t="n">
-        <v>219</v>
+        <v>117</v>
       </c>
       <c r="I542" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="543">
@@ -20511,10 +20511,10 @@
         <v>100</v>
       </c>
       <c r="H543" t="n">
-        <v>1885</v>
+        <v>1851</v>
       </c>
       <c r="I543" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="544">
@@ -20548,10 +20548,10 @@
         <v>7</v>
       </c>
       <c r="H544" t="n">
-        <v>634</v>
+        <v>0</v>
       </c>
       <c r="I544" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="545">
@@ -20585,10 +20585,10 @@
         <v>6</v>
       </c>
       <c r="H545" t="n">
-        <v>6824</v>
+        <v>6401</v>
       </c>
       <c r="I545" t="n">
-        <v>262</v>
+        <v>253</v>
       </c>
     </row>
     <row r="546">
@@ -20622,10 +20622,10 @@
         <v>78</v>
       </c>
       <c r="H546" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="I546" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="547">
@@ -20687,19 +20687,19 @@
         </is>
       </c>
       <c r="E548" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F548" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G548" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H548" t="n">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="I548" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="549">
@@ -20733,10 +20733,10 @@
         <v>85</v>
       </c>
       <c r="H549" t="n">
-        <v>1565</v>
+        <v>1524</v>
       </c>
       <c r="I549" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="550">
@@ -20770,10 +20770,10 @@
         <v>6</v>
       </c>
       <c r="H550" t="n">
-        <v>243</v>
+        <v>100</v>
       </c>
       <c r="I550" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="551">
@@ -20807,10 +20807,10 @@
         <v>1</v>
       </c>
       <c r="H551" t="n">
-        <v>884</v>
+        <v>573</v>
       </c>
       <c r="I551" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="552">
@@ -20844,10 +20844,10 @@
         <v>28</v>
       </c>
       <c r="H552" t="n">
-        <v>737</v>
+        <v>280</v>
       </c>
       <c r="I552" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="553">
@@ -20881,10 +20881,10 @@
         <v>29</v>
       </c>
       <c r="H553" t="n">
-        <v>7360</v>
+        <v>5941</v>
       </c>
       <c r="I553" t="n">
-        <v>238</v>
+        <v>201</v>
       </c>
     </row>
     <row r="554">
@@ -21423,7 +21423,7 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E568" t="n">
@@ -21436,10 +21436,10 @@
         <v>0</v>
       </c>
       <c r="H568" t="n">
-        <v>0</v>
+        <v>2607</v>
       </c>
       <c r="I568" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="569">
@@ -21455,12 +21455,12 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E569" t="n">
@@ -21473,10 +21473,10 @@
         <v>0</v>
       </c>
       <c r="H569" t="n">
-        <v>2742</v>
+        <v>157</v>
       </c>
       <c r="I569" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
     </row>
     <row r="570">
@@ -21497,7 +21497,7 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E570" t="n">
@@ -21510,10 +21510,10 @@
         <v>0</v>
       </c>
       <c r="H570" t="n">
-        <v>177</v>
+        <v>926</v>
       </c>
       <c r="I570" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="571">
@@ -21529,12 +21529,12 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E571" t="n">
@@ -21547,10 +21547,10 @@
         <v>0</v>
       </c>
       <c r="H571" t="n">
-        <v>1015</v>
+        <v>0</v>
       </c>
       <c r="I571" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="572">
@@ -21571,7 +21571,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E572" t="n">
@@ -21584,10 +21584,10 @@
         <v>0</v>
       </c>
       <c r="H572" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="I572" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="573">
@@ -21603,7 +21603,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -21621,10 +21621,10 @@
         <v>0</v>
       </c>
       <c r="H573" t="n">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="I573" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="574">
@@ -21640,7 +21640,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -21658,10 +21658,10 @@
         <v>0</v>
       </c>
       <c r="H574" t="n">
-        <v>237</v>
+        <v>40</v>
       </c>
       <c r="I574" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="575">
@@ -21677,12 +21677,12 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E575" t="n">
@@ -21695,10 +21695,10 @@
         <v>0</v>
       </c>
       <c r="H575" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="I575" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="576">
@@ -21719,7 +21719,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E576" t="n">
@@ -21732,10 +21732,10 @@
         <v>0</v>
       </c>
       <c r="H576" t="n">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="I576" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="577">
@@ -21751,7 +21751,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -21769,10 +21769,10 @@
         <v>0</v>
       </c>
       <c r="H577" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="I577" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="578">
@@ -21788,12 +21788,12 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E578" t="n">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E579" t="n">
@@ -21843,10 +21843,10 @@
         <v>0</v>
       </c>
       <c r="H579" t="n">
-        <v>0</v>
+        <v>978</v>
       </c>
       <c r="I579" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="580">
@@ -21857,33 +21857,33 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E580" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F580" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G580" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H580" t="n">
-        <v>1073</v>
+        <v>15</v>
       </c>
       <c r="I580" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="581">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -21908,19 +21908,19 @@
         </is>
       </c>
       <c r="E581" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F581" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G581" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H581" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I581" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="582">
@@ -21941,7 +21941,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E582" t="n">
@@ -21973,22 +21973,22 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E583" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F583" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G583" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H583" t="n">
         <v>0</v>
@@ -22015,23 +22015,23 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E584" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F584" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G584" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H584" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I584" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="585">
@@ -22047,28 +22047,28 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E585" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F585" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G585" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H585" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="I585" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="586">
@@ -22089,23 +22089,23 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E586" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F586" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G586" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H586" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="I586" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="587">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -22130,19 +22130,19 @@
         </is>
       </c>
       <c r="E587" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F587" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G587" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H587" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I587" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="588">
@@ -22158,22 +22158,22 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E588" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F588" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G588" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -22200,17 +22200,17 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E589" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F589" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G589" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -22232,22 +22232,22 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E590" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F590" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G590" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -22274,17 +22274,17 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E591" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F591" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G591" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H591" t="n">
         <v>0</v>
@@ -22306,12 +22306,12 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E592" t="n">
@@ -22348,7 +22348,7 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E593" t="n">
@@ -22380,28 +22380,28 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F594" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G594" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H594" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I594" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="595">
@@ -22422,23 +22422,23 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F595" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G595" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H595" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I595" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="596">
@@ -22449,27 +22449,27 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>7</v>
+        <v>482</v>
       </c>
       <c r="F596" t="n">
-        <v>7</v>
+        <v>485</v>
       </c>
       <c r="G596" t="n">
-        <v>7</v>
+        <v>485</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -22500,13 +22500,13 @@
         </is>
       </c>
       <c r="E597" t="n">
-        <v>482</v>
+        <v>91</v>
       </c>
       <c r="F597" t="n">
-        <v>485</v>
+        <v>91</v>
       </c>
       <c r="G597" t="n">
-        <v>485</v>
+        <v>91</v>
       </c>
       <c r="H597" t="n">
         <v>0</v>
@@ -22533,17 +22533,17 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E598" t="n">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="F598" t="n">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="G598" t="n">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -22565,22 +22565,22 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E599" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F599" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G599" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -22607,17 +22607,17 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E600" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F600" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G600" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H600" t="n">
         <v>0</v>
@@ -22639,12 +22639,12 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E601" t="n">
@@ -22681,7 +22681,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E602" t="n">
@@ -22713,7 +22713,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -22750,22 +22750,22 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E604" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F604" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G604" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H604" t="n">
         <v>0</v>
@@ -22787,7 +22787,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -22796,13 +22796,13 @@
         </is>
       </c>
       <c r="E605" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F605" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G605" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H605" t="n">
         <v>0</v>
@@ -22829,17 +22829,17 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E606" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F606" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G606" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H606" t="n">
         <v>0</v>
@@ -22856,33 +22856,33 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E607" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F607" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G607" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H607" t="n">
-        <v>0</v>
+        <v>539</v>
       </c>
       <c r="I607" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="608">
@@ -23064,10 +23064,10 @@
         <v>5</v>
       </c>
       <c r="H612" t="n">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="I612" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="613">
@@ -23804,10 +23804,10 @@
         <v>9</v>
       </c>
       <c r="H632" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="I632" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="633">
@@ -23989,10 +23989,10 @@
         <v>1</v>
       </c>
       <c r="H637" t="n">
-        <v>4913</v>
+        <v>4358</v>
       </c>
       <c r="I637" t="n">
-        <v>147</v>
+        <v>128</v>
       </c>
     </row>
     <row r="638">
@@ -24174,10 +24174,10 @@
         <v>1</v>
       </c>
       <c r="H642" t="n">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="I642" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="643">
@@ -24396,10 +24396,10 @@
         <v>7</v>
       </c>
       <c r="H648" t="n">
-        <v>428</v>
+        <v>532</v>
       </c>
       <c r="I648" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="649">
@@ -24470,10 +24470,10 @@
         <v>6</v>
       </c>
       <c r="H650" t="n">
-        <v>383</v>
+        <v>423</v>
       </c>
       <c r="I650" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="651">
@@ -24544,10 +24544,10 @@
         <v>35</v>
       </c>
       <c r="H652" t="n">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="I652" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="653">
@@ -24581,10 +24581,10 @@
         <v>13</v>
       </c>
       <c r="H653" t="n">
-        <v>463</v>
+        <v>513</v>
       </c>
       <c r="I653" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="654">
@@ -24618,10 +24618,10 @@
         <v>30</v>
       </c>
       <c r="H654" t="n">
-        <v>14133</v>
+        <v>17048</v>
       </c>
       <c r="I654" t="n">
-        <v>565</v>
+        <v>682</v>
       </c>
     </row>
     <row r="655">
@@ -24655,10 +24655,10 @@
         <v>141</v>
       </c>
       <c r="H655" t="n">
-        <v>3068</v>
+        <v>3927</v>
       </c>
       <c r="I655" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
     </row>
     <row r="656">
@@ -24692,10 +24692,10 @@
         <v>280</v>
       </c>
       <c r="H656" t="n">
-        <v>17757</v>
+        <v>19090</v>
       </c>
       <c r="I656" t="n">
-        <v>956</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="657">
@@ -24766,10 +24766,10 @@
         <v>57</v>
       </c>
       <c r="H658" t="n">
-        <v>1428</v>
+        <v>1448</v>
       </c>
       <c r="I658" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="659">
@@ -24840,10 +24840,10 @@
         <v>16</v>
       </c>
       <c r="H660" t="n">
-        <v>18436</v>
+        <v>13998</v>
       </c>
       <c r="I660" t="n">
-        <v>831</v>
+        <v>650</v>
       </c>
     </row>
     <row r="661">
@@ -24988,10 +24988,10 @@
         <v>82</v>
       </c>
       <c r="H664" t="n">
-        <v>2852</v>
+        <v>3091</v>
       </c>
       <c r="I664" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="665">
@@ -25062,10 +25062,10 @@
         <v>6</v>
       </c>
       <c r="H666" t="n">
-        <v>5286</v>
+        <v>5879</v>
       </c>
       <c r="I666" t="n">
-        <v>218</v>
+        <v>241</v>
       </c>
     </row>
     <row r="667">
@@ -25136,10 +25136,10 @@
         <v>58</v>
       </c>
       <c r="H668" t="n">
-        <v>39452</v>
+        <v>42289</v>
       </c>
       <c r="I668" t="n">
-        <v>1565</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="669">
@@ -25469,10 +25469,10 @@
         <v>22</v>
       </c>
       <c r="H677" t="n">
-        <v>6449</v>
+        <v>6652</v>
       </c>
       <c r="I677" t="n">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="678">
@@ -25543,10 +25543,10 @@
         <v>154</v>
       </c>
       <c r="H679" t="n">
-        <v>1555</v>
+        <v>1065</v>
       </c>
       <c r="I679" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="680">
@@ -25802,10 +25802,10 @@
         <v>51</v>
       </c>
       <c r="H686" t="n">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="I686" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="687">
@@ -25913,10 +25913,10 @@
         <v>7</v>
       </c>
       <c r="H689" t="n">
-        <v>4170</v>
+        <v>4208</v>
       </c>
       <c r="I689" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="690">
@@ -25950,10 +25950,10 @@
         <v>13</v>
       </c>
       <c r="H690" t="n">
-        <v>471</v>
+        <v>524</v>
       </c>
       <c r="I690" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="691">
@@ -26963,33 +26963,33 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E718" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F718" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G718" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H718" t="n">
-        <v>0</v>
+        <v>5657</v>
       </c>
       <c r="I718" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
     </row>
     <row r="719">
@@ -27010,17 +27010,17 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E719" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F719" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G719" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -27042,28 +27042,28 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E720" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="F720" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G720" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="H720" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="I720" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="721">
@@ -27084,23 +27084,23 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E721" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F721" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G721" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="H721" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="I721" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="722">
@@ -27116,28 +27116,28 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E722" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F722" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G722" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H722" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="I722" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="723">
@@ -27158,23 +27158,23 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E723" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F723" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G723" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H723" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I723" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="724">
@@ -27190,28 +27190,28 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E724" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="F724" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G724" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="H724" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I724" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="725">
@@ -27232,23 +27232,23 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E725" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F725" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G725" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H725" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="I725" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="726">
@@ -27264,28 +27264,28 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E726" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="F726" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="G726" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="H726" t="n">
-        <v>1331</v>
+        <v>0</v>
       </c>
       <c r="I726" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="727">
@@ -27306,23 +27306,23 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E727" t="n">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="F727" t="n">
-        <v>123</v>
+        <v>44</v>
       </c>
       <c r="G727" t="n">
-        <v>123</v>
+        <v>44</v>
       </c>
       <c r="H727" t="n">
-        <v>0</v>
+        <v>1450</v>
       </c>
       <c r="I727" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="728">
@@ -27338,22 +27338,22 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E728" t="n">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="F728" t="n">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G728" t="n">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="H728" t="n">
         <v>0</v>
@@ -27380,17 +27380,17 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E729" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F729" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G729" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H729" t="n">
         <v>0</v>
@@ -27412,7 +27412,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -27421,13 +27421,13 @@
         </is>
       </c>
       <c r="E730" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F730" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="G730" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -27449,22 +27449,22 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E731" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F731" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G731" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H731" t="n">
         <v>0</v>
@@ -27491,17 +27491,17 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E732" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F732" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G732" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H732" t="n">
         <v>0</v>
@@ -27523,28 +27523,28 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E733" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="F733" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="G733" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="H733" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I733" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="734">
@@ -27565,23 +27565,23 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E734" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="F734" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G734" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="H734" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I734" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="735">
@@ -27597,22 +27597,22 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E735" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="F735" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="G735" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -27639,17 +27639,17 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E736" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F736" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G736" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -27671,12 +27671,12 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E737" t="n">
@@ -27713,17 +27713,17 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E738" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F738" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G738" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H738" t="n">
         <v>0</v>
@@ -27740,12 +27740,12 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
@@ -27754,13 +27754,13 @@
         </is>
       </c>
       <c r="E739" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="F739" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="G739" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -27782,22 +27782,22 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E740" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F740" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G740" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H740" t="n">
         <v>0</v>
@@ -27824,17 +27824,17 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E741" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F741" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G741" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H741" t="n">
         <v>0</v>
@@ -27856,22 +27856,22 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E742" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F742" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G742" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H742" t="n">
         <v>0</v>
@@ -27898,17 +27898,17 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E743" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F743" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G743" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H743" t="n">
         <v>0</v>
@@ -27930,22 +27930,22 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E744" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F744" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G744" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H744" t="n">
         <v>0</v>
@@ -27972,23 +27972,23 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E745" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F745" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G745" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H745" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="I745" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="746">
@@ -28004,28 +28004,28 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E746" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F746" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G746" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H746" t="n">
-        <v>115</v>
+        <v>351</v>
       </c>
       <c r="I746" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="747">
@@ -28046,23 +28046,23 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E747" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="F747" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="G747" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="H747" t="n">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="I747" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="748">
@@ -28078,28 +28078,28 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E748" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="F748" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="G748" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="H748" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I748" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="749">
@@ -28120,23 +28120,23 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E749" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F749" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G749" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H749" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I749" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="750">
@@ -28152,7 +28152,7 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
@@ -28161,19 +28161,19 @@
         </is>
       </c>
       <c r="E750" t="n">
+        <v>8</v>
+      </c>
+      <c r="F750" t="n">
+        <v>8</v>
+      </c>
+      <c r="G750" t="n">
+        <v>8</v>
+      </c>
+      <c r="H750" t="n">
+        <v>80</v>
+      </c>
+      <c r="I750" t="n">
         <v>2</v>
-      </c>
-      <c r="F750" t="n">
-        <v>2</v>
-      </c>
-      <c r="G750" t="n">
-        <v>2</v>
-      </c>
-      <c r="H750" t="n">
-        <v>329</v>
-      </c>
-      <c r="I750" t="n">
-        <v>29</v>
       </c>
     </row>
     <row r="751">
@@ -28189,28 +28189,28 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E751" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F751" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G751" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H751" t="n">
-        <v>54</v>
+        <v>372</v>
       </c>
       <c r="I751" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="752">
@@ -28231,23 +28231,23 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E752" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F752" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G752" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H752" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="I752" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="753">
@@ -28263,28 +28263,28 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E753" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F753" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G753" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H753" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I753" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="754">
@@ -28305,17 +28305,17 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E754" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F754" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G754" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H754" t="n">
         <v>0</v>
@@ -28337,12 +28337,12 @@
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E755" t="n">
@@ -28379,17 +28379,17 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E756" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F756" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G756" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H756" t="n">
         <v>0</v>
@@ -28406,12 +28406,12 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
@@ -28420,13 +28420,13 @@
         </is>
       </c>
       <c r="E757" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F757" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G757" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H757" t="n">
         <v>0</v>
@@ -28614,10 +28614,10 @@
         <v>16</v>
       </c>
       <c r="H762" t="n">
-        <v>136</v>
+        <v>717</v>
       </c>
       <c r="I762" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="763">
@@ -28725,10 +28725,10 @@
         <v>1</v>
       </c>
       <c r="H765" t="n">
-        <v>2495</v>
+        <v>2615</v>
       </c>
       <c r="I765" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="766">
@@ -28910,10 +28910,10 @@
         <v>1</v>
       </c>
       <c r="H770" t="n">
-        <v>364</v>
+        <v>409</v>
       </c>
       <c r="I770" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="771">
@@ -28975,7 +28975,7 @@
         </is>
       </c>
       <c r="E772" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F772" t="n">
         <v>101</v>
@@ -28984,10 +28984,10 @@
         <v>101</v>
       </c>
       <c r="H772" t="n">
-        <v>4099</v>
+        <v>298</v>
       </c>
       <c r="I772" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
     </row>
     <row r="773">
@@ -29012,19 +29012,19 @@
         </is>
       </c>
       <c r="E773" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F773" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G773" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H773" t="n">
-        <v>3256</v>
+        <v>4558</v>
       </c>
       <c r="I773" t="n">
-        <v>148</v>
+        <v>202</v>
       </c>
     </row>
     <row r="774">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="E774" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F774" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G774" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H774" t="n">
         <v>0</v>
@@ -29095,10 +29095,10 @@
         <v>5</v>
       </c>
       <c r="H775" t="n">
-        <v>587</v>
+        <v>749</v>
       </c>
       <c r="I775" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="776">
@@ -29169,10 +29169,10 @@
         <v>3</v>
       </c>
       <c r="H777" t="n">
-        <v>303</v>
+        <v>494</v>
       </c>
       <c r="I777" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="778">
@@ -29197,19 +29197,19 @@
         </is>
       </c>
       <c r="E778" t="n">
+        <v>14</v>
+      </c>
+      <c r="F778" t="n">
+        <v>14</v>
+      </c>
+      <c r="G778" t="n">
+        <v>14</v>
+      </c>
+      <c r="H778" t="n">
+        <v>353</v>
+      </c>
+      <c r="I778" t="n">
         <v>13</v>
-      </c>
-      <c r="F778" t="n">
-        <v>13</v>
-      </c>
-      <c r="G778" t="n">
-        <v>13</v>
-      </c>
-      <c r="H778" t="n">
-        <v>301</v>
-      </c>
-      <c r="I778" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="779">
@@ -29234,19 +29234,19 @@
         </is>
       </c>
       <c r="E779" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F779" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G779" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H779" t="n">
-        <v>5589</v>
+        <v>8742</v>
       </c>
       <c r="I779" t="n">
-        <v>192</v>
+        <v>303</v>
       </c>
     </row>
     <row r="780">
@@ -29271,19 +29271,19 @@
         </is>
       </c>
       <c r="E780" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F780" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G780" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="H780" t="n">
-        <v>117</v>
+        <v>391</v>
       </c>
       <c r="I780" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="781">
@@ -29308,19 +29308,19 @@
         </is>
       </c>
       <c r="E781" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F781" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G781" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H781" t="n">
-        <v>6299</v>
+        <v>8291</v>
       </c>
       <c r="I781" t="n">
-        <v>252</v>
+        <v>330</v>
       </c>
     </row>
     <row r="782">
@@ -29382,19 +29382,19 @@
         </is>
       </c>
       <c r="E783" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F783" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G783" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H783" t="n">
-        <v>924</v>
+        <v>1412</v>
       </c>
       <c r="I783" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="784">
@@ -29465,10 +29465,10 @@
         <v>5</v>
       </c>
       <c r="H785" t="n">
-        <v>7900</v>
+        <v>6755</v>
       </c>
       <c r="I785" t="n">
-        <v>284</v>
+        <v>238</v>
       </c>
     </row>
     <row r="786">
@@ -29567,13 +29567,13 @@
         </is>
       </c>
       <c r="E788" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F788" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G788" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H788" t="n">
         <v>65</v>
@@ -29607,16 +29607,16 @@
         <v>16</v>
       </c>
       <c r="F789" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G789" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H789" t="n">
-        <v>1503</v>
+        <v>2470</v>
       </c>
       <c r="I789" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
     </row>
     <row r="790">
@@ -29678,19 +29678,19 @@
         </is>
       </c>
       <c r="E791" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F791" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G791" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H791" t="n">
-        <v>3133</v>
+        <v>3884</v>
       </c>
       <c r="I791" t="n">
-        <v>109</v>
+        <v>141</v>
       </c>
     </row>
     <row r="792">
@@ -29715,19 +29715,19 @@
         </is>
       </c>
       <c r="E792" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F792" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G792" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H792" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="I792" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="793">
@@ -29752,19 +29752,19 @@
         </is>
       </c>
       <c r="E793" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F793" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G793" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H793" t="n">
-        <v>7764</v>
+        <v>15885</v>
       </c>
       <c r="I793" t="n">
-        <v>252</v>
+        <v>490</v>
       </c>
     </row>
     <row r="794">
@@ -29789,19 +29789,19 @@
         </is>
       </c>
       <c r="E794" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="F794" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G794" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="H794" t="n">
-        <v>159</v>
+        <v>46</v>
       </c>
       <c r="I794" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="795">
@@ -29826,13 +29826,13 @@
         </is>
       </c>
       <c r="E795" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F795" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G795" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H795" t="n">
         <v>0</v>
@@ -29863,13 +29863,13 @@
         </is>
       </c>
       <c r="E796" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F796" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G796" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H796" t="n">
         <v>0</v>
@@ -29900,19 +29900,19 @@
         </is>
       </c>
       <c r="E797" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F797" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G797" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H797" t="n">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="I797" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="798">
@@ -29974,19 +29974,19 @@
         </is>
       </c>
       <c r="E799" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F799" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G799" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H799" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I799" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="800">
@@ -30011,19 +30011,19 @@
         </is>
       </c>
       <c r="E800" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F800" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G800" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H800" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="I800" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="801">
@@ -30057,10 +30057,10 @@
         <v>9</v>
       </c>
       <c r="H801" t="n">
-        <v>5875</v>
+        <v>7994</v>
       </c>
       <c r="I801" t="n">
-        <v>258</v>
+        <v>352</v>
       </c>
     </row>
     <row r="802">
@@ -30085,19 +30085,19 @@
         </is>
       </c>
       <c r="E802" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F802" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G802" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="H802" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="I802" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="803">
@@ -30122,19 +30122,19 @@
         </is>
       </c>
       <c r="E803" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="F803" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="G803" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="H803" t="n">
-        <v>1014</v>
+        <v>2516</v>
       </c>
       <c r="I803" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
     </row>
     <row r="804">
@@ -30159,13 +30159,13 @@
         </is>
       </c>
       <c r="E804" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F804" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G804" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H804" t="n">
         <v>0</v>
@@ -30196,19 +30196,19 @@
         </is>
       </c>
       <c r="E805" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F805" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G805" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H805" t="n">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="I805" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="806">
@@ -30270,13 +30270,13 @@
         </is>
       </c>
       <c r="E807" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F807" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G807" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H807" t="n">
         <v>209</v>
@@ -30353,10 +30353,10 @@
         <v>2</v>
       </c>
       <c r="H809" t="n">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I809" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="810">
@@ -30418,13 +30418,13 @@
         </is>
       </c>
       <c r="E811" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F811" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G811" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H811" t="n">
         <v>84</v>
@@ -30501,10 +30501,10 @@
         <v>3</v>
       </c>
       <c r="H813" t="n">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="I813" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="814">
@@ -30529,19 +30529,19 @@
         </is>
       </c>
       <c r="E814" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F814" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G814" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H814" t="n">
-        <v>30</v>
+        <v>3966</v>
       </c>
       <c r="I814" t="n">
-        <v>2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="815">
@@ -30566,19 +30566,19 @@
         </is>
       </c>
       <c r="E815" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F815" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G815" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H815" t="n">
-        <v>1706</v>
+        <v>2656</v>
       </c>
       <c r="I815" t="n">
-        <v>76</v>
+        <v>123</v>
       </c>
     </row>
     <row r="816">
@@ -30603,13 +30603,13 @@
         </is>
       </c>
       <c r="E816" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F816" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G816" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H816" t="n">
         <v>0</v>
@@ -30631,12 +30631,12 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E817" t="n">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
@@ -30677,13 +30677,13 @@
         </is>
       </c>
       <c r="E818" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F818" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G818" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H818" t="n">
         <v>0</v>
@@ -30705,7 +30705,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
@@ -30714,13 +30714,13 @@
         </is>
       </c>
       <c r="E819" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F819" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G819" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H819" t="n">
         <v>0</v>
@@ -30742,28 +30742,28 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E820" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F820" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G820" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H820" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="I820" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="821">
@@ -30779,22 +30779,22 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E821" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F821" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G821" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H821" t="n">
         <v>0</v>
@@ -30816,7 +30816,7 @@
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
@@ -30825,19 +30825,19 @@
         </is>
       </c>
       <c r="E822" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F822" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G822" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H822" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="I822" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="823">
@@ -30853,7 +30853,7 @@
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
@@ -30862,13 +30862,13 @@
         </is>
       </c>
       <c r="E823" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F823" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G823" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -30890,7 +30890,7 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
@@ -30899,19 +30899,19 @@
         </is>
       </c>
       <c r="E824" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F824" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G824" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H824" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I824" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="825">
@@ -30927,22 +30927,22 @@
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E825" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F825" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G825" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H825" t="n">
         <v>0</v>
@@ -30964,7 +30964,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
@@ -30973,19 +30973,19 @@
         </is>
       </c>
       <c r="E826" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F826" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G826" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H826" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="I826" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="827">
@@ -30996,12 +30996,12 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
@@ -31010,13 +31010,13 @@
         </is>
       </c>
       <c r="E827" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F827" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G827" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -31033,7 +31033,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -31047,19 +31047,19 @@
         </is>
       </c>
       <c r="E828" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F828" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G828" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H828" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I828" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="829">
@@ -31070,33 +31070,33 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E829" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F829" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G829" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H829" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="I829" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="830">
@@ -31107,12 +31107,12 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -31121,13 +31121,13 @@
         </is>
       </c>
       <c r="E830" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F830" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G830" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -31144,12 +31144,12 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -31158,19 +31158,19 @@
         </is>
       </c>
       <c r="E831" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F831" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G831" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H831" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I831" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="832">
@@ -31186,12 +31186,12 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E832" t="n">
@@ -31218,27 +31218,27 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E833" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F833" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G833" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -31255,27 +31255,27 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E834" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F834" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G834" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -31292,17 +31292,17 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E835" t="n">
@@ -31329,12 +31329,12 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
@@ -31343,13 +31343,13 @@
         </is>
       </c>
       <c r="E836" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F836" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G836" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -31371,7 +31371,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
@@ -31380,19 +31380,19 @@
         </is>
       </c>
       <c r="E837" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F837" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G837" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H837" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I837" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="838">
@@ -31408,22 +31408,22 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E838" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F838" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G838" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H838" t="n">
         <v>0</v>
@@ -31445,22 +31445,22 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E839" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F839" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G839" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -31482,7 +31482,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -31491,13 +31491,13 @@
         </is>
       </c>
       <c r="E840" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F840" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G840" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H840" t="n">
         <v>0</v>
@@ -31519,7 +31519,7 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
@@ -31528,13 +31528,13 @@
         </is>
       </c>
       <c r="E841" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F841" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G841" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H841" t="n">
         <v>0</v>
@@ -31556,7 +31556,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -31565,13 +31565,13 @@
         </is>
       </c>
       <c r="E842" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F842" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G842" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H842" t="n">
         <v>0</v>
@@ -31588,12 +31588,12 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
@@ -31602,19 +31602,19 @@
         </is>
       </c>
       <c r="E843" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F843" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G843" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H843" t="n">
-        <v>1448</v>
+        <v>5104</v>
       </c>
       <c r="I843" t="n">
-        <v>65</v>
+        <v>179</v>
       </c>
     </row>
     <row r="844">
@@ -31625,33 +31625,33 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E844" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F844" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G844" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H844" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I844" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="845">
@@ -31662,12 +31662,12 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -31676,19 +31676,19 @@
         </is>
       </c>
       <c r="E845" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F845" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G845" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H845" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="I845" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="846">
@@ -31699,33 +31699,33 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E846" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F846" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G846" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H846" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="I846" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="847">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
@@ -31750,13 +31750,13 @@
         </is>
       </c>
       <c r="E847" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F847" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G847" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -31778,7 +31778,7 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
@@ -31787,19 +31787,19 @@
         </is>
       </c>
       <c r="E848" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F848" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G848" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H848" t="n">
-        <v>0</v>
+        <v>2018</v>
       </c>
       <c r="I848" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
     </row>
     <row r="849">
@@ -31815,7 +31815,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
@@ -31852,7 +31852,7 @@
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
@@ -31870,10 +31870,10 @@
         <v>0</v>
       </c>
       <c r="H850" t="n">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="I850" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="851">
@@ -31884,33 +31884,33 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E851" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F851" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G851" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H851" t="n">
-        <v>301</v>
+        <v>639</v>
       </c>
       <c r="I851" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="852">
@@ -31921,12 +31921,12 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
@@ -31958,27 +31958,27 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E853" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F853" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G853" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H853" t="n">
         <v>0</v>
@@ -31995,12 +31995,12 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -32018,10 +32018,10 @@
         <v>0</v>
       </c>
       <c r="H854" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I854" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="855">
@@ -32032,33 +32032,33 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E855" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F855" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G855" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H855" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="I855" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="856">
@@ -32074,28 +32074,28 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E856" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F856" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G856" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H856" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I856" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="857">
@@ -32111,7 +32111,7 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
@@ -32120,19 +32120,19 @@
         </is>
       </c>
       <c r="E857" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F857" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G857" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H857" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I857" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="858">
@@ -32148,7 +32148,7 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -32157,13 +32157,13 @@
         </is>
       </c>
       <c r="E858" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F858" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G858" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H858" t="n">
         <v>0</v>
@@ -32185,7 +32185,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -32222,7 +32222,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -32231,19 +32231,19 @@
         </is>
       </c>
       <c r="E860" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F860" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G860" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H860" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I860" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="861">
@@ -32259,7 +32259,7 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
@@ -32268,13 +32268,13 @@
         </is>
       </c>
       <c r="E861" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F861" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G861" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -32296,7 +32296,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
@@ -32305,19 +32305,19 @@
         </is>
       </c>
       <c r="E862" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F862" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G862" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H862" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I862" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="863">
@@ -32333,7 +32333,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
@@ -32342,19 +32342,19 @@
         </is>
       </c>
       <c r="E863" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F863" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G863" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H863" t="n">
-        <v>305</v>
+        <v>61</v>
       </c>
       <c r="I863" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="864">
@@ -32370,7 +32370,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
@@ -32407,7 +32407,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
@@ -32416,19 +32416,19 @@
         </is>
       </c>
       <c r="E865" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F865" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G865" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H865" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I865" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="866">
@@ -32439,12 +32439,12 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
@@ -32453,13 +32453,13 @@
         </is>
       </c>
       <c r="E866" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F866" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G866" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -32476,12 +32476,12 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -32490,13 +32490,13 @@
         </is>
       </c>
       <c r="E867" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F867" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G867" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -32513,17 +32513,17 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E868" t="n">
@@ -32550,12 +32550,12 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
@@ -32564,13 +32564,13 @@
         </is>
       </c>
       <c r="E869" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F869" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G869" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -32587,12 +32587,12 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
@@ -32624,12 +32624,12 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
@@ -32638,19 +32638,19 @@
         </is>
       </c>
       <c r="E871" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F871" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G871" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H871" t="n">
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="I871" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="872">
@@ -32661,12 +32661,12 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -32684,10 +32684,10 @@
         <v>3</v>
       </c>
       <c r="H872" t="n">
-        <v>124</v>
+        <v>638</v>
       </c>
       <c r="I872" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
     </row>
     <row r="873">
@@ -32698,12 +32698,12 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
@@ -32712,19 +32712,19 @@
         </is>
       </c>
       <c r="E873" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F873" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="G873" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="H873" t="n">
-        <v>392</v>
+        <v>50</v>
       </c>
       <c r="I873" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="874">
@@ -32740,28 +32740,28 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E874" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F874" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G874" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H874" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I874" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="875">
@@ -32777,12 +32777,12 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E875" t="n">
@@ -32814,7 +32814,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
@@ -32823,19 +32823,19 @@
         </is>
       </c>
       <c r="E876" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F876" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G876" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H876" t="n">
-        <v>2440</v>
+        <v>0</v>
       </c>
       <c r="I876" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="877">
@@ -32851,28 +32851,28 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E877" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F877" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G877" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H877" t="n">
-        <v>177</v>
+        <v>335</v>
       </c>
       <c r="I877" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="878">
@@ -32888,22 +32888,22 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E878" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F878" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G878" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -32925,28 +32925,28 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E879" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F879" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G879" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H879" t="n">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="I879" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="880">
@@ -32962,28 +32962,28 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E880" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F880" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="G880" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="H880" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="I880" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="881">
@@ -32999,7 +32999,7 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
@@ -33008,7 +33008,7 @@
         </is>
       </c>
       <c r="E881" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F881" t="n">
         <v>5</v>
@@ -33017,10 +33017,269 @@
         <v>5</v>
       </c>
       <c r="H881" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I881" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>£25K-£50K</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E882" t="n">
+        <v>1</v>
+      </c>
+      <c r="F882" t="n">
+        <v>1</v>
+      </c>
+      <c r="G882" t="n">
+        <v>1</v>
+      </c>
+      <c r="H882" t="n">
+        <v>0</v>
+      </c>
+      <c r="I882" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>£25K-£50K</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E883" t="n">
+        <v>4</v>
+      </c>
+      <c r="F883" t="n">
+        <v>4</v>
+      </c>
+      <c r="G883" t="n">
+        <v>4</v>
+      </c>
+      <c r="H883" t="n">
+        <v>2666</v>
+      </c>
+      <c r="I883" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E884" t="n">
+        <v>9</v>
+      </c>
+      <c r="F884" t="n">
+        <v>9</v>
+      </c>
+      <c r="G884" t="n">
+        <v>9</v>
+      </c>
+      <c r="H884" t="n">
+        <v>666</v>
+      </c>
+      <c r="I884" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E885" t="n">
+        <v>1</v>
+      </c>
+      <c r="F885" t="n">
+        <v>1</v>
+      </c>
+      <c r="G885" t="n">
+        <v>1</v>
+      </c>
+      <c r="H885" t="n">
+        <v>0</v>
+      </c>
+      <c r="I885" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E886" t="n">
+        <v>0</v>
+      </c>
+      <c r="F886" t="n">
+        <v>0</v>
+      </c>
+      <c r="G886" t="n">
+        <v>0</v>
+      </c>
+      <c r="H886" t="n">
+        <v>324</v>
+      </c>
+      <c r="I886" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E887" t="n">
+        <v>3</v>
+      </c>
+      <c r="F887" t="n">
+        <v>3</v>
+      </c>
+      <c r="G887" t="n">
+        <v>3</v>
+      </c>
+      <c r="H887" t="n">
+        <v>42</v>
+      </c>
+      <c r="I887" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E888" t="n">
+        <v>6</v>
+      </c>
+      <c r="F888" t="n">
+        <v>7</v>
+      </c>
+      <c r="G888" t="n">
+        <v>7</v>
+      </c>
+      <c r="H888" t="n">
+        <v>187</v>
+      </c>
+      <c r="I888" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -28938,13 +28938,13 @@
         </is>
       </c>
       <c r="E771" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F771" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G771" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H771" t="n">
         <v>298</v>
@@ -29200,10 +29200,10 @@
         <v>10</v>
       </c>
       <c r="F778" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G778" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H778" t="n">
         <v>9168</v>
@@ -29271,13 +29271,13 @@
         </is>
       </c>
       <c r="E780" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F780" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G780" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H780" t="n">
         <v>8577</v>
@@ -29567,13 +29567,13 @@
         </is>
       </c>
       <c r="E788" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F788" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G788" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H788" t="n">
         <v>2644</v>
@@ -29752,13 +29752,13 @@
         </is>
       </c>
       <c r="E793" t="n">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="F793" t="n">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="G793" t="n">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="H793" t="n">
         <v>46</v>
@@ -30011,13 +30011,13 @@
         </is>
       </c>
       <c r="E800" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F800" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G800" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H800" t="n">
         <v>8246</v>
@@ -30085,13 +30085,13 @@
         </is>
       </c>
       <c r="E802" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F802" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G802" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H802" t="n">
         <v>2830</v>
@@ -30159,13 +30159,13 @@
         </is>
       </c>
       <c r="E804" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F804" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G804" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H804" t="n">
         <v>149</v>
@@ -30381,13 +30381,13 @@
         </is>
       </c>
       <c r="E810" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F810" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G810" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H810" t="n">
         <v>103</v>
@@ -30566,13 +30566,13 @@
         </is>
       </c>
       <c r="E815" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F815" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G815" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H815" t="n">
         <v>0</v>
@@ -30862,13 +30862,13 @@
         </is>
       </c>
       <c r="E823" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F823" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G823" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H823" t="n">
         <v>59</v>
@@ -31084,13 +31084,13 @@
         </is>
       </c>
       <c r="E829" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F829" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G829" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -31380,13 +31380,13 @@
         </is>
       </c>
       <c r="E837" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F837" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G837" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H837" t="n">
         <v>0</v>
@@ -31602,13 +31602,13 @@
         </is>
       </c>
       <c r="E843" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F843" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G843" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -31815,28 +31815,28 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E849" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F849" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G849" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H849" t="n">
-        <v>2089</v>
+        <v>0</v>
       </c>
       <c r="I849" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="850">
@@ -31852,7 +31852,7 @@
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
@@ -31861,19 +31861,19 @@
         </is>
       </c>
       <c r="E850" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F850" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G850" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H850" t="n">
-        <v>19</v>
+        <v>2089</v>
       </c>
       <c r="I850" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
     </row>
     <row r="851">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E851" t="n">
@@ -31907,10 +31907,10 @@
         <v>1</v>
       </c>
       <c r="H851" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I851" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="852">
@@ -31931,23 +31931,23 @@
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E852" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F852" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G852" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H852" t="n">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="I852" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="853">
@@ -31963,7 +31963,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
@@ -31972,19 +31972,19 @@
         </is>
       </c>
       <c r="E853" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F853" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G853" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H853" t="n">
-        <v>654</v>
+        <v>255</v>
       </c>
       <c r="I853" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="854">
@@ -32000,7 +32000,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -32009,19 +32009,19 @@
         </is>
       </c>
       <c r="E854" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F854" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G854" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H854" t="n">
-        <v>0</v>
+        <v>654</v>
       </c>
       <c r="I854" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="855">
@@ -32037,7 +32037,7 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
@@ -32046,13 +32046,13 @@
         </is>
       </c>
       <c r="E855" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F855" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G855" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H855" t="n">
         <v>0</v>
@@ -32074,7 +32074,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
@@ -32092,10 +32092,10 @@
         <v>0</v>
       </c>
       <c r="H856" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I856" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="857">
@@ -32111,7 +32111,7 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
@@ -32120,19 +32120,19 @@
         </is>
       </c>
       <c r="E857" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F857" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G857" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H857" t="n">
-        <v>231</v>
+        <v>19</v>
       </c>
       <c r="I857" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="858">
@@ -32143,33 +32143,33 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E858" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F858" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G858" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H858" t="n">
-        <v>20</v>
+        <v>231</v>
       </c>
       <c r="I858" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="859">
@@ -32190,23 +32190,23 @@
       </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E859" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F859" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G859" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H859" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I859" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="860">
@@ -32222,22 +32222,22 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E860" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F860" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G860" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H860" t="n">
         <v>0</v>
@@ -32259,22 +32259,22 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E861" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F861" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G861" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -32296,28 +32296,28 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E862" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F862" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G862" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H862" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I862" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="863">
@@ -32338,23 +32338,23 @@
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E863" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F863" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G863" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H863" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I863" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="864">
@@ -32370,28 +32370,28 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E864" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F864" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G864" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H864" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I864" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="865">
@@ -32412,23 +32412,23 @@
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E865" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F865" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G865" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H865" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="I865" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="866">
@@ -32444,28 +32444,28 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E866" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F866" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G866" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H866" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I866" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="867">
@@ -32486,7 +32486,7 @@
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E867" t="n">
@@ -32518,12 +32518,12 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E868" t="n">
@@ -32560,17 +32560,17 @@
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E869" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F869" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G869" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -32592,22 +32592,22 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E870" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F870" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G870" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -32634,17 +32634,17 @@
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E871" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F871" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G871" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -32666,22 +32666,22 @@
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E872" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F872" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G872" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -32708,23 +32708,23 @@
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E873" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F873" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G873" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H873" t="n">
-        <v>632</v>
+        <v>0</v>
       </c>
       <c r="I873" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="874">
@@ -32740,28 +32740,28 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E874" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F874" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G874" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H874" t="n">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="I874" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
     </row>
     <row r="875">
@@ -32782,23 +32782,23 @@
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E875" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F875" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G875" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H875" t="n">
-        <v>50</v>
+        <v>648</v>
       </c>
       <c r="I875" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="876">
@@ -32809,33 +32809,33 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E876" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F876" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G876" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H876" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I876" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="877">
@@ -32851,7 +32851,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
@@ -32860,19 +32860,19 @@
         </is>
       </c>
       <c r="E877" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F877" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G877" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H877" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I877" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="878">
@@ -33008,13 +33008,13 @@
         </is>
       </c>
       <c r="E881" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F881" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G881" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -33045,13 +33045,13 @@
         </is>
       </c>
       <c r="E882" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F882" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G882" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H882" t="n">
         <v>214</v>
@@ -33082,13 +33082,13 @@
         </is>
       </c>
       <c r="E883" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F883" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G883" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H883" t="n">
         <v>836</v>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I891"/>
+  <dimension ref="A1:I896"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2779,13 +2779,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F64" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G64" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H64" t="n">
         <v>1520</v>
@@ -3075,13 +3075,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F72" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G72" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H72" t="n">
         <v>94</v>
@@ -8847,13 +8847,13 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F228" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G228" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H228" t="n">
         <v>796</v>
@@ -9143,13 +9143,13 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F236" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G236" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H236" t="n">
         <v>189</v>
@@ -10290,13 +10290,13 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F267" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G267" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H267" t="n">
         <v>135</v>
@@ -10549,13 +10549,13 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F274" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G274" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H274" t="n">
         <v>135</v>
@@ -11400,19 +11400,19 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F297" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G297" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H297" t="n">
-        <v>9163</v>
+        <v>9188</v>
       </c>
       <c r="I297" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="298">
@@ -11844,19 +11844,19 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F309" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G309" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H309" t="n">
-        <v>32855</v>
+        <v>32829</v>
       </c>
       <c r="I309" t="n">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="310">
@@ -15951,13 +15951,13 @@
         </is>
       </c>
       <c r="E420" t="n">
+        <v>31</v>
+      </c>
+      <c r="F420" t="n">
         <v>32</v>
       </c>
-      <c r="F420" t="n">
-        <v>33</v>
-      </c>
       <c r="G420" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H420" t="n">
         <v>162</v>
@@ -16062,13 +16062,13 @@
         </is>
       </c>
       <c r="E423" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F423" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G423" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H423" t="n">
         <v>8683</v>
@@ -16358,13 +16358,13 @@
         </is>
       </c>
       <c r="E431" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F431" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G431" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H431" t="n">
         <v>484</v>
@@ -16469,13 +16469,13 @@
         </is>
       </c>
       <c r="E434" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F434" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G434" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H434" t="n">
         <v>191</v>
@@ -16839,13 +16839,13 @@
         </is>
       </c>
       <c r="E444" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F444" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G444" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H444" t="n">
         <v>411</v>
@@ -17135,13 +17135,13 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F452" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G452" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H452" t="n">
         <v>61</v>
@@ -18134,13 +18134,13 @@
         </is>
       </c>
       <c r="E479" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F479" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G479" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H479" t="n">
         <v>10719</v>
@@ -18430,13 +18430,13 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F487" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G487" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H487" t="n">
         <v>3840</v>
@@ -18578,13 +18578,13 @@
         </is>
       </c>
       <c r="E491" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F491" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G491" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H491" t="n">
         <v>9779</v>
@@ -18957,10 +18957,10 @@
         <v>77</v>
       </c>
       <c r="H501" t="n">
-        <v>3400</v>
+        <v>2960</v>
       </c>
       <c r="I501" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
     </row>
     <row r="502">
@@ -19253,10 +19253,10 @@
         <v>32</v>
       </c>
       <c r="H509" t="n">
-        <v>941</v>
+        <v>1381</v>
       </c>
       <c r="I509" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="510">
@@ -20428,13 +20428,13 @@
         </is>
       </c>
       <c r="E541" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F541" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G541" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H541" t="n">
         <v>406</v>
@@ -20474,10 +20474,10 @@
         <v>127</v>
       </c>
       <c r="H542" t="n">
-        <v>4854</v>
+        <v>4914</v>
       </c>
       <c r="I542" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="543">
@@ -20502,13 +20502,13 @@
         </is>
       </c>
       <c r="E543" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F543" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G543" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H543" t="n">
         <v>50</v>
@@ -20761,13 +20761,13 @@
         </is>
       </c>
       <c r="E550" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F550" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G550" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H550" t="n">
         <v>1326</v>
@@ -20909,19 +20909,19 @@
         </is>
       </c>
       <c r="E554" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F554" t="n">
+        <v>27</v>
+      </c>
+      <c r="G554" t="n">
         <v>28</v>
       </c>
-      <c r="G554" t="n">
-        <v>29</v>
-      </c>
       <c r="H554" t="n">
-        <v>4859</v>
+        <v>4799</v>
       </c>
       <c r="I554" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="555">
@@ -21510,10 +21510,10 @@
         <v>0</v>
       </c>
       <c r="H570" t="n">
-        <v>768</v>
+        <v>729</v>
       </c>
       <c r="I570" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="571">
@@ -21732,10 +21732,10 @@
         <v>0</v>
       </c>
       <c r="H576" t="n">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="I576" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="577">
@@ -22056,13 +22056,13 @@
         </is>
       </c>
       <c r="E585" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F585" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G585" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H585" t="n">
         <v>0</v>
@@ -22241,13 +22241,13 @@
         </is>
       </c>
       <c r="E590" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F590" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G590" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -23092,13 +23092,13 @@
         </is>
       </c>
       <c r="E613" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F613" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G613" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -23314,13 +23314,13 @@
         </is>
       </c>
       <c r="E619" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F619" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G619" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -24498,13 +24498,13 @@
         </is>
       </c>
       <c r="E651" t="n">
+        <v>11</v>
+      </c>
+      <c r="F651" t="n">
         <v>12</v>
       </c>
-      <c r="F651" t="n">
-        <v>13</v>
-      </c>
       <c r="G651" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H651" t="n">
         <v>513</v>
@@ -24609,19 +24609,19 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F654" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G654" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H654" t="n">
-        <v>19775</v>
+        <v>25173</v>
       </c>
       <c r="I654" t="n">
-        <v>1042</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="655">
@@ -24692,10 +24692,10 @@
         <v>57</v>
       </c>
       <c r="H656" t="n">
-        <v>1575</v>
+        <v>1550</v>
       </c>
       <c r="I656" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="657">
@@ -24720,13 +24720,13 @@
         </is>
       </c>
       <c r="E657" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F657" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G657" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H657" t="n">
         <v>1000</v>
@@ -24905,13 +24905,13 @@
         </is>
       </c>
       <c r="E662" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F662" t="n">
+        <v>80</v>
+      </c>
+      <c r="G662" t="n">
         <v>81</v>
-      </c>
-      <c r="G662" t="n">
-        <v>82</v>
       </c>
       <c r="H662" t="n">
         <v>3385</v>
@@ -25053,19 +25053,19 @@
         </is>
       </c>
       <c r="E666" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F666" t="n">
+        <v>56</v>
+      </c>
+      <c r="G666" t="n">
         <v>57</v>
       </c>
-      <c r="G666" t="n">
-        <v>58</v>
-      </c>
       <c r="H666" t="n">
-        <v>43677</v>
+        <v>38304</v>
       </c>
       <c r="I666" t="n">
-        <v>1725</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="667">
@@ -25497,19 +25497,19 @@
         </is>
       </c>
       <c r="E678" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F678" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G678" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H678" t="n">
-        <v>1178</v>
+        <v>1136</v>
       </c>
       <c r="I678" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="679">
@@ -25793,19 +25793,19 @@
         </is>
       </c>
       <c r="E686" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F686" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G686" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H686" t="n">
-        <v>207</v>
+        <v>249</v>
       </c>
       <c r="I686" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="687">
@@ -25941,13 +25941,13 @@
         </is>
       </c>
       <c r="E690" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F690" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G690" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H690" t="n">
         <v>790</v>
@@ -27310,13 +27310,13 @@
         </is>
       </c>
       <c r="E727" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F727" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G727" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H727" t="n">
         <v>26</v>
@@ -27569,13 +27569,13 @@
         </is>
       </c>
       <c r="E734" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F734" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G734" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H734" t="n">
         <v>0</v>
@@ -27717,13 +27717,13 @@
         </is>
       </c>
       <c r="E738" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F738" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G738" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H738" t="n">
         <v>0</v>
@@ -28938,13 +28938,13 @@
         </is>
       </c>
       <c r="E771" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F771" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="G771" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="H771" t="n">
         <v>298</v>
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="E777" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F777" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G777" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H777" t="n">
         <v>406</v>
@@ -29206,10 +29206,10 @@
         <v>13</v>
       </c>
       <c r="H778" t="n">
-        <v>9168</v>
+        <v>9019</v>
       </c>
       <c r="I778" t="n">
-        <v>318</v>
+        <v>313</v>
       </c>
     </row>
     <row r="779">
@@ -29234,13 +29234,13 @@
         </is>
       </c>
       <c r="E779" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F779" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G779" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H779" t="n">
         <v>391</v>
@@ -29271,19 +29271,19 @@
         </is>
       </c>
       <c r="E780" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F780" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G780" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H780" t="n">
-        <v>8577</v>
+        <v>8793</v>
       </c>
       <c r="I780" t="n">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="781">
@@ -29382,13 +29382,13 @@
         </is>
       </c>
       <c r="E783" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F783" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G783" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H783" t="n">
         <v>0</v>
@@ -29428,10 +29428,10 @@
         <v>5</v>
       </c>
       <c r="H784" t="n">
-        <v>7270</v>
+        <v>7331</v>
       </c>
       <c r="I784" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="785">
@@ -29567,13 +29567,13 @@
         </is>
       </c>
       <c r="E788" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F788" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G788" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H788" t="n">
         <v>2644</v>
@@ -29715,19 +29715,19 @@
         </is>
       </c>
       <c r="E792" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F792" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G792" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H792" t="n">
-        <v>16962</v>
+        <v>16835</v>
       </c>
       <c r="I792" t="n">
-        <v>523</v>
+        <v>518</v>
       </c>
     </row>
     <row r="793">
@@ -29752,19 +29752,19 @@
         </is>
       </c>
       <c r="E793" t="n">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="F793" t="n">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="G793" t="n">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="H793" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="I793" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="794">
@@ -29974,13 +29974,13 @@
         </is>
       </c>
       <c r="E799" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F799" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G799" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H799" t="n">
         <v>51</v>
@@ -30011,13 +30011,13 @@
         </is>
       </c>
       <c r="E800" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F800" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G800" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H800" t="n">
         <v>8246</v>
@@ -30048,13 +30048,13 @@
         </is>
       </c>
       <c r="E801" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F801" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G801" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H801" t="n">
         <v>265</v>
@@ -30085,19 +30085,19 @@
         </is>
       </c>
       <c r="E802" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F802" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G802" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H802" t="n">
-        <v>2830</v>
+        <v>2739</v>
       </c>
       <c r="I802" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="803">
@@ -30122,13 +30122,13 @@
         </is>
       </c>
       <c r="E803" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F803" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G803" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H803" t="n">
         <v>0</v>
@@ -30159,13 +30159,13 @@
         </is>
       </c>
       <c r="E804" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F804" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G804" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H804" t="n">
         <v>149</v>
@@ -30196,19 +30196,19 @@
         </is>
       </c>
       <c r="E805" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F805" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G805" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H805" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I805" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="806">
@@ -30233,13 +30233,13 @@
         </is>
       </c>
       <c r="E806" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F806" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G806" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H806" t="n">
         <v>209</v>
@@ -30344,13 +30344,13 @@
         </is>
       </c>
       <c r="E809" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F809" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G809" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -30390,10 +30390,10 @@
         <v>35</v>
       </c>
       <c r="H810" t="n">
-        <v>103</v>
+        <v>194</v>
       </c>
       <c r="I810" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="811">
@@ -30492,13 +30492,13 @@
         </is>
       </c>
       <c r="E813" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F813" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G813" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H813" t="n">
         <v>4171</v>
@@ -30529,13 +30529,13 @@
         </is>
       </c>
       <c r="E814" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F814" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G814" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H814" t="n">
         <v>2675</v>
@@ -30566,13 +30566,13 @@
         </is>
       </c>
       <c r="E815" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F815" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G815" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H815" t="n">
         <v>0</v>
@@ -30751,13 +30751,13 @@
         </is>
       </c>
       <c r="E820" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F820" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G820" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H820" t="n">
         <v>20</v>
@@ -30788,13 +30788,13 @@
         </is>
       </c>
       <c r="E821" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F821" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G821" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H821" t="n">
         <v>0</v>
@@ -30825,13 +30825,13 @@
         </is>
       </c>
       <c r="E822" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F822" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G822" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H822" t="n">
         <v>0</v>
@@ -30862,13 +30862,13 @@
         </is>
       </c>
       <c r="E823" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F823" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G823" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H823" t="n">
         <v>59</v>
@@ -30899,13 +30899,13 @@
         </is>
       </c>
       <c r="E824" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F824" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G824" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -31080,17 +31080,17 @@
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E829" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F829" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G829" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -31121,19 +31121,19 @@
         </is>
       </c>
       <c r="E830" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F830" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G830" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H830" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="I830" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="831">
@@ -31144,27 +31144,27 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E831" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F831" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G831" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -31181,12 +31181,12 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
@@ -31195,19 +31195,19 @@
         </is>
       </c>
       <c r="E832" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F832" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G832" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H832" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="I832" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="833">
@@ -31218,7 +31218,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -31228,17 +31228,17 @@
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E833" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F833" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G833" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -31255,12 +31255,12 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
@@ -31269,19 +31269,19 @@
         </is>
       </c>
       <c r="E834" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F834" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G834" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H834" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I834" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="835">
@@ -31297,22 +31297,22 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E835" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F835" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G835" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
@@ -31371,7 +31371,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
@@ -31403,33 +31403,33 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E838" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F838" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G838" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H838" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I838" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="839">
@@ -31440,27 +31440,27 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E839" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F839" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G839" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -31482,7 +31482,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -31491,19 +31491,19 @@
         </is>
       </c>
       <c r="E840" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F840" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G840" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H840" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I840" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="841">
@@ -31519,22 +31519,22 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E841" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F841" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G841" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H841" t="n">
         <v>0</v>
@@ -31556,7 +31556,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -31565,13 +31565,13 @@
         </is>
       </c>
       <c r="E842" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F842" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G842" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H842" t="n">
         <v>0</v>
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
@@ -31602,13 +31602,13 @@
         </is>
       </c>
       <c r="E843" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F843" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G843" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -31630,28 +31630,28 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E844" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F844" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G844" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H844" t="n">
-        <v>5278</v>
+        <v>0</v>
       </c>
       <c r="I844" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="845">
@@ -31667,22 +31667,22 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E845" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F845" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G845" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H845" t="n">
         <v>0</v>
@@ -31704,7 +31704,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
@@ -31713,19 +31713,19 @@
         </is>
       </c>
       <c r="E846" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F846" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G846" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H846" t="n">
-        <v>0</v>
+        <v>5278</v>
       </c>
       <c r="I846" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
     </row>
     <row r="847">
@@ -31741,7 +31741,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
@@ -31778,7 +31778,7 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
@@ -31787,10 +31787,10 @@
         </is>
       </c>
       <c r="E848" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F848" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G848" t="n">
         <v>8</v>
@@ -31810,12 +31810,12 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
@@ -31824,13 +31824,13 @@
         </is>
       </c>
       <c r="E849" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F849" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G849" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -31847,12 +31847,12 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
@@ -31861,19 +31861,19 @@
         </is>
       </c>
       <c r="E850" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F850" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G850" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H850" t="n">
-        <v>2089</v>
+        <v>0</v>
       </c>
       <c r="I850" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="851">
@@ -31889,7 +31889,7 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
@@ -31898,19 +31898,19 @@
         </is>
       </c>
       <c r="E851" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F851" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G851" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H851" t="n">
-        <v>19</v>
+        <v>2089</v>
       </c>
       <c r="I851" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
     </row>
     <row r="852">
@@ -31926,12 +31926,12 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E852" t="n">
@@ -31944,10 +31944,10 @@
         <v>1</v>
       </c>
       <c r="H852" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I852" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="853">
@@ -31968,23 +31968,23 @@
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E853" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F853" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G853" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H853" t="n">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="I853" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="854">
@@ -32000,7 +32000,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -32009,19 +32009,19 @@
         </is>
       </c>
       <c r="E854" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F854" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G854" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H854" t="n">
-        <v>654</v>
+        <v>255</v>
       </c>
       <c r="I854" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="855">
@@ -32037,22 +32037,22 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E855" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F855" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G855" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H855" t="n">
         <v>0</v>
@@ -32074,7 +32074,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
@@ -32083,19 +32083,19 @@
         </is>
       </c>
       <c r="E856" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F856" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G856" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H856" t="n">
-        <v>0</v>
+        <v>654</v>
       </c>
       <c r="I856" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="857">
@@ -32111,7 +32111,7 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
@@ -32120,19 +32120,19 @@
         </is>
       </c>
       <c r="E857" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F857" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G857" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H857" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I857" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="858">
@@ -32148,7 +32148,7 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -32166,10 +32166,10 @@
         <v>0</v>
       </c>
       <c r="H858" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="I858" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="859">
@@ -32180,12 +32180,12 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -32194,19 +32194,19 @@
         </is>
       </c>
       <c r="E859" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F859" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G859" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H859" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I859" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="860">
@@ -32217,12 +32217,12 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -32240,10 +32240,10 @@
         <v>1</v>
       </c>
       <c r="H860" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I860" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="861">
@@ -32254,12 +32254,12 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
@@ -32268,13 +32268,13 @@
         </is>
       </c>
       <c r="E861" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F861" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G861" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -32291,12 +32291,12 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
@@ -32305,19 +32305,19 @@
         </is>
       </c>
       <c r="E862" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F862" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G862" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H862" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="I862" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="863">
@@ -32333,7 +32333,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
@@ -32342,19 +32342,19 @@
         </is>
       </c>
       <c r="E863" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F863" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G863" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H863" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I863" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="864">
@@ -32370,7 +32370,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
@@ -32407,7 +32407,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
@@ -32416,19 +32416,19 @@
         </is>
       </c>
       <c r="E865" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F865" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G865" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H865" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I865" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="866">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
@@ -32453,19 +32453,19 @@
         </is>
       </c>
       <c r="E866" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F866" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G866" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H866" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="I866" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="867">
@@ -32481,7 +32481,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -32490,19 +32490,19 @@
         </is>
       </c>
       <c r="E867" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F867" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G867" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H867" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I867" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="868">
@@ -32518,7 +32518,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
@@ -32555,7 +32555,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
@@ -32564,19 +32564,19 @@
         </is>
       </c>
       <c r="E869" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F869" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G869" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H869" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I869" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="870">
@@ -32592,7 +32592,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
@@ -32601,19 +32601,19 @@
         </is>
       </c>
       <c r="E870" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="F870" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="G870" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H870" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="I870" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="871">
@@ -32629,7 +32629,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
@@ -32666,7 +32666,7 @@
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -32675,13 +32675,13 @@
         </is>
       </c>
       <c r="E872" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F872" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G872" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -32703,7 +32703,7 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
@@ -32740,7 +32740,7 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
@@ -32749,19 +32749,19 @@
         </is>
       </c>
       <c r="E874" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F874" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G874" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H874" t="n">
-        <v>632</v>
+        <v>0</v>
       </c>
       <c r="I874" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="875">
@@ -32777,7 +32777,7 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
@@ -32786,19 +32786,19 @@
         </is>
       </c>
       <c r="E875" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F875" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G875" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H875" t="n">
-        <v>648</v>
+        <v>0</v>
       </c>
       <c r="I875" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="876">
@@ -32814,7 +32814,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
@@ -32823,19 +32823,19 @@
         </is>
       </c>
       <c r="E876" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F876" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G876" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H876" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I876" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="877">
@@ -32846,12 +32846,12 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
@@ -32860,19 +32860,19 @@
         </is>
       </c>
       <c r="E877" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F877" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G877" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H877" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I877" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="878">
@@ -32883,12 +32883,12 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
@@ -32897,19 +32897,19 @@
         </is>
       </c>
       <c r="E878" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F878" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G878" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H878" t="n">
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="I878" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="879">
@@ -32920,33 +32920,33 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E879" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F879" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G879" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H879" t="n">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="I879" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
     </row>
     <row r="880">
@@ -32957,33 +32957,33 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E880" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F880" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G880" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H880" t="n">
-        <v>556</v>
+        <v>50</v>
       </c>
       <c r="I880" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="881">
@@ -32999,12 +32999,12 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E881" t="n">
@@ -33017,10 +33017,10 @@
         <v>8</v>
       </c>
       <c r="H881" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I881" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="882">
@@ -33036,28 +33036,28 @@
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E882" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F882" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G882" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H882" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="I882" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="883">
@@ -33073,7 +33073,7 @@
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
@@ -33082,19 +33082,19 @@
         </is>
       </c>
       <c r="E883" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="F883" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="G883" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="H883" t="n">
-        <v>836</v>
+        <v>0</v>
       </c>
       <c r="I883" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="884">
@@ -33110,28 +33110,28 @@
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E884" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F884" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G884" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H884" t="n">
-        <v>0</v>
+        <v>556</v>
       </c>
       <c r="I884" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="885">
@@ -33147,22 +33147,22 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E885" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F885" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G885" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H885" t="n">
         <v>0</v>
@@ -33184,28 +33184,28 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E886" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F886" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G886" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H886" t="n">
-        <v>2666</v>
+        <v>214</v>
       </c>
       <c r="I886" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
     </row>
     <row r="887">
@@ -33221,7 +33221,7 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
@@ -33230,19 +33230,19 @@
         </is>
       </c>
       <c r="E887" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="F887" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="G887" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="H887" t="n">
-        <v>666</v>
+        <v>836</v>
       </c>
       <c r="I887" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="888">
@@ -33258,22 +33258,22 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E888" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F888" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G888" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -33295,28 +33295,28 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E889" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F889" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G889" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H889" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="I889" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="890">
@@ -33332,28 +33332,28 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E890" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F890" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G890" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H890" t="n">
-        <v>42</v>
+        <v>2666</v>
       </c>
       <c r="I890" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
     </row>
     <row r="891">
@@ -33369,27 +33369,212 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E891" t="n">
+        <v>2</v>
+      </c>
+      <c r="F891" t="n">
+        <v>2</v>
+      </c>
+      <c r="G891" t="n">
+        <v>2</v>
+      </c>
+      <c r="H891" t="n">
+        <v>0</v>
+      </c>
+      <c r="I891" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E892" t="n">
+        <v>11</v>
+      </c>
+      <c r="F892" t="n">
+        <v>11</v>
+      </c>
+      <c r="G892" t="n">
+        <v>11</v>
+      </c>
+      <c r="H892" t="n">
+        <v>666</v>
+      </c>
+      <c r="I892" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E893" t="n">
+        <v>1</v>
+      </c>
+      <c r="F893" t="n">
+        <v>1</v>
+      </c>
+      <c r="G893" t="n">
+        <v>1</v>
+      </c>
+      <c r="H893" t="n">
+        <v>0</v>
+      </c>
+      <c r="I893" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E894" t="n">
+        <v>0</v>
+      </c>
+      <c r="F894" t="n">
+        <v>0</v>
+      </c>
+      <c r="G894" t="n">
+        <v>0</v>
+      </c>
+      <c r="H894" t="n">
+        <v>324</v>
+      </c>
+      <c r="I894" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
           <t>£5K-£10K</t>
         </is>
       </c>
-      <c r="D891" t="inlineStr">
-        <is>
-          <t>Old</t>
-        </is>
-      </c>
-      <c r="E891" t="n">
-        <v>7</v>
-      </c>
-      <c r="F891" t="n">
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E895" t="n">
+        <v>4</v>
+      </c>
+      <c r="F895" t="n">
+        <v>4</v>
+      </c>
+      <c r="G895" t="n">
+        <v>4</v>
+      </c>
+      <c r="H895" t="n">
+        <v>42</v>
+      </c>
+      <c r="I895" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E896" t="n">
         <v>8</v>
       </c>
-      <c r="G891" t="n">
-        <v>8</v>
-      </c>
-      <c r="H891" t="n">
+      <c r="F896" t="n">
+        <v>9</v>
+      </c>
+      <c r="G896" t="n">
+        <v>9</v>
+      </c>
+      <c r="H896" t="n">
         <v>293</v>
       </c>
-      <c r="I891" t="n">
+      <c r="I896" t="n">
         <v>11</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -22398,10 +22398,10 @@
         <v>43</v>
       </c>
       <c r="H594" t="n">
-        <v>51164</v>
+        <v>50176</v>
       </c>
       <c r="I594" t="n">
-        <v>2124</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="595">
@@ -22472,10 +22472,10 @@
         <v>241</v>
       </c>
       <c r="H596" t="n">
-        <v>18151</v>
+        <v>17495</v>
       </c>
       <c r="I596" t="n">
-        <v>753</v>
+        <v>732</v>
       </c>
     </row>
     <row r="597">
@@ -22546,10 +22546,10 @@
         <v>85</v>
       </c>
       <c r="H598" t="n">
-        <v>1778</v>
+        <v>1753</v>
       </c>
       <c r="I598" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="599">
@@ -22620,7 +22620,7 @@
         <v>19</v>
       </c>
       <c r="H600" t="n">
-        <v>11074</v>
+        <v>11033</v>
       </c>
       <c r="I600" t="n">
         <v>447</v>
@@ -22768,10 +22768,10 @@
         <v>104</v>
       </c>
       <c r="H604" t="n">
-        <v>3399</v>
+        <v>3327</v>
       </c>
       <c r="I604" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="605">
@@ -22842,10 +22842,10 @@
         <v>1</v>
       </c>
       <c r="H606" t="n">
-        <v>8886</v>
+        <v>8662</v>
       </c>
       <c r="I606" t="n">
-        <v>373</v>
+        <v>365</v>
       </c>
     </row>
     <row r="607">
@@ -22916,10 +22916,10 @@
         <v>56</v>
       </c>
       <c r="H608" t="n">
-        <v>16946</v>
+        <v>16092</v>
       </c>
       <c r="I608" t="n">
-        <v>918</v>
+        <v>889</v>
       </c>
     </row>
     <row r="609">
@@ -23323,10 +23323,10 @@
         <v>70</v>
       </c>
       <c r="H619" t="n">
-        <v>1759</v>
+        <v>1778</v>
       </c>
       <c r="I619" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="620">
@@ -23437,7 +23437,7 @@
         <v>14</v>
       </c>
       <c r="I622" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="623">
@@ -23952,10 +23952,10 @@
         <v>6</v>
       </c>
       <c r="H636" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="I636" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="637">
@@ -23989,10 +23989,10 @@
         <v>15</v>
       </c>
       <c r="H637" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="I637" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="638">
@@ -24174,10 +24174,10 @@
         <v>7</v>
       </c>
       <c r="H642" t="n">
-        <v>391</v>
+        <v>356</v>
       </c>
       <c r="I642" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="643">
@@ -24211,10 +24211,10 @@
         <v>18</v>
       </c>
       <c r="H643" t="n">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="I643" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="644">
@@ -24285,10 +24285,10 @@
         <v>2</v>
       </c>
       <c r="H645" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I645" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="646">
@@ -24766,10 +24766,10 @@
         <v>0</v>
       </c>
       <c r="H658" t="n">
-        <v>5612</v>
+        <v>5455</v>
       </c>
       <c r="I658" t="n">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="659">
@@ -25839,10 +25839,10 @@
         <v>5</v>
       </c>
       <c r="H687" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="I687" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="688">
@@ -25876,10 +25876,10 @@
         <v>18</v>
       </c>
       <c r="H688" t="n">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="I688" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="689">
@@ -27060,10 +27060,10 @@
         <v>16</v>
       </c>
       <c r="H720" t="n">
-        <v>33360</v>
+        <v>33486</v>
       </c>
       <c r="I720" t="n">
-        <v>1180</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="721">
@@ -27134,10 +27134,10 @@
         <v>96</v>
       </c>
       <c r="H722" t="n">
-        <v>13467</v>
+        <v>13733</v>
       </c>
       <c r="I722" t="n">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="723">
@@ -27208,10 +27208,10 @@
         <v>16</v>
       </c>
       <c r="H724" t="n">
-        <v>2404</v>
+        <v>2425</v>
       </c>
       <c r="I724" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="725">
@@ -27282,10 +27282,10 @@
         <v>5</v>
       </c>
       <c r="H726" t="n">
-        <v>11437</v>
+        <v>11489</v>
       </c>
       <c r="I726" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="727">
@@ -27467,10 +27467,10 @@
         <v>2</v>
       </c>
       <c r="H731" t="n">
-        <v>5149</v>
+        <v>5169</v>
       </c>
       <c r="I731" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="732">
@@ -27504,10 +27504,10 @@
         <v>21</v>
       </c>
       <c r="H732" t="n">
-        <v>6442</v>
+        <v>6540</v>
       </c>
       <c r="I732" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="733">
@@ -27541,10 +27541,10 @@
         <v>21</v>
       </c>
       <c r="H733" t="n">
-        <v>10870</v>
+        <v>11180</v>
       </c>
       <c r="I733" t="n">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="734">
@@ -27837,10 +27837,10 @@
         <v>10</v>
       </c>
       <c r="H741" t="n">
-        <v>2410</v>
+        <v>2429</v>
       </c>
       <c r="I741" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="742">
@@ -27911,10 +27911,10 @@
         <v>101</v>
       </c>
       <c r="H743" t="n">
-        <v>3929</v>
+        <v>3948</v>
       </c>
       <c r="I743" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="744">
@@ -28318,10 +28318,10 @@
         <v>28</v>
       </c>
       <c r="H754" t="n">
-        <v>2208</v>
+        <v>2224</v>
       </c>
       <c r="I754" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="755">
@@ -29539,10 +29539,10 @@
         <v>2</v>
       </c>
       <c r="H787" t="n">
-        <v>6444</v>
+        <v>6548</v>
       </c>
       <c r="I787" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="788">
@@ -31611,10 +31611,10 @@
         <v>3</v>
       </c>
       <c r="H843" t="n">
-        <v>2164</v>
+        <v>2311</v>
       </c>
       <c r="I843" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="844">
@@ -31685,10 +31685,10 @@
         <v>22</v>
       </c>
       <c r="H845" t="n">
-        <v>969</v>
+        <v>1289</v>
       </c>
       <c r="I845" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="846">
@@ -31759,10 +31759,10 @@
         <v>5</v>
       </c>
       <c r="H847" t="n">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="I847" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="848">
@@ -31907,10 +31907,10 @@
         <v>9</v>
       </c>
       <c r="H851" t="n">
-        <v>206</v>
+        <v>296</v>
       </c>
       <c r="I851" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="852">
@@ -31944,10 +31944,10 @@
         <v>2</v>
       </c>
       <c r="H852" t="n">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="I852" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="853">
@@ -32018,10 +32018,10 @@
         <v>8</v>
       </c>
       <c r="H854" t="n">
-        <v>1224</v>
+        <v>1243</v>
       </c>
       <c r="I854" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="855">
@@ -32092,10 +32092,10 @@
         <v>3</v>
       </c>
       <c r="H856" t="n">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="I856" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="857">
@@ -32314,10 +32314,10 @@
         <v>7</v>
       </c>
       <c r="H862" t="n">
-        <v>257</v>
+        <v>322</v>
       </c>
       <c r="I862" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="863">
@@ -32499,10 +32499,10 @@
         <v>3</v>
       </c>
       <c r="H867" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I867" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="868">
@@ -32613,7 +32613,7 @@
         <v>20</v>
       </c>
       <c r="I870" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="871">
@@ -32684,10 +32684,10 @@
         <v>4</v>
       </c>
       <c r="H872" t="n">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="I872" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="873">
@@ -33720,10 +33720,10 @@
         <v>1</v>
       </c>
       <c r="H900" t="n">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="I900" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="901">
@@ -34571,10 +34571,10 @@
         <v>0</v>
       </c>
       <c r="H923" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I923" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="924">
@@ -34756,10 +34756,10 @@
         <v>1</v>
       </c>
       <c r="H928" t="n">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="I928" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="929">

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3873" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3877" uniqueCount="49">
   <si>
     <t>Month</t>
   </si>
@@ -518,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I967"/>
+  <dimension ref="A1:I968"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -25330,13 +25330,13 @@
         <v>47</v>
       </c>
       <c r="E856">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F856">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G856">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H856">
         <v>0</v>
@@ -25475,13 +25475,13 @@
         <v>47</v>
       </c>
       <c r="E861">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F861">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G861">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H861">
         <v>0</v>
@@ -25533,13 +25533,13 @@
         <v>47</v>
       </c>
       <c r="E863">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F863">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G863">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H863">
         <v>0</v>
@@ -25591,13 +25591,13 @@
         <v>47</v>
       </c>
       <c r="E865">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F865">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G865">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H865">
         <v>0</v>
@@ -25736,13 +25736,13 @@
         <v>48</v>
       </c>
       <c r="E870">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F870">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G870">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H870">
         <v>343</v>
@@ -25852,13 +25852,13 @@
         <v>47</v>
       </c>
       <c r="E874">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F874">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G874">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H874">
         <v>0</v>
@@ -25881,13 +25881,13 @@
         <v>48</v>
       </c>
       <c r="E875">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F875">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G875">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H875">
         <v>201</v>
@@ -26084,13 +26084,13 @@
         <v>47</v>
       </c>
       <c r="E882">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F882">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G882">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H882">
         <v>0</v>
@@ -26171,13 +26171,13 @@
         <v>48</v>
       </c>
       <c r="E885">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F885">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G885">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H885">
         <v>60</v>
@@ -26258,13 +26258,13 @@
         <v>47</v>
       </c>
       <c r="E888">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F888">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G888">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H888">
         <v>0</v>
@@ -26548,13 +26548,13 @@
         <v>47</v>
       </c>
       <c r="E898">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F898">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G898">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H898">
         <v>0</v>
@@ -26577,13 +26577,13 @@
         <v>48</v>
       </c>
       <c r="E899">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F899">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G899">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H899">
         <v>12</v>
@@ -26606,13 +26606,13 @@
         <v>47</v>
       </c>
       <c r="E900">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F900">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G900">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H900">
         <v>0</v>
@@ -26722,13 +26722,13 @@
         <v>47</v>
       </c>
       <c r="E904">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F904">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G904">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H904">
         <v>0</v>
@@ -26780,13 +26780,13 @@
         <v>48</v>
       </c>
       <c r="E906">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F906">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G906">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H906">
         <v>19</v>
@@ -27012,13 +27012,13 @@
         <v>47</v>
       </c>
       <c r="E914">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F914">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G914">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H914">
         <v>0</v>
@@ -27035,19 +27035,19 @@
         <v>26</v>
       </c>
       <c r="C915" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D915" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E915">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F915">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G915">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H915">
         <v>0</v>
@@ -27067,7 +27067,7 @@
         <v>38</v>
       </c>
       <c r="D916" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E916">
         <v>13</v>
@@ -27093,19 +27093,19 @@
         <v>26</v>
       </c>
       <c r="C917" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D917" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E917">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F917">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G917">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H917">
         <v>0</v>
@@ -27125,16 +27125,16 @@
         <v>39</v>
       </c>
       <c r="D918" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E918">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="F918">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="G918">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="H918">
         <v>0</v>
@@ -27151,19 +27151,19 @@
         <v>26</v>
       </c>
       <c r="C919" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D919" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E919">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="F919">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="G919">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="H919">
         <v>0</v>
@@ -27183,16 +27183,16 @@
         <v>40</v>
       </c>
       <c r="D920" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E920">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F920">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G920">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H920">
         <v>0</v>
@@ -27209,19 +27209,19 @@
         <v>26</v>
       </c>
       <c r="C921" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D921" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E921">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F921">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G921">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H921">
         <v>0</v>
@@ -27241,16 +27241,16 @@
         <v>41</v>
       </c>
       <c r="D922" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E922">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F922">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G922">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H922">
         <v>0</v>
@@ -27267,19 +27267,19 @@
         <v>26</v>
       </c>
       <c r="C923" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D923" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E923">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F923">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G923">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H923">
         <v>0</v>
@@ -27299,7 +27299,7 @@
         <v>43</v>
       </c>
       <c r="D924" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E924">
         <v>8</v>
@@ -27325,19 +27325,19 @@
         <v>26</v>
       </c>
       <c r="C925" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D925" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E925">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F925">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G925">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H925">
         <v>0</v>
@@ -27357,7 +27357,7 @@
         <v>46</v>
       </c>
       <c r="D926" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E926">
         <v>3</v>
@@ -27369,10 +27369,10 @@
         <v>3</v>
       </c>
       <c r="H926">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="I926">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="927" spans="1:9">
@@ -27383,25 +27383,25 @@
         <v>26</v>
       </c>
       <c r="C927" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D927" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E927">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F927">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G927">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H927">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="I927">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="928" spans="1:9">
@@ -27415,16 +27415,16 @@
         <v>44</v>
       </c>
       <c r="D928" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E928">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F928">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G928">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H928">
         <v>0</v>
@@ -27438,22 +27438,22 @@
         <v>24</v>
       </c>
       <c r="B929" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C929" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D929" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E929">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F929">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="G929">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="H929">
         <v>0</v>
@@ -27473,16 +27473,16 @@
         <v>45</v>
       </c>
       <c r="D930" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E930">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F930">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G930">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H930">
         <v>0</v>
@@ -27499,19 +27499,19 @@
         <v>31</v>
       </c>
       <c r="C931" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D931" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E931">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F931">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G931">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H931">
         <v>0</v>
@@ -27531,16 +27531,16 @@
         <v>36</v>
       </c>
       <c r="D932" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E932">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F932">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G932">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H932">
         <v>0</v>
@@ -27557,19 +27557,19 @@
         <v>31</v>
       </c>
       <c r="C933" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D933" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E933">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F933">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G933">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H933">
         <v>0</v>
@@ -27589,16 +27589,16 @@
         <v>37</v>
       </c>
       <c r="D934" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E934">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F934">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G934">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H934">
         <v>0</v>
@@ -27615,19 +27615,19 @@
         <v>31</v>
       </c>
       <c r="C935" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D935" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E935">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F935">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G935">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H935">
         <v>0</v>
@@ -27647,16 +27647,16 @@
         <v>38</v>
       </c>
       <c r="D936" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E936">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F936">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G936">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H936">
         <v>0</v>
@@ -27673,19 +27673,19 @@
         <v>31</v>
       </c>
       <c r="C937" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D937" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E937">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F937">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G937">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H937">
         <v>0</v>
@@ -27705,22 +27705,22 @@
         <v>39</v>
       </c>
       <c r="D938" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E938">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="F938">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G938">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="H938">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I938">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="939" spans="1:9">
@@ -27731,25 +27731,25 @@
         <v>31</v>
       </c>
       <c r="C939" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D939" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E939">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F939">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="G939">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H939">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I939">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="940" spans="1:9">
@@ -27763,16 +27763,16 @@
         <v>40</v>
       </c>
       <c r="D940" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E940">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F940">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G940">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H940">
         <v>0</v>
@@ -27789,19 +27789,19 @@
         <v>31</v>
       </c>
       <c r="C941" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D941" t="s">
         <v>48</v>
       </c>
       <c r="E941">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F941">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G941">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H941">
         <v>0</v>
@@ -27818,19 +27818,19 @@
         <v>31</v>
       </c>
       <c r="C942" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D942" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E942">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F942">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G942">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H942">
         <v>0</v>
@@ -27850,16 +27850,16 @@
         <v>43</v>
       </c>
       <c r="D943" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E943">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F943">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G943">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H943">
         <v>0</v>
@@ -27876,19 +27876,19 @@
         <v>31</v>
       </c>
       <c r="C944" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D944" t="s">
         <v>48</v>
       </c>
       <c r="E944">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F944">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G944">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H944">
         <v>0</v>
@@ -27902,28 +27902,28 @@
         <v>24</v>
       </c>
       <c r="B945" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C945" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D945" t="s">
         <v>48</v>
       </c>
       <c r="E945">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F945">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G945">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H945">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I945">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="946" spans="1:9">
@@ -27934,22 +27934,22 @@
         <v>34</v>
       </c>
       <c r="C946" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D946" t="s">
         <v>48</v>
       </c>
       <c r="E946">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F946">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G946">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H946">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I946">
         <v>1</v>
@@ -27963,10 +27963,10 @@
         <v>34</v>
       </c>
       <c r="C947" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D947" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E947">
         <v>1</v>
@@ -27978,10 +27978,10 @@
         <v>1</v>
       </c>
       <c r="H947">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I947">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="948" spans="1:9">
@@ -27995,16 +27995,16 @@
         <v>40</v>
       </c>
       <c r="D948" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E948">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F948">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G948">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H948">
         <v>0</v>
@@ -28021,7 +28021,7 @@
         <v>34</v>
       </c>
       <c r="C949" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D949" t="s">
         <v>48</v>
@@ -28050,7 +28050,7 @@
         <v>34</v>
       </c>
       <c r="C950" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D950" t="s">
         <v>48</v>
@@ -28079,7 +28079,7 @@
         <v>34</v>
       </c>
       <c r="C951" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D951" t="s">
         <v>48</v>
@@ -28094,10 +28094,10 @@
         <v>0</v>
       </c>
       <c r="H951">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="I951">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="952" spans="1:9">
@@ -28105,28 +28105,28 @@
         <v>24</v>
       </c>
       <c r="B952" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C952" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D952" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E952">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F952">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G952">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H952">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="I952">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="953" spans="1:9">
@@ -28140,16 +28140,16 @@
         <v>45</v>
       </c>
       <c r="D953" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E953">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F953">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G953">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H953">
         <v>0</v>
@@ -28166,19 +28166,19 @@
         <v>30</v>
       </c>
       <c r="C954" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D954" t="s">
         <v>48</v>
       </c>
       <c r="E954">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F954">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G954">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H954">
         <v>0</v>
@@ -28195,19 +28195,19 @@
         <v>30</v>
       </c>
       <c r="C955" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D955" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E955">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F955">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G955">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H955">
         <v>0</v>
@@ -28227,16 +28227,16 @@
         <v>37</v>
       </c>
       <c r="D956" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E956">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F956">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G956">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H956">
         <v>0</v>
@@ -28253,25 +28253,25 @@
         <v>30</v>
       </c>
       <c r="C957" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D957" t="s">
         <v>48</v>
       </c>
       <c r="E957">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F957">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G957">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H957">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="I957">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="958" spans="1:9">
@@ -28282,25 +28282,25 @@
         <v>30</v>
       </c>
       <c r="C958" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D958" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E958">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F958">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G958">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H958">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="I958">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="959" spans="1:9">
@@ -28314,22 +28314,22 @@
         <v>39</v>
       </c>
       <c r="D959" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E959">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F959">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G959">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H959">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="I959">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="960" spans="1:9">
@@ -28340,25 +28340,25 @@
         <v>30</v>
       </c>
       <c r="C960" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D960" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E960">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F960">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G960">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H960">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="I960">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="961" spans="1:9">
@@ -28372,22 +28372,22 @@
         <v>40</v>
       </c>
       <c r="D961" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E961">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F961">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G961">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H961">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I961">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="962" spans="1:9">
@@ -28398,25 +28398,25 @@
         <v>30</v>
       </c>
       <c r="C962" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D962" t="s">
         <v>48</v>
       </c>
       <c r="E962">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="F962">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="G962">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H962">
-        <v>349</v>
+        <v>40</v>
       </c>
       <c r="I962">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="963" spans="1:9">
@@ -28427,25 +28427,25 @@
         <v>30</v>
       </c>
       <c r="C963" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D963" t="s">
         <v>48</v>
       </c>
       <c r="E963">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F963">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G963">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H963">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="I963">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="964" spans="1:9">
@@ -28456,19 +28456,19 @@
         <v>30</v>
       </c>
       <c r="C964" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D964" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E964">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F964">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G964">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H964">
         <v>0</v>
@@ -28488,22 +28488,22 @@
         <v>43</v>
       </c>
       <c r="D965" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E965">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F965">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G965">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H965">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I965">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="966" spans="1:9">
@@ -28514,25 +28514,25 @@
         <v>30</v>
       </c>
       <c r="C966" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D966" t="s">
         <v>48</v>
       </c>
       <c r="E966">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F966">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G966">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H966">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="I966">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="967" spans="1:9">
@@ -28543,24 +28543,53 @@
         <v>30</v>
       </c>
       <c r="C967" t="s">
+        <v>46</v>
+      </c>
+      <c r="D967" t="s">
+        <v>48</v>
+      </c>
+      <c r="E967">
+        <v>0</v>
+      </c>
+      <c r="F967">
+        <v>0</v>
+      </c>
+      <c r="G967">
+        <v>0</v>
+      </c>
+      <c r="H967">
+        <v>40</v>
+      </c>
+      <c r="I967">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="968" spans="1:9">
+      <c r="A968" t="s">
+        <v>24</v>
+      </c>
+      <c r="B968" t="s">
+        <v>30</v>
+      </c>
+      <c r="C968" t="s">
         <v>44</v>
       </c>
-      <c r="D967" t="s">
-        <v>48</v>
-      </c>
-      <c r="E967">
+      <c r="D968" t="s">
+        <v>48</v>
+      </c>
+      <c r="E968">
         <v>5</v>
       </c>
-      <c r="F967">
+      <c r="F968">
         <v>5</v>
       </c>
-      <c r="G967">
+      <c r="G968">
         <v>5</v>
       </c>
-      <c r="H967">
+      <c r="H968">
         <v>71</v>
       </c>
-      <c r="I967">
+      <c r="I968">
         <v>3</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4113" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4133" uniqueCount="55">
   <si>
     <t>Month</t>
   </si>
@@ -536,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1027"/>
+  <dimension ref="A1:I1032"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -25580,13 +25580,13 @@
         <v>53</v>
       </c>
       <c r="E864">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F864">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G864">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H864">
         <v>0</v>
@@ -25635,7 +25635,7 @@
         <v>42</v>
       </c>
       <c r="D866" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E866">
         <v>1</v>
@@ -25661,19 +25661,19 @@
         <v>31</v>
       </c>
       <c r="C867" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D867" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E867">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F867">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G867">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H867">
         <v>0</v>
@@ -25690,19 +25690,19 @@
         <v>31</v>
       </c>
       <c r="C868" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D868" t="s">
         <v>53</v>
       </c>
       <c r="E868">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F868">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G868">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H868">
         <v>0</v>
@@ -25719,25 +25719,25 @@
         <v>31</v>
       </c>
       <c r="C869" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D869" t="s">
         <v>53</v>
       </c>
       <c r="E869">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="F869">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G869">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="H869">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I869">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="870" spans="1:9">
@@ -25748,19 +25748,19 @@
         <v>31</v>
       </c>
       <c r="C870" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D870" t="s">
         <v>54</v>
       </c>
       <c r="E870">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="F870">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G870">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="H870">
         <v>0</v>
@@ -25777,25 +25777,25 @@
         <v>31</v>
       </c>
       <c r="C871" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D871" t="s">
         <v>53</v>
       </c>
       <c r="E871">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="F871">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="G871">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="H871">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I871">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="872" spans="1:9">
@@ -25806,19 +25806,19 @@
         <v>31</v>
       </c>
       <c r="C872" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D872" t="s">
         <v>54</v>
       </c>
       <c r="E872">
-        <v>136</v>
+        <v>27</v>
       </c>
       <c r="F872">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="G872">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="H872">
         <v>0</v>
@@ -25835,19 +25835,19 @@
         <v>31</v>
       </c>
       <c r="C873" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D873" t="s">
         <v>53</v>
       </c>
       <c r="E873">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="F873">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="G873">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="H873">
         <v>0</v>
@@ -25864,19 +25864,19 @@
         <v>31</v>
       </c>
       <c r="C874" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D874" t="s">
         <v>54</v>
       </c>
       <c r="E874">
-        <v>8</v>
+        <v>161</v>
       </c>
       <c r="F874">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="G874">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="H874">
         <v>0</v>
@@ -25893,19 +25893,19 @@
         <v>31</v>
       </c>
       <c r="C875" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D875" t="s">
         <v>53</v>
       </c>
       <c r="E875">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F875">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G875">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H875">
         <v>0</v>
@@ -25922,19 +25922,19 @@
         <v>31</v>
       </c>
       <c r="C876" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D876" t="s">
         <v>54</v>
       </c>
       <c r="E876">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F876">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G876">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H876">
         <v>0</v>
@@ -25951,19 +25951,19 @@
         <v>31</v>
       </c>
       <c r="C877" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D877" t="s">
         <v>53</v>
       </c>
       <c r="E877">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F877">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G877">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H877">
         <v>0</v>
@@ -25980,19 +25980,19 @@
         <v>31</v>
       </c>
       <c r="C878" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D878" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E878">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F878">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G878">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H878">
         <v>0</v>
@@ -26009,19 +26009,19 @@
         <v>31</v>
       </c>
       <c r="C879" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D879" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E879">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F879">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G879">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="H879">
         <v>0</v>
@@ -26038,19 +26038,19 @@
         <v>31</v>
       </c>
       <c r="C880" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D880" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E880">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F880">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G880">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H880">
         <v>0</v>
@@ -26067,19 +26067,19 @@
         <v>31</v>
       </c>
       <c r="C881" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D881" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E881">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F881">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="G881">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H881">
         <v>0</v>
@@ -26096,25 +26096,25 @@
         <v>31</v>
       </c>
       <c r="C882" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D882" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E882">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F882">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G882">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H882">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I882">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="883" spans="1:9">
@@ -26125,19 +26125,19 @@
         <v>31</v>
       </c>
       <c r="C883" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D883" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E883">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="F883">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="G883">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="H883">
         <v>0</v>
@@ -26151,28 +26151,28 @@
         <v>24</v>
       </c>
       <c r="B884" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C884" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D884" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E884">
-        <v>182</v>
+        <v>5</v>
       </c>
       <c r="F884">
-        <v>190</v>
+        <v>5</v>
       </c>
       <c r="G884">
-        <v>190</v>
+        <v>5</v>
       </c>
       <c r="H884">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I884">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="885" spans="1:9">
@@ -26180,25 +26180,25 @@
         <v>24</v>
       </c>
       <c r="B885" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C885" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D885" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E885">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="F885">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="G885">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="H885">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I885">
         <v>1</v>
@@ -26209,22 +26209,22 @@
         <v>24</v>
       </c>
       <c r="B886" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C886" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D886" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E886">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="F886">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="G886">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="H886">
         <v>0</v>
@@ -26241,22 +26241,22 @@
         <v>25</v>
       </c>
       <c r="C887" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D887" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E887">
-        <v>7</v>
+        <v>216</v>
       </c>
       <c r="F887">
-        <v>7</v>
+        <v>224</v>
       </c>
       <c r="G887">
-        <v>7</v>
+        <v>224</v>
       </c>
       <c r="H887">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I887">
         <v>1</v>
@@ -26270,25 +26270,25 @@
         <v>25</v>
       </c>
       <c r="C888" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D888" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E888">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F888">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G888">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H888">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I888">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="889" spans="1:9">
@@ -26299,25 +26299,25 @@
         <v>25</v>
       </c>
       <c r="C889" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D889" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E889">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F889">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G889">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H889">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="I889">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="890" spans="1:9">
@@ -26328,25 +26328,25 @@
         <v>25</v>
       </c>
       <c r="C890" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D890" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E890">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F890">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G890">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H890">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I890">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="891" spans="1:9">
@@ -26357,25 +26357,25 @@
         <v>25</v>
       </c>
       <c r="C891" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D891" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E891">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F891">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G891">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H891">
-        <v>5917</v>
+        <v>0</v>
       </c>
       <c r="I891">
-        <v>211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="892" spans="1:9">
@@ -26386,25 +26386,25 @@
         <v>25</v>
       </c>
       <c r="C892" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D892" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E892">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="F892">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="G892">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="H892">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="I892">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="893" spans="1:9">
@@ -26415,25 +26415,25 @@
         <v>25</v>
       </c>
       <c r="C893" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D893" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E893">
-        <v>103</v>
+        <v>10</v>
       </c>
       <c r="F893">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="G893">
-        <v>127</v>
+        <v>10</v>
       </c>
       <c r="H893">
-        <v>3432</v>
+        <v>0</v>
       </c>
       <c r="I893">
-        <v>122</v>
+        <v>0</v>
       </c>
     </row>
     <row r="894" spans="1:9">
@@ -26444,25 +26444,25 @@
         <v>25</v>
       </c>
       <c r="C894" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D894" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E894">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="F894">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="G894">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="H894">
-        <v>0</v>
+        <v>5917</v>
       </c>
       <c r="I894">
-        <v>0</v>
+        <v>211</v>
       </c>
     </row>
     <row r="895" spans="1:9">
@@ -26473,25 +26473,25 @@
         <v>25</v>
       </c>
       <c r="C895" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D895" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E895">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="F895">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="G895">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="H895">
-        <v>739</v>
+        <v>25</v>
       </c>
       <c r="I895">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="896" spans="1:9">
@@ -26502,25 +26502,25 @@
         <v>25</v>
       </c>
       <c r="C896" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D896" t="s">
         <v>54</v>
       </c>
       <c r="E896">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="F896">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="G896">
-        <v>5</v>
+        <v>128</v>
       </c>
       <c r="H896">
-        <v>2656</v>
+        <v>3432</v>
       </c>
       <c r="I896">
-        <v>105</v>
+        <v>122</v>
       </c>
     </row>
     <row r="897" spans="1:9">
@@ -26531,19 +26531,19 @@
         <v>25</v>
       </c>
       <c r="C897" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D897" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E897">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="F897">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="G897">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="H897">
         <v>0</v>
@@ -26560,25 +26560,25 @@
         <v>25</v>
       </c>
       <c r="C898" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D898" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E898">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F898">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="G898">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="H898">
-        <v>158</v>
+        <v>739</v>
       </c>
       <c r="I898">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="899" spans="1:9">
@@ -26589,25 +26589,25 @@
         <v>25</v>
       </c>
       <c r="C899" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D899" t="s">
         <v>54</v>
       </c>
       <c r="E899">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F899">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="G899">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="H899">
-        <v>601</v>
+        <v>2656</v>
       </c>
       <c r="I899">
-        <v>31</v>
+        <v>105</v>
       </c>
     </row>
     <row r="900" spans="1:9">
@@ -26618,25 +26618,25 @@
         <v>25</v>
       </c>
       <c r="C900" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D900" t="s">
         <v>54</v>
       </c>
       <c r="E900">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F900">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G900">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H900">
-        <v>2098</v>
+        <v>0</v>
       </c>
       <c r="I900">
-        <v>122</v>
+        <v>0</v>
       </c>
     </row>
     <row r="901" spans="1:9">
@@ -26647,25 +26647,25 @@
         <v>25</v>
       </c>
       <c r="C901" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D901" t="s">
         <v>53</v>
       </c>
       <c r="E901">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="F901">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="G901">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="H901">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="I901">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="902" spans="1:9">
@@ -26676,25 +26676,25 @@
         <v>25</v>
       </c>
       <c r="C902" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D902" t="s">
         <v>54</v>
       </c>
       <c r="E902">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="F902">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="G902">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="H902">
-        <v>4319</v>
+        <v>601</v>
       </c>
       <c r="I902">
-        <v>161</v>
+        <v>31</v>
       </c>
     </row>
     <row r="903" spans="1:9">
@@ -26702,28 +26702,28 @@
         <v>24</v>
       </c>
       <c r="B903" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C903" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D903" t="s">
         <v>54</v>
       </c>
       <c r="E903">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F903">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G903">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H903">
-        <v>0</v>
+        <v>2098</v>
       </c>
       <c r="I903">
-        <v>0</v>
+        <v>122</v>
       </c>
     </row>
     <row r="904" spans="1:9">
@@ -26731,22 +26731,22 @@
         <v>24</v>
       </c>
       <c r="B904" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C904" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D904" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E904">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F904">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G904">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H904">
         <v>0</v>
@@ -26760,7 +26760,7 @@
         <v>24</v>
       </c>
       <c r="B905" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C905" t="s">
         <v>50</v>
@@ -26769,19 +26769,19 @@
         <v>54</v>
       </c>
       <c r="E905">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F905">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G905">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H905">
-        <v>0</v>
+        <v>4319</v>
       </c>
       <c r="I905">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="906" spans="1:9">
@@ -26789,22 +26789,22 @@
         <v>24</v>
       </c>
       <c r="B906" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C906" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D906" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E906">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="F906">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G906">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="H906">
         <v>0</v>
@@ -26818,28 +26818,28 @@
         <v>24</v>
       </c>
       <c r="B907" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C907" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D907" t="s">
         <v>54</v>
       </c>
       <c r="E907">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F907">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G907">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H907">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="I907">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="908" spans="1:9">
@@ -26847,22 +26847,22 @@
         <v>24</v>
       </c>
       <c r="B908" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C908" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D908" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E908">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F908">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G908">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H908">
         <v>0</v>
@@ -26879,19 +26879,19 @@
         <v>26</v>
       </c>
       <c r="C909" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D909" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E909">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="F909">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G909">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="H909">
         <v>0</v>
@@ -26908,25 +26908,25 @@
         <v>26</v>
       </c>
       <c r="C910" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D910" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E910">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="F910">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G910">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H910">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="I910">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="911" spans="1:9">
@@ -26937,25 +26937,25 @@
         <v>26</v>
       </c>
       <c r="C911" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D911" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E911">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F911">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G911">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H911">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I911">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="912" spans="1:9">
@@ -26966,25 +26966,25 @@
         <v>26</v>
       </c>
       <c r="C912" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D912" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E912">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F912">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G912">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H912">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="I912">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="913" spans="1:9">
@@ -26995,25 +26995,25 @@
         <v>26</v>
       </c>
       <c r="C913" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D913" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E913">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F913">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G913">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H913">
-        <v>529</v>
+        <v>0</v>
       </c>
       <c r="I913">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="914" spans="1:9">
@@ -27024,25 +27024,25 @@
         <v>26</v>
       </c>
       <c r="C914" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D914" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E914">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F914">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G914">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H914">
-        <v>23</v>
+        <v>150</v>
       </c>
       <c r="I914">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="915" spans="1:9">
@@ -27053,25 +27053,25 @@
         <v>26</v>
       </c>
       <c r="C915" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D915" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E915">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="F915">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="G915">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="H915">
-        <v>475</v>
+        <v>65</v>
       </c>
       <c r="I915">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="916" spans="1:9">
@@ -27082,25 +27082,25 @@
         <v>26</v>
       </c>
       <c r="C916" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D916" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E916">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="F916">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="G916">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="H916">
-        <v>0</v>
+        <v>529</v>
       </c>
       <c r="I916">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="917" spans="1:9">
@@ -27111,25 +27111,25 @@
         <v>26</v>
       </c>
       <c r="C917" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D917" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E917">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F917">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G917">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="H917">
-        <v>318</v>
+        <v>23</v>
       </c>
       <c r="I917">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="918" spans="1:9">
@@ -27140,25 +27140,25 @@
         <v>26</v>
       </c>
       <c r="C918" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D918" t="s">
         <v>54</v>
       </c>
       <c r="E918">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="F918">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="G918">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="H918">
-        <v>212</v>
+        <v>475</v>
       </c>
       <c r="I918">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="919" spans="1:9">
@@ -27169,25 +27169,25 @@
         <v>26</v>
       </c>
       <c r="C919" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D919" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E919">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="F919">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="G919">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="H919">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I919">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="920" spans="1:9">
@@ -27198,25 +27198,25 @@
         <v>26</v>
       </c>
       <c r="C920" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D920" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E920">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F920">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G920">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H920">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="I920">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="921" spans="1:9">
@@ -27227,25 +27227,25 @@
         <v>26</v>
       </c>
       <c r="C921" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D921" t="s">
         <v>54</v>
       </c>
       <c r="E921">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="F921">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="G921">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="H921">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="I921">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="922" spans="1:9">
@@ -27256,25 +27256,25 @@
         <v>26</v>
       </c>
       <c r="C922" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D922" t="s">
         <v>54</v>
       </c>
       <c r="E922">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F922">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G922">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H922">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I922">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="923" spans="1:9">
@@ -27285,25 +27285,25 @@
         <v>26</v>
       </c>
       <c r="C923" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D923" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E923">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F923">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="G923">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="H923">
-        <v>328</v>
+        <v>0</v>
       </c>
       <c r="I923">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="924" spans="1:9">
@@ -27311,28 +27311,28 @@
         <v>24</v>
       </c>
       <c r="B924" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C924" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D924" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E924">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F924">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="G924">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="H924">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I924">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="925" spans="1:9">
@@ -27340,22 +27340,22 @@
         <v>24</v>
       </c>
       <c r="B925" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C925" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D925" t="s">
         <v>54</v>
       </c>
       <c r="E925">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F925">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G925">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H925">
         <v>0</v>
@@ -27369,28 +27369,28 @@
         <v>24</v>
       </c>
       <c r="B926" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C926" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D926" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E926">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F926">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G926">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H926">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="I926">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="927" spans="1:9">
@@ -27401,19 +27401,19 @@
         <v>30</v>
       </c>
       <c r="C927" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D927" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E927">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F927">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G927">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H927">
         <v>0</v>
@@ -27430,10 +27430,10 @@
         <v>30</v>
       </c>
       <c r="C928" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D928" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E928">
         <v>2</v>
@@ -27459,19 +27459,19 @@
         <v>30</v>
       </c>
       <c r="C929" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D929" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E929">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F929">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G929">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H929">
         <v>0</v>
@@ -27488,19 +27488,19 @@
         <v>30</v>
       </c>
       <c r="C930" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D930" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E930">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F930">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G930">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H930">
         <v>0</v>
@@ -27517,19 +27517,19 @@
         <v>30</v>
       </c>
       <c r="C931" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D931" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E931">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F931">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G931">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H931">
         <v>0</v>
@@ -27546,25 +27546,25 @@
         <v>30</v>
       </c>
       <c r="C932" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D932" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E932">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F932">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G932">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H932">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I932">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="933" spans="1:9">
@@ -27575,25 +27575,25 @@
         <v>30</v>
       </c>
       <c r="C933" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D933" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E933">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="F933">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="G933">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="H933">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I933">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="934" spans="1:9">
@@ -27604,19 +27604,19 @@
         <v>30</v>
       </c>
       <c r="C934" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D934" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E934">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F934">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G934">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="H934">
         <v>0</v>
@@ -27633,25 +27633,25 @@
         <v>30</v>
       </c>
       <c r="C935" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D935" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E935">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="F935">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="G935">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H935">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I935">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="936" spans="1:9">
@@ -27662,25 +27662,25 @@
         <v>30</v>
       </c>
       <c r="C936" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D936" t="s">
         <v>54</v>
       </c>
       <c r="E936">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="F936">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="G936">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="H936">
-        <v>272</v>
+        <v>38</v>
       </c>
       <c r="I936">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="937" spans="1:9">
@@ -27691,19 +27691,19 @@
         <v>30</v>
       </c>
       <c r="C937" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D937" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E937">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F937">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="G937">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="H937">
         <v>0</v>
@@ -27720,25 +27720,25 @@
         <v>30</v>
       </c>
       <c r="C938" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D938" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E938">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="F938">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="G938">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H938">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I938">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="939" spans="1:9">
@@ -27749,25 +27749,25 @@
         <v>30</v>
       </c>
       <c r="C939" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D939" t="s">
         <v>54</v>
       </c>
       <c r="E939">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F939">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="G939">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H939">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="I939">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="940" spans="1:9">
@@ -27778,19 +27778,19 @@
         <v>30</v>
       </c>
       <c r="C940" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D940" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E940">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F940">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G940">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H940">
         <v>0</v>
@@ -27807,25 +27807,25 @@
         <v>30</v>
       </c>
       <c r="C941" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D941" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E941">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="F941">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="G941">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H941">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I941">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="942" spans="1:9">
@@ -27833,22 +27833,22 @@
         <v>24</v>
       </c>
       <c r="B942" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C942" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D942" t="s">
         <v>54</v>
       </c>
       <c r="E942">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="F942">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="G942">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H942">
         <v>0</v>
@@ -27862,13 +27862,13 @@
         <v>24</v>
       </c>
       <c r="B943" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C943" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D943" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E943">
         <v>2</v>
@@ -27891,22 +27891,22 @@
         <v>24</v>
       </c>
       <c r="B944" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C944" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D944" t="s">
         <v>54</v>
       </c>
       <c r="E944">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F944">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G944">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H944">
         <v>0</v>
@@ -27923,7 +27923,7 @@
         <v>39</v>
       </c>
       <c r="C945" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D945" t="s">
         <v>54</v>
@@ -27952,19 +27952,19 @@
         <v>39</v>
       </c>
       <c r="C946" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D946" t="s">
         <v>54</v>
       </c>
       <c r="E946">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F946">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G946">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H946">
         <v>0</v>
@@ -27978,22 +27978,22 @@
         <v>24</v>
       </c>
       <c r="B947" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C947" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D947" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E947">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F947">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G947">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H947">
         <v>0</v>
@@ -28007,13 +28007,13 @@
         <v>24</v>
       </c>
       <c r="B948" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C948" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D948" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E948">
         <v>1</v>
@@ -28036,22 +28036,22 @@
         <v>24</v>
       </c>
       <c r="B949" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C949" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D949" t="s">
         <v>54</v>
       </c>
       <c r="E949">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F949">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G949">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H949">
         <v>0</v>
@@ -28068,19 +28068,19 @@
         <v>32</v>
       </c>
       <c r="C950" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D950" t="s">
         <v>53</v>
       </c>
       <c r="E950">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F950">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G950">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H950">
         <v>0</v>
@@ -28097,25 +28097,25 @@
         <v>32</v>
       </c>
       <c r="C951" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D951" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E951">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F951">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G951">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H951">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="I951">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="952" spans="1:9">
@@ -28126,19 +28126,19 @@
         <v>32</v>
       </c>
       <c r="C952" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D952" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E952">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F952">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G952">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H952">
         <v>0</v>
@@ -28155,19 +28155,19 @@
         <v>32</v>
       </c>
       <c r="C953" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D953" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E953">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F953">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G953">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H953">
         <v>0</v>
@@ -28184,25 +28184,25 @@
         <v>32</v>
       </c>
       <c r="C954" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D954" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E954">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F954">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G954">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H954">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="I954">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="955" spans="1:9">
@@ -28213,25 +28213,25 @@
         <v>32</v>
       </c>
       <c r="C955" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D955" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E955">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F955">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G955">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H955">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I955">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="956" spans="1:9">
@@ -28242,19 +28242,19 @@
         <v>32</v>
       </c>
       <c r="C956" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D956" t="s">
         <v>54</v>
       </c>
       <c r="E956">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F956">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G956">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H956">
         <v>0</v>
@@ -28268,28 +28268,28 @@
         <v>24</v>
       </c>
       <c r="B957" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C957" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D957" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E957">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F957">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G957">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H957">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I957">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="958" spans="1:9">
@@ -28297,10 +28297,10 @@
         <v>24</v>
       </c>
       <c r="B958" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C958" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D958" t="s">
         <v>54</v>
@@ -28326,28 +28326,28 @@
         <v>24</v>
       </c>
       <c r="B959" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C959" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D959" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E959">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F959">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G959">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H959">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I959">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="960" spans="1:9">
@@ -28355,22 +28355,22 @@
         <v>24</v>
       </c>
       <c r="B960" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C960" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D960" t="s">
         <v>54</v>
       </c>
       <c r="E960">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F960">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G960">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H960">
         <v>0</v>
@@ -28384,28 +28384,28 @@
         <v>24</v>
       </c>
       <c r="B961" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C961" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D961" t="s">
         <v>54</v>
       </c>
       <c r="E961">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F961">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G961">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H961">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I961">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="962" spans="1:9">
@@ -28413,13 +28413,13 @@
         <v>24</v>
       </c>
       <c r="B962" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C962" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D962" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E962">
         <v>1</v>
@@ -28442,7 +28442,7 @@
         <v>24</v>
       </c>
       <c r="B963" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C963" t="s">
         <v>45</v>
@@ -28471,7 +28471,7 @@
         <v>24</v>
       </c>
       <c r="B964" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C964" t="s">
         <v>45</v>
@@ -28500,22 +28500,22 @@
         <v>24</v>
       </c>
       <c r="B965" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C965" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D965" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E965">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F965">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G965">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H965">
         <v>0</v>
@@ -28532,10 +28532,10 @@
         <v>35</v>
       </c>
       <c r="C966" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D966" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E966">
         <v>1</v>
@@ -28561,19 +28561,19 @@
         <v>35</v>
       </c>
       <c r="C967" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D967" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E967">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F967">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G967">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H967">
         <v>0</v>
@@ -28587,22 +28587,22 @@
         <v>24</v>
       </c>
       <c r="B968" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C968" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D968" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E968">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F968">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G968">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H968">
         <v>0</v>
@@ -28616,22 +28616,22 @@
         <v>24</v>
       </c>
       <c r="B969" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C969" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D969" t="s">
         <v>53</v>
       </c>
       <c r="E969">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F969">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G969">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H969">
         <v>0</v>
@@ -28645,22 +28645,22 @@
         <v>24</v>
       </c>
       <c r="B970" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C970" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D970" t="s">
         <v>54</v>
       </c>
       <c r="E970">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F970">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G970">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H970">
         <v>0</v>
@@ -28674,22 +28674,22 @@
         <v>24</v>
       </c>
       <c r="B971" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C971" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D971" t="s">
         <v>54</v>
       </c>
       <c r="E971">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F971">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G971">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H971">
         <v>0</v>
@@ -28706,19 +28706,19 @@
         <v>37</v>
       </c>
       <c r="C972" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D972" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E972">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F972">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G972">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H972">
         <v>0</v>
@@ -28735,19 +28735,19 @@
         <v>37</v>
       </c>
       <c r="C973" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D973" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E973">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F973">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G973">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H973">
         <v>0</v>
@@ -28761,22 +28761,22 @@
         <v>24</v>
       </c>
       <c r="B974" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C974" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D974" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E974">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F974">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="G974">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H974">
         <v>0</v>
@@ -28790,22 +28790,22 @@
         <v>24</v>
       </c>
       <c r="B975" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C975" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D975" t="s">
         <v>54</v>
       </c>
       <c r="E975">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F975">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G975">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H975">
         <v>0</v>
@@ -28819,22 +28819,22 @@
         <v>24</v>
       </c>
       <c r="B976" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C976" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D976" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E976">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F976">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G976">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H976">
         <v>0</v>
@@ -28848,22 +28848,22 @@
         <v>24</v>
       </c>
       <c r="B977" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C977" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D977" t="s">
         <v>54</v>
       </c>
       <c r="E977">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F977">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G977">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H977">
         <v>0</v>
@@ -28880,19 +28880,19 @@
         <v>38</v>
       </c>
       <c r="C978" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D978" t="s">
         <v>53</v>
       </c>
       <c r="E978">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F978">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="G978">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="H978">
         <v>0</v>
@@ -28909,25 +28909,25 @@
         <v>38</v>
       </c>
       <c r="C979" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D979" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E979">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F979">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G979">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H979">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I979">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="980" spans="1:9">
@@ -28938,19 +28938,19 @@
         <v>38</v>
       </c>
       <c r="C980" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D980" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E980">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F980">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="G980">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="H980">
         <v>0</v>
@@ -28967,25 +28967,25 @@
         <v>38</v>
       </c>
       <c r="C981" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D981" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E981">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="F981">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="G981">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="H981">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="I981">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="982" spans="1:9">
@@ -28996,19 +28996,19 @@
         <v>38</v>
       </c>
       <c r="C982" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D982" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E982">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="F982">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="G982">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="H982">
         <v>0</v>
@@ -29025,19 +29025,19 @@
         <v>38</v>
       </c>
       <c r="C983" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D983" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E983">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="F983">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="G983">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="H983">
         <v>0</v>
@@ -29054,22 +29054,22 @@
         <v>38</v>
       </c>
       <c r="C984" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D984" t="s">
         <v>54</v>
       </c>
       <c r="E984">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F984">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G984">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H984">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I984">
         <v>2</v>
@@ -29083,19 +29083,19 @@
         <v>38</v>
       </c>
       <c r="C985" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D985" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E985">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="F985">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="G985">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="H985">
         <v>0</v>
@@ -29112,25 +29112,25 @@
         <v>38</v>
       </c>
       <c r="C986" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D986" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E986">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="F986">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="G986">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="H986">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="I986">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="987" spans="1:9">
@@ -29141,19 +29141,19 @@
         <v>38</v>
       </c>
       <c r="C987" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D987" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E987">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F987">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="G987">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="H987">
         <v>0</v>
@@ -29170,19 +29170,19 @@
         <v>38</v>
       </c>
       <c r="C988" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D988" t="s">
         <v>54</v>
       </c>
       <c r="E988">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="F988">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="G988">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="H988">
         <v>0</v>
@@ -29199,25 +29199,25 @@
         <v>38</v>
       </c>
       <c r="C989" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D989" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E989">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F989">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G989">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H989">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I989">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="990" spans="1:9">
@@ -29228,19 +29228,19 @@
         <v>38</v>
       </c>
       <c r="C990" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D990" t="s">
         <v>54</v>
       </c>
       <c r="E990">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F990">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G990">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H990">
         <v>0</v>
@@ -29254,28 +29254,28 @@
         <v>24</v>
       </c>
       <c r="B991" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C991" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D991" t="s">
         <v>53</v>
       </c>
       <c r="E991">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F991">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="G991">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="H991">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I991">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="992" spans="1:9">
@@ -29283,22 +29283,22 @@
         <v>24</v>
       </c>
       <c r="B992" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C992" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D992" t="s">
         <v>54</v>
       </c>
       <c r="E992">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F992">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G992">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H992">
         <v>0</v>
@@ -29312,28 +29312,28 @@
         <v>24</v>
       </c>
       <c r="B993" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C993" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D993" t="s">
         <v>54</v>
       </c>
       <c r="E993">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F993">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G993">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H993">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I993">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="994" spans="1:9">
@@ -29341,22 +29341,22 @@
         <v>24</v>
       </c>
       <c r="B994" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C994" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D994" t="s">
         <v>53</v>
       </c>
       <c r="E994">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F994">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G994">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H994">
         <v>0</v>
@@ -29370,28 +29370,28 @@
         <v>24</v>
       </c>
       <c r="B995" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C995" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D995" t="s">
         <v>54</v>
       </c>
       <c r="E995">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F995">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G995">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H995">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I995">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="996" spans="1:9">
@@ -29402,19 +29402,19 @@
         <v>34</v>
       </c>
       <c r="C996" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D996" t="s">
         <v>53</v>
       </c>
       <c r="E996">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F996">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G996">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H996">
         <v>0</v>
@@ -29431,19 +29431,19 @@
         <v>34</v>
       </c>
       <c r="C997" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D997" t="s">
         <v>54</v>
       </c>
       <c r="E997">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F997">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G997">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H997">
         <v>0</v>
@@ -29460,25 +29460,25 @@
         <v>34</v>
       </c>
       <c r="C998" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D998" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E998">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F998">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G998">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H998">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I998">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="999" spans="1:9">
@@ -29489,10 +29489,10 @@
         <v>34</v>
       </c>
       <c r="C999" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D999" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E999">
         <v>2</v>
@@ -29518,25 +29518,25 @@
         <v>34</v>
       </c>
       <c r="C1000" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D1000" t="s">
         <v>54</v>
       </c>
       <c r="E1000">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F1000">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G1000">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H1000">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I1000">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1001" spans="1:9">
@@ -29547,19 +29547,19 @@
         <v>34</v>
       </c>
       <c r="C1001" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D1001" t="s">
         <v>53</v>
       </c>
       <c r="E1001">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F1001">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1001">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1001">
         <v>0</v>
@@ -29576,25 +29576,25 @@
         <v>34</v>
       </c>
       <c r="C1002" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D1002" t="s">
         <v>54</v>
       </c>
       <c r="E1002">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1002">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1002">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H1002">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="I1002">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1003" spans="1:9">
@@ -29602,22 +29602,22 @@
         <v>24</v>
       </c>
       <c r="B1003" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C1003" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D1003" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1003">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1003">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1003">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1003">
         <v>0</v>
@@ -29631,22 +29631,22 @@
         <v>24</v>
       </c>
       <c r="B1004" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C1004" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D1004" t="s">
         <v>54</v>
       </c>
       <c r="E1004">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1004">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1004">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1004">
         <v>0</v>
@@ -29660,22 +29660,22 @@
         <v>24</v>
       </c>
       <c r="B1005" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C1005" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D1005" t="s">
         <v>54</v>
       </c>
       <c r="E1005">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1005">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1005">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1005">
         <v>0</v>
@@ -29689,13 +29689,13 @@
         <v>24</v>
       </c>
       <c r="B1006" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C1006" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D1006" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1006">
         <v>1</v>
@@ -29718,7 +29718,7 @@
         <v>24</v>
       </c>
       <c r="B1007" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C1007" t="s">
         <v>50</v>
@@ -29727,19 +29727,19 @@
         <v>54</v>
       </c>
       <c r="E1007">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1007">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1007">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1007">
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="I1007">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1008" spans="1:9">
@@ -29747,22 +29747,22 @@
         <v>24</v>
       </c>
       <c r="B1008" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C1008" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D1008" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1008">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F1008">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G1008">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H1008">
         <v>0</v>
@@ -29776,22 +29776,22 @@
         <v>24</v>
       </c>
       <c r="B1009" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C1009" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D1009" t="s">
         <v>54</v>
       </c>
       <c r="E1009">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1009">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1009">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1009">
         <v>0</v>
@@ -29805,13 +29805,13 @@
         <v>24</v>
       </c>
       <c r="B1010" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C1010" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D1010" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1010">
         <v>1</v>
@@ -29834,22 +29834,22 @@
         <v>24</v>
       </c>
       <c r="B1011" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C1011" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D1011" t="s">
         <v>54</v>
       </c>
       <c r="E1011">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F1011">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1011">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1011">
         <v>0</v>
@@ -29863,28 +29863,28 @@
         <v>24</v>
       </c>
       <c r="B1012" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C1012" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D1012" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1012">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1012">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1012">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1012">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I1012">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1013" spans="1:9">
@@ -29895,19 +29895,19 @@
         <v>28</v>
       </c>
       <c r="C1013" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D1013" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1013">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F1013">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G1013">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H1013">
         <v>0</v>
@@ -29924,19 +29924,19 @@
         <v>28</v>
       </c>
       <c r="C1014" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D1014" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1014">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1014">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1014">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1014">
         <v>0</v>
@@ -29953,25 +29953,25 @@
         <v>28</v>
       </c>
       <c r="C1015" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D1015" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1015">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F1015">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1015">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1015">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="I1015">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1016" spans="1:9">
@@ -29982,19 +29982,19 @@
         <v>28</v>
       </c>
       <c r="C1016" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D1016" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1016">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F1016">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G1016">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H1016">
         <v>0</v>
@@ -30011,25 +30011,25 @@
         <v>28</v>
       </c>
       <c r="C1017" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D1017" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1017">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F1017">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G1017">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="H1017">
-        <v>216</v>
+        <v>19</v>
       </c>
       <c r="I1017">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1018" spans="1:9">
@@ -30040,19 +30040,19 @@
         <v>28</v>
       </c>
       <c r="C1018" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D1018" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1018">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F1018">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="G1018">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H1018">
         <v>0</v>
@@ -30069,25 +30069,25 @@
         <v>28</v>
       </c>
       <c r="C1019" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D1019" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1019">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F1019">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G1019">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="H1019">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I1019">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1020" spans="1:9">
@@ -30098,25 +30098,25 @@
         <v>28</v>
       </c>
       <c r="C1020" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D1020" t="s">
         <v>54</v>
       </c>
       <c r="E1020">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F1020">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1020">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1020">
-        <v>77</v>
+        <v>324</v>
       </c>
       <c r="I1020">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1021" spans="1:9">
@@ -30127,19 +30127,19 @@
         <v>28</v>
       </c>
       <c r="C1021" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D1021" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1021">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F1021">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="G1021">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H1021">
         <v>0</v>
@@ -30156,25 +30156,25 @@
         <v>28</v>
       </c>
       <c r="C1022" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D1022" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1022">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F1022">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G1022">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H1022">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="I1022">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1023" spans="1:9">
@@ -30185,25 +30185,25 @@
         <v>28</v>
       </c>
       <c r="C1023" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D1023" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1023">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F1023">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G1023">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H1023">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I1023">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1024" spans="1:9">
@@ -30214,25 +30214,25 @@
         <v>28</v>
       </c>
       <c r="C1024" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D1024" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1024">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F1024">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="G1024">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="H1024">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I1024">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1025" spans="1:9">
@@ -30243,25 +30243,25 @@
         <v>28</v>
       </c>
       <c r="C1025" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D1025" t="s">
         <v>54</v>
       </c>
       <c r="E1025">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1025">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1025">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1025">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="I1025">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1026" spans="1:9">
@@ -30272,19 +30272,19 @@
         <v>28</v>
       </c>
       <c r="C1026" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D1026" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1026">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F1026">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G1026">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H1026">
         <v>0</v>
@@ -30301,24 +30301,169 @@
         <v>28</v>
       </c>
       <c r="C1027" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1027" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1027">
+        <v>31</v>
+      </c>
+      <c r="F1027">
+        <v>31</v>
+      </c>
+      <c r="G1027">
+        <v>31</v>
+      </c>
+      <c r="H1027">
+        <v>0</v>
+      </c>
+      <c r="I1027">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:9">
+      <c r="A1028" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1028" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1028" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1028">
+        <v>29</v>
+      </c>
+      <c r="F1028">
+        <v>32</v>
+      </c>
+      <c r="G1028">
+        <v>32</v>
+      </c>
+      <c r="H1028">
+        <v>19</v>
+      </c>
+      <c r="I1028">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:9">
+      <c r="A1029" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1029" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1029" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1029" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1029">
+        <v>1</v>
+      </c>
+      <c r="F1029">
+        <v>1</v>
+      </c>
+      <c r="G1029">
+        <v>1</v>
+      </c>
+      <c r="H1029">
+        <v>0</v>
+      </c>
+      <c r="I1029">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:9">
+      <c r="A1030" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1030" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1030" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1030" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1030">
+        <v>0</v>
+      </c>
+      <c r="F1030">
+        <v>0</v>
+      </c>
+      <c r="G1030">
+        <v>0</v>
+      </c>
+      <c r="H1030">
+        <v>40</v>
+      </c>
+      <c r="I1030">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:9">
+      <c r="A1031" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1031" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1031" t="s">
         <v>50</v>
       </c>
-      <c r="D1027" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1027">
+      <c r="D1031" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1031">
+        <v>1</v>
+      </c>
+      <c r="F1031">
+        <v>1</v>
+      </c>
+      <c r="G1031">
+        <v>1</v>
+      </c>
+      <c r="H1031">
+        <v>0</v>
+      </c>
+      <c r="I1031">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:9">
+      <c r="A1032" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1032" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1032" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1032" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1032">
         <v>8</v>
       </c>
-      <c r="F1027">
+      <c r="F1032">
         <v>8</v>
       </c>
-      <c r="G1027">
+      <c r="G1032">
         <v>8</v>
       </c>
-      <c r="H1027">
-        <v>0</v>
-      </c>
-      <c r="I1027">
+      <c r="H1032">
+        <v>0</v>
+      </c>
+      <c r="I1032">
         <v>0</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -17324,7 +17324,7 @@
         <v>157</v>
       </c>
       <c r="I579">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="580" spans="1:9">
@@ -17382,7 +17382,7 @@
         <v>219</v>
       </c>
       <c r="I581">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="582" spans="1:9">
@@ -17469,7 +17469,7 @@
         <v>167</v>
       </c>
       <c r="I584">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="585" spans="1:9">
@@ -17498,7 +17498,7 @@
         <v>229</v>
       </c>
       <c r="I585">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="586" spans="1:9">
@@ -17524,10 +17524,10 @@
         <v>41</v>
       </c>
       <c r="H586">
-        <v>34508</v>
+        <v>34352</v>
       </c>
       <c r="I586">
-        <v>1486</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="587" spans="1:9">
@@ -17556,7 +17556,7 @@
         <v>2107</v>
       </c>
       <c r="I587">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="588" spans="1:9">
@@ -17582,10 +17582,10 @@
         <v>255</v>
       </c>
       <c r="H588">
-        <v>18036</v>
+        <v>18046</v>
       </c>
       <c r="I588">
-        <v>906</v>
+        <v>859</v>
       </c>
     </row>
     <row r="589" spans="1:9">
@@ -17614,7 +17614,7 @@
         <v>278</v>
       </c>
       <c r="I589">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="590" spans="1:9">
@@ -17643,7 +17643,7 @@
         <v>1335</v>
       </c>
       <c r="I590">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="591" spans="1:9">
@@ -17672,7 +17672,7 @@
         <v>982</v>
       </c>
       <c r="I591">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="592" spans="1:9">
@@ -17701,7 +17701,7 @@
         <v>10482</v>
       </c>
       <c r="I592">
-        <v>438</v>
+        <v>401</v>
       </c>
     </row>
     <row r="593" spans="1:9">
@@ -17788,7 +17788,7 @@
         <v>964</v>
       </c>
       <c r="I595">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="596" spans="1:9">
@@ -17817,7 +17817,7 @@
         <v>2745</v>
       </c>
       <c r="I596">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="597" spans="1:9">
@@ -17872,10 +17872,10 @@
         <v>4</v>
       </c>
       <c r="H598">
-        <v>9341</v>
+        <v>9380</v>
       </c>
       <c r="I598">
-        <v>373</v>
+        <v>344</v>
       </c>
     </row>
     <row r="599" spans="1:9">
@@ -17904,7 +17904,7 @@
         <v>2910</v>
       </c>
       <c r="I599">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
     <row r="600" spans="1:9">
@@ -17933,7 +17933,7 @@
         <v>7079</v>
       </c>
       <c r="I600">
-        <v>299</v>
+        <v>278</v>
       </c>
     </row>
     <row r="601" spans="1:9">
@@ -18136,7 +18136,7 @@
         <v>152</v>
       </c>
       <c r="I607">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="608" spans="1:9">
@@ -18165,7 +18165,7 @@
         <v>509</v>
       </c>
       <c r="I608">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="609" spans="1:9">
@@ -18194,7 +18194,7 @@
         <v>321</v>
       </c>
       <c r="I609">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="610" spans="1:9">
@@ -18542,7 +18542,7 @@
         <v>1776</v>
       </c>
       <c r="I621">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="622" spans="1:9">
@@ -18571,7 +18571,7 @@
         <v>502</v>
       </c>
       <c r="I622">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="623" spans="1:9">
@@ -18600,7 +18600,7 @@
         <v>68</v>
       </c>
       <c r="I623">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="624" spans="1:9">
@@ -18861,7 +18861,7 @@
         <v>830</v>
       </c>
       <c r="I632">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="633" spans="1:9">
@@ -18890,7 +18890,7 @@
         <v>33</v>
       </c>
       <c r="I633">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="634" spans="1:9">
@@ -19499,7 +19499,7 @@
         <v>268</v>
       </c>
       <c r="I654">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="655" spans="1:9">
@@ -19557,7 +19557,7 @@
         <v>535</v>
       </c>
       <c r="I656">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="657" spans="1:9">
@@ -20282,7 +20282,7 @@
         <v>780</v>
       </c>
       <c r="I681">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="682" spans="1:9">
@@ -20340,7 +20340,7 @@
         <v>269</v>
       </c>
       <c r="I683">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="684" spans="1:9">
@@ -20659,7 +20659,7 @@
         <v>401</v>
       </c>
       <c r="I694">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="695" spans="1:9">
@@ -20775,7 +20775,7 @@
         <v>275</v>
       </c>
       <c r="I698">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="699" spans="1:9">
@@ -20888,10 +20888,10 @@
         <v>12</v>
       </c>
       <c r="H702">
-        <v>37778</v>
+        <v>37934</v>
       </c>
       <c r="I702">
-        <v>1334</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="703" spans="1:9">
@@ -20920,7 +20920,7 @@
         <v>683</v>
       </c>
       <c r="I703">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="704" spans="1:9">
@@ -20949,7 +20949,7 @@
         <v>12305</v>
       </c>
       <c r="I704">
-        <v>483</v>
+        <v>442</v>
       </c>
     </row>
     <row r="705" spans="1:9">
@@ -21007,7 +21007,7 @@
         <v>2605</v>
       </c>
       <c r="I706">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="707" spans="1:9">
@@ -21062,10 +21062,10 @@
         <v>5</v>
       </c>
       <c r="H708">
-        <v>13171</v>
+        <v>13106</v>
       </c>
       <c r="I708">
-        <v>574</v>
+        <v>527</v>
       </c>
     </row>
     <row r="709" spans="1:9">
@@ -21123,7 +21123,7 @@
         <v>25</v>
       </c>
       <c r="I710">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="711" spans="1:9">
@@ -21152,7 +21152,7 @@
         <v>3397</v>
       </c>
       <c r="I711">
-        <v>137</v>
+        <v>113</v>
       </c>
     </row>
     <row r="712" spans="1:9">
@@ -21210,7 +21210,7 @@
         <v>12852</v>
       </c>
       <c r="I713">
-        <v>447</v>
+        <v>396</v>
       </c>
     </row>
     <row r="714" spans="1:9">
@@ -21239,7 +21239,7 @@
         <v>7008</v>
       </c>
       <c r="I714">
-        <v>313</v>
+        <v>291</v>
       </c>
     </row>
     <row r="715" spans="1:9">
@@ -21268,7 +21268,7 @@
         <v>17270</v>
       </c>
       <c r="I715">
-        <v>554</v>
+        <v>519</v>
       </c>
     </row>
     <row r="716" spans="1:9">
@@ -21729,10 +21729,10 @@
         <v>9</v>
       </c>
       <c r="H731">
-        <v>2756</v>
+        <v>2672</v>
       </c>
       <c r="I731">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="732" spans="1:9">
@@ -21761,7 +21761,7 @@
         <v>220</v>
       </c>
       <c r="I732">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="733" spans="1:9">
@@ -21790,7 +21790,7 @@
         <v>3231</v>
       </c>
       <c r="I733">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="734" spans="1:9">
@@ -21848,7 +21848,7 @@
         <v>317</v>
       </c>
       <c r="I735">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="736" spans="1:9">
@@ -21877,7 +21877,7 @@
         <v>501</v>
       </c>
       <c r="I736">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="737" spans="1:9">
@@ -21906,7 +21906,7 @@
         <v>2791</v>
       </c>
       <c r="I737">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="738" spans="1:9">
@@ -22022,7 +22022,7 @@
         <v>98</v>
       </c>
       <c r="I741">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="742" spans="1:9">
@@ -22138,7 +22138,7 @@
         <v>3168</v>
       </c>
       <c r="I745">
-        <v>156</v>
+        <v>139</v>
       </c>
     </row>
     <row r="746" spans="1:9">
@@ -22370,7 +22370,7 @@
         <v>1039</v>
       </c>
       <c r="I753">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="754" spans="1:9">
@@ -22428,7 +22428,7 @@
         <v>730</v>
       </c>
       <c r="I755">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="756" spans="1:9">
@@ -22689,7 +22689,7 @@
         <v>587</v>
       </c>
       <c r="I764">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="765" spans="1:9">
@@ -24255,7 +24255,7 @@
         <v>1167</v>
       </c>
       <c r="I818">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="819" spans="1:9">
@@ -24313,7 +24313,7 @@
         <v>1036</v>
       </c>
       <c r="I820">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="821" spans="1:9">
@@ -24429,7 +24429,7 @@
         <v>548</v>
       </c>
       <c r="I824">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="825" spans="1:9">
@@ -24458,7 +24458,7 @@
         <v>317</v>
       </c>
       <c r="I825">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="826" spans="1:9">
@@ -24487,7 +24487,7 @@
         <v>312</v>
       </c>
       <c r="I826">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="827" spans="1:9">
@@ -24748,7 +24748,7 @@
         <v>407</v>
       </c>
       <c r="I835">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="836" spans="1:9">
@@ -25618,7 +25618,7 @@
         <v>6700</v>
       </c>
       <c r="I865">
-        <v>244</v>
+        <v>226</v>
       </c>
     </row>
     <row r="866" spans="1:9">
@@ -25676,7 +25676,7 @@
         <v>3391</v>
       </c>
       <c r="I867">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="868" spans="1:9">
@@ -25734,7 +25734,7 @@
         <v>767</v>
       </c>
       <c r="I869">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="870" spans="1:9">
@@ -25760,10 +25760,10 @@
         <v>5</v>
       </c>
       <c r="H870">
-        <v>3042</v>
+        <v>3107</v>
       </c>
       <c r="I870">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="871" spans="1:9">
@@ -25850,7 +25850,7 @@
         <v>158</v>
       </c>
       <c r="I873">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="874" spans="1:9">
@@ -25879,7 +25879,7 @@
         <v>577</v>
       </c>
       <c r="I874">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="875" spans="1:9">
@@ -25908,7 +25908,7 @@
         <v>2345</v>
       </c>
       <c r="I875">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="876" spans="1:9">
@@ -25966,7 +25966,7 @@
         <v>5307</v>
       </c>
       <c r="I877">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="878" spans="1:9">
@@ -26227,7 +26227,7 @@
         <v>165</v>
       </c>
       <c r="I886">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="887" spans="1:9">
@@ -26282,7 +26282,7 @@
         <v>8</v>
       </c>
       <c r="H888">
-        <v>637</v>
+        <v>721</v>
       </c>
       <c r="I888">
         <v>27</v>
@@ -26343,7 +26343,7 @@
         <v>475</v>
       </c>
       <c r="I890">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="891" spans="1:9">
@@ -26401,7 +26401,7 @@
         <v>318</v>
       </c>
       <c r="I892">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="893" spans="1:9">
@@ -26430,7 +26430,7 @@
         <v>245</v>
       </c>
       <c r="I893">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="894" spans="1:9">
@@ -26546,7 +26546,7 @@
         <v>95</v>
       </c>
       <c r="I897">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="898" spans="1:9">
@@ -26633,7 +26633,7 @@
         <v>263</v>
       </c>
       <c r="I900">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="901" spans="1:9">
@@ -27010,7 +27010,7 @@
         <v>291</v>
       </c>
       <c r="I913">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="914" spans="1:9">
@@ -28518,7 +28518,7 @@
         <v>48</v>
       </c>
       <c r="I965">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="966" spans="1:9">
@@ -28605,7 +28605,7 @@
         <v>60</v>
       </c>
       <c r="I968">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="969" spans="1:9">
@@ -29446,7 +29446,7 @@
         <v>324</v>
       </c>
       <c r="I997">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="998" spans="1:9">
@@ -29620,7 +29620,7 @@
         <v>77</v>
       </c>
       <c r="I1003">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1004" spans="1:9">

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4713" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4709" uniqueCount="55">
   <si>
     <t>Month</t>
   </si>
@@ -536,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1177"/>
+  <dimension ref="A1:I1176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -30162,13 +30162,13 @@
         <v>53</v>
       </c>
       <c r="E1022">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F1022">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G1022">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H1022">
         <v>0</v>
@@ -30220,13 +30220,13 @@
         <v>53</v>
       </c>
       <c r="E1024">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1024">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1024">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1024">
         <v>25</v>
@@ -30394,13 +30394,13 @@
         <v>53</v>
       </c>
       <c r="E1030">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F1030">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G1030">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H1030">
         <v>25</v>
@@ -30452,13 +30452,13 @@
         <v>53</v>
       </c>
       <c r="E1032">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F1032">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G1032">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H1032">
         <v>60</v>
@@ -30597,13 +30597,13 @@
         <v>53</v>
       </c>
       <c r="E1037">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F1037">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G1037">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H1037">
         <v>158</v>
@@ -30829,13 +30829,13 @@
         <v>53</v>
       </c>
       <c r="E1045">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F1045">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G1045">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H1045">
         <v>0</v>
@@ -31061,13 +31061,13 @@
         <v>53</v>
       </c>
       <c r="E1053">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F1053">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G1053">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H1053">
         <v>23</v>
@@ -31119,13 +31119,13 @@
         <v>53</v>
       </c>
       <c r="E1055">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F1055">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1055">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H1055">
         <v>19</v>
@@ -31409,13 +31409,13 @@
         <v>53</v>
       </c>
       <c r="E1065">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F1065">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1065">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1065">
         <v>0</v>
@@ -31641,13 +31641,13 @@
         <v>53</v>
       </c>
       <c r="E1073">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1073">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1073">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H1073">
         <v>15</v>
@@ -32708,7 +32708,7 @@
         <v>38</v>
       </c>
       <c r="C1110" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1110" t="s">
         <v>53</v>
@@ -32737,19 +32737,19 @@
         <v>38</v>
       </c>
       <c r="C1111" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1111" t="s">
         <v>53</v>
       </c>
       <c r="E1111">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1111">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1111">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1111">
         <v>0</v>
@@ -32769,16 +32769,16 @@
         <v>45</v>
       </c>
       <c r="D1112" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1112">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F1112">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1112">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H1112">
         <v>0</v>
@@ -32795,19 +32795,19 @@
         <v>38</v>
       </c>
       <c r="C1113" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D1113" t="s">
         <v>54</v>
       </c>
       <c r="E1113">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F1113">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G1113">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H1113">
         <v>0</v>
@@ -32824,10 +32824,10 @@
         <v>38</v>
       </c>
       <c r="C1114" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D1114" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1114">
         <v>1</v>
@@ -32856,16 +32856,16 @@
         <v>49</v>
       </c>
       <c r="D1115" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1115">
         <v>0</v>
@@ -32882,19 +32882,19 @@
         <v>38</v>
       </c>
       <c r="C1116" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1116" t="s">
         <v>54</v>
       </c>
       <c r="E1116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1116">
         <v>0</v>
@@ -32908,22 +32908,22 @@
         <v>24</v>
       </c>
       <c r="B1117" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C1117" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D1117" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1117">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F1117">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1117">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1117">
         <v>0</v>
@@ -32940,19 +32940,19 @@
         <v>33</v>
       </c>
       <c r="C1118" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1118" t="s">
         <v>53</v>
       </c>
       <c r="E1118">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F1118">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1118">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1118">
         <v>0</v>
@@ -32972,16 +32972,16 @@
         <v>42</v>
       </c>
       <c r="D1119" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1119">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F1119">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G1119">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H1119">
         <v>0</v>
@@ -32998,19 +32998,19 @@
         <v>33</v>
       </c>
       <c r="C1120" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1120" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1120">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F1120">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G1120">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H1120">
         <v>0</v>
@@ -33030,16 +33030,16 @@
         <v>43</v>
       </c>
       <c r="D1121" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1121">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F1121">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1121">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H1121">
         <v>0</v>
@@ -33056,19 +33056,19 @@
         <v>33</v>
       </c>
       <c r="C1122" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1122" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1122">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F1122">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1122">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H1122">
         <v>0</v>
@@ -33088,22 +33088,22 @@
         <v>44</v>
       </c>
       <c r="D1123" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1123">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F1123">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G1123">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H1123">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I1123">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1124" spans="1:9">
@@ -33114,25 +33114,25 @@
         <v>33</v>
       </c>
       <c r="C1124" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1124" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1124">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F1124">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="G1124">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="H1124">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I1124">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1125" spans="1:9">
@@ -33146,22 +33146,22 @@
         <v>45</v>
       </c>
       <c r="D1125" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1125">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="F1125">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="G1125">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="H1125">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="I1125">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1126" spans="1:9">
@@ -33172,25 +33172,25 @@
         <v>33</v>
       </c>
       <c r="C1126" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D1126" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1126">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="F1126">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="G1126">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H1126">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="I1126">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1127" spans="1:9">
@@ -33204,16 +33204,16 @@
         <v>46</v>
       </c>
       <c r="D1127" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1127">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F1127">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G1127">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H1127">
         <v>0</v>
@@ -33230,25 +33230,25 @@
         <v>33</v>
       </c>
       <c r="C1128" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D1128" t="s">
         <v>54</v>
       </c>
       <c r="E1128">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F1128">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="G1128">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="H1128">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I1128">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1129" spans="1:9">
@@ -33259,25 +33259,25 @@
         <v>33</v>
       </c>
       <c r="C1129" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D1129" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1129">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1129">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1129">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1129">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I1129">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1130" spans="1:9">
@@ -33291,16 +33291,16 @@
         <v>48</v>
       </c>
       <c r="D1130" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1130">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F1130">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G1130">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H1130">
         <v>0</v>
@@ -33317,25 +33317,25 @@
         <v>33</v>
       </c>
       <c r="C1131" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D1131" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1131">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F1131">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="G1131">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="H1131">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I1131">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1132" spans="1:9">
@@ -33349,22 +33349,22 @@
         <v>49</v>
       </c>
       <c r="D1132" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1132">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F1132">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G1132">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H1132">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I1132">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1133" spans="1:9">
@@ -33375,19 +33375,19 @@
         <v>33</v>
       </c>
       <c r="C1133" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1133" t="s">
         <v>54</v>
       </c>
       <c r="E1133">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="F1133">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="G1133">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="H1133">
         <v>0</v>
@@ -33404,19 +33404,19 @@
         <v>33</v>
       </c>
       <c r="C1134" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D1134" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1134">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F1134">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1134">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1134">
         <v>0</v>
@@ -33436,16 +33436,16 @@
         <v>50</v>
       </c>
       <c r="D1135" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1135">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F1135">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G1135">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H1135">
         <v>0</v>
@@ -33459,22 +33459,22 @@
         <v>24</v>
       </c>
       <c r="B1136" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1136" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D1136" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1136">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F1136">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G1136">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H1136">
         <v>0</v>
@@ -33494,16 +33494,16 @@
         <v>41</v>
       </c>
       <c r="D1137" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1137">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F1137">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1137">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H1137">
         <v>0</v>
@@ -33520,19 +33520,19 @@
         <v>34</v>
       </c>
       <c r="C1138" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D1138" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1138">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1138">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1138">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H1138">
         <v>0</v>
@@ -33549,19 +33549,19 @@
         <v>34</v>
       </c>
       <c r="C1139" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1139" t="s">
         <v>53</v>
       </c>
       <c r="E1139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1139">
         <v>0</v>
@@ -33581,22 +33581,22 @@
         <v>44</v>
       </c>
       <c r="D1140" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1140">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F1140">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1140">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1140">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I1140">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1141" spans="1:9">
@@ -33607,25 +33607,25 @@
         <v>34</v>
       </c>
       <c r="C1141" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1141" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1141">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1141">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1141">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1141">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I1141">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1142" spans="1:9">
@@ -33639,22 +33639,22 @@
         <v>45</v>
       </c>
       <c r="D1142" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1142">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F1142">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1142">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1142">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I1142">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1143" spans="1:9">
@@ -33665,25 +33665,25 @@
         <v>34</v>
       </c>
       <c r="C1143" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D1143" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1143">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F1143">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1143">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1143">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I1143">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1144" spans="1:9">
@@ -33697,7 +33697,7 @@
         <v>46</v>
       </c>
       <c r="D1144" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1144">
         <v>3</v>
@@ -33723,10 +33723,10 @@
         <v>34</v>
       </c>
       <c r="C1145" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D1145" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1145">
         <v>3</v>
@@ -33755,16 +33755,16 @@
         <v>49</v>
       </c>
       <c r="D1146" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F1146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1146">
         <v>0</v>
@@ -33781,19 +33781,19 @@
         <v>34</v>
       </c>
       <c r="C1147" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1147" t="s">
         <v>54</v>
       </c>
       <c r="E1147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1147">
         <v>0</v>
@@ -33810,25 +33810,25 @@
         <v>34</v>
       </c>
       <c r="C1148" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D1148" t="s">
         <v>54</v>
       </c>
       <c r="E1148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1148">
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="I1148">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1149" spans="1:9">
@@ -33836,10 +33836,10 @@
         <v>24</v>
       </c>
       <c r="B1149" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C1149" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D1149" t="s">
         <v>54</v>
@@ -33854,10 +33854,10 @@
         <v>1</v>
       </c>
       <c r="H1149">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="I1149">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1150" spans="1:9">
@@ -33868,19 +33868,19 @@
         <v>40</v>
       </c>
       <c r="C1150" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1150" t="s">
         <v>54</v>
       </c>
       <c r="E1150">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F1150">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1150">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1150">
         <v>0</v>
@@ -33897,19 +33897,19 @@
         <v>40</v>
       </c>
       <c r="C1151" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D1151" t="s">
         <v>54</v>
       </c>
       <c r="E1151">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F1151">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1151">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1151">
         <v>0</v>
@@ -33926,7 +33926,7 @@
         <v>40</v>
       </c>
       <c r="C1152" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D1152" t="s">
         <v>54</v>
@@ -33955,7 +33955,7 @@
         <v>40</v>
       </c>
       <c r="C1153" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D1153" t="s">
         <v>54</v>
@@ -33981,22 +33981,22 @@
         <v>24</v>
       </c>
       <c r="B1154" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C1154" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D1154" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1154">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1154">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1154">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H1154">
         <v>0</v>
@@ -34016,16 +34016,16 @@
         <v>41</v>
       </c>
       <c r="D1155" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1155">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F1155">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G1155">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H1155">
         <v>0</v>
@@ -34042,19 +34042,19 @@
         <v>31</v>
       </c>
       <c r="C1156" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1156" t="s">
         <v>54</v>
       </c>
       <c r="E1156">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F1156">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G1156">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H1156">
         <v>0</v>
@@ -34071,25 +34071,25 @@
         <v>31</v>
       </c>
       <c r="C1157" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1157" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1157">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F1157">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1157">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1157">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I1157">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1158" spans="1:9">
@@ -34103,22 +34103,22 @@
         <v>43</v>
       </c>
       <c r="D1158" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1158">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F1158">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G1158">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H1158">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I1158">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1159" spans="1:9">
@@ -34129,25 +34129,25 @@
         <v>31</v>
       </c>
       <c r="C1159" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1159" t="s">
         <v>54</v>
       </c>
       <c r="E1159">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F1159">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G1159">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H1159">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="I1159">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1160" spans="1:9">
@@ -34158,25 +34158,25 @@
         <v>31</v>
       </c>
       <c r="C1160" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1160" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1160">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F1160">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="G1160">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="H1160">
-        <v>324</v>
+        <v>19</v>
       </c>
       <c r="I1160">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1161" spans="1:9">
@@ -34190,22 +34190,22 @@
         <v>45</v>
       </c>
       <c r="D1161" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1161">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="F1161">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G1161">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H1161">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="I1161">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1162" spans="1:9">
@@ -34216,10 +34216,10 @@
         <v>31</v>
       </c>
       <c r="C1162" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D1162" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1162">
         <v>42</v>
@@ -34231,10 +34231,10 @@
         <v>42</v>
       </c>
       <c r="H1162">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="I1162">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1163" spans="1:9">
@@ -34248,22 +34248,22 @@
         <v>46</v>
       </c>
       <c r="D1163" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1163">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F1163">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G1163">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H1163">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I1163">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1164" spans="1:9">
@@ -34274,25 +34274,25 @@
         <v>31</v>
       </c>
       <c r="C1164" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D1164" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1164">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F1164">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="G1164">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H1164">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I1164">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1165" spans="1:9">
@@ -34306,7 +34306,7 @@
         <v>47</v>
       </c>
       <c r="D1165" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1165">
         <v>1</v>
@@ -34318,10 +34318,10 @@
         <v>1</v>
       </c>
       <c r="H1165">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I1165">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1166" spans="1:9">
@@ -34332,25 +34332,25 @@
         <v>31</v>
       </c>
       <c r="C1166" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D1166" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1166">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1166">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1166">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1166">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="I1166">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1167" spans="1:9">
@@ -34364,16 +34364,16 @@
         <v>48</v>
       </c>
       <c r="D1167" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1167">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F1167">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1167">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H1167">
         <v>0</v>
@@ -34390,25 +34390,25 @@
         <v>31</v>
       </c>
       <c r="C1168" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D1168" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1168">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F1168">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="G1168">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H1168">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I1168">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1169" spans="1:9">
@@ -34422,19 +34422,19 @@
         <v>49</v>
       </c>
       <c r="D1169" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1169">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F1169">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G1169">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H1169">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1169">
         <v>1</v>
@@ -34448,25 +34448,25 @@
         <v>31</v>
       </c>
       <c r="C1170" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1170" t="s">
         <v>54</v>
       </c>
       <c r="E1170">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F1170">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G1170">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H1170">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="I1170">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1171" spans="1:9">
@@ -34477,25 +34477,25 @@
         <v>31</v>
       </c>
       <c r="C1171" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D1171" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1171">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1171">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1171">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H1171">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I1171">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1172" spans="1:9">
@@ -34509,22 +34509,22 @@
         <v>50</v>
       </c>
       <c r="D1172" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1172">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F1172">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1172">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H1172">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="I1172">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1173" spans="1:9">
@@ -34532,28 +34532,28 @@
         <v>24</v>
       </c>
       <c r="B1173" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C1173" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D1173" t="s">
         <v>54</v>
       </c>
       <c r="E1173">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F1173">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G1173">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H1173">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="I1173">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1174" spans="1:9">
@@ -34564,7 +34564,7 @@
         <v>27</v>
       </c>
       <c r="C1174" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D1174" t="s">
         <v>54</v>
@@ -34593,7 +34593,7 @@
         <v>27</v>
       </c>
       <c r="C1175" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D1175" t="s">
         <v>54</v>
@@ -34622,7 +34622,7 @@
         <v>27</v>
       </c>
       <c r="C1176" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D1176" t="s">
         <v>54</v>
@@ -34640,35 +34640,6 @@
         <v>0</v>
       </c>
       <c r="I1176">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1177" spans="1:9">
-      <c r="A1177" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1177" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1177" t="s">
-        <v>50</v>
-      </c>
-      <c r="D1177" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1177">
-        <v>1</v>
-      </c>
-      <c r="F1177">
-        <v>1</v>
-      </c>
-      <c r="G1177">
-        <v>1</v>
-      </c>
-      <c r="H1177">
-        <v>0</v>
-      </c>
-      <c r="I1177">
         <v>0</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4681" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4689" uniqueCount="55">
   <si>
     <t>Month</t>
   </si>
@@ -536,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1169"/>
+  <dimension ref="A1:I1171"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -29147,13 +29147,13 @@
         <v>53</v>
       </c>
       <c r="E987">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F987">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G987">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H987">
         <v>0</v>
@@ -29205,13 +29205,13 @@
         <v>53</v>
       </c>
       <c r="E989">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F989">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G989">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H989">
         <v>0</v>
@@ -29408,13 +29408,13 @@
         <v>53</v>
       </c>
       <c r="E996">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F996">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G996">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H996">
         <v>0</v>
@@ -29640,13 +29640,13 @@
         <v>53</v>
       </c>
       <c r="E1004">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1004">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1004">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H1004">
         <v>0</v>
@@ -29814,13 +29814,13 @@
         <v>53</v>
       </c>
       <c r="E1010">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="F1010">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="G1010">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="H1010">
         <v>0</v>
@@ -29872,13 +29872,13 @@
         <v>53</v>
       </c>
       <c r="E1012">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F1012">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G1012">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H1012">
         <v>25</v>
@@ -29930,13 +29930,13 @@
         <v>53</v>
       </c>
       <c r="E1014">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1014">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1014">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H1014">
         <v>0</v>
@@ -30046,13 +30046,13 @@
         <v>53</v>
       </c>
       <c r="E1018">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F1018">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G1018">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H1018">
         <v>59</v>
@@ -30104,13 +30104,13 @@
         <v>53</v>
       </c>
       <c r="E1020">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F1020">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G1020">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H1020">
         <v>80</v>
@@ -30249,13 +30249,13 @@
         <v>53</v>
       </c>
       <c r="E1025">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F1025">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G1025">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H1025">
         <v>157</v>
@@ -30481,13 +30481,13 @@
         <v>53</v>
       </c>
       <c r="E1033">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F1033">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G1033">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H1033">
         <v>0</v>
@@ -30539,13 +30539,13 @@
         <v>53</v>
       </c>
       <c r="E1035">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F1035">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1035">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1035">
         <v>0</v>
@@ -30597,13 +30597,13 @@
         <v>53</v>
       </c>
       <c r="E1037">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1037">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1037">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1037">
         <v>0</v>
@@ -30713,13 +30713,13 @@
         <v>53</v>
       </c>
       <c r="E1041">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F1041">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G1041">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H1041">
         <v>23</v>
@@ -30771,13 +30771,13 @@
         <v>53</v>
       </c>
       <c r="E1043">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F1043">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G1043">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H1043">
         <v>19</v>
@@ -30916,13 +30916,13 @@
         <v>53</v>
       </c>
       <c r="E1048">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F1048">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G1048">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H1048">
         <v>0</v>
@@ -31061,13 +31061,13 @@
         <v>53</v>
       </c>
       <c r="E1053">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F1053">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G1053">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H1053">
         <v>0</v>
@@ -31119,13 +31119,13 @@
         <v>53</v>
       </c>
       <c r="E1055">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F1055">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1055">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1055">
         <v>0</v>
@@ -31351,13 +31351,13 @@
         <v>53</v>
       </c>
       <c r="E1063">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F1063">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G1063">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H1063">
         <v>0</v>
@@ -31496,13 +31496,13 @@
         <v>53</v>
       </c>
       <c r="E1068">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F1068">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1068">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H1068">
         <v>0</v>
@@ -32598,13 +32598,13 @@
         <v>53</v>
       </c>
       <c r="E1106">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F1106">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1106">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H1106">
         <v>0</v>
@@ -32656,13 +32656,13 @@
         <v>53</v>
       </c>
       <c r="E1108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1108">
         <v>0</v>
@@ -32888,13 +32888,13 @@
         <v>53</v>
       </c>
       <c r="E1116">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F1116">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G1116">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H1116">
         <v>14</v>
@@ -33033,13 +33033,13 @@
         <v>53</v>
       </c>
       <c r="E1121">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F1121">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1121">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1121">
         <v>60</v>
@@ -33207,13 +33207,13 @@
         <v>53</v>
       </c>
       <c r="E1127">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1127">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1127">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1127">
         <v>0</v>
@@ -33259,19 +33259,19 @@
         <v>33</v>
       </c>
       <c r="C1129" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D1129" t="s">
         <v>53</v>
       </c>
       <c r="E1129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1129">
         <v>0</v>
@@ -33288,19 +33288,19 @@
         <v>33</v>
       </c>
       <c r="C1130" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D1130" t="s">
         <v>53</v>
       </c>
       <c r="E1130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1130">
         <v>0</v>
@@ -33320,22 +33320,22 @@
         <v>44</v>
       </c>
       <c r="D1131" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1131">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F1131">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1131">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H1131">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I1131">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1132" spans="1:9">
@@ -33346,10 +33346,10 @@
         <v>33</v>
       </c>
       <c r="C1132" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D1132" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1132">
         <v>4</v>
@@ -33361,10 +33361,10 @@
         <v>4</v>
       </c>
       <c r="H1132">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I1132">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1133" spans="1:9">
@@ -33378,22 +33378,22 @@
         <v>45</v>
       </c>
       <c r="D1133" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1133">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F1133">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1133">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1133">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I1133">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1134" spans="1:9">
@@ -33404,25 +33404,25 @@
         <v>33</v>
       </c>
       <c r="C1134" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D1134" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1134">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F1134">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1134">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1134">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I1134">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1135" spans="1:9">
@@ -33436,16 +33436,16 @@
         <v>46</v>
       </c>
       <c r="D1135" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1135">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1135">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1135">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1135">
         <v>0</v>
@@ -33462,10 +33462,10 @@
         <v>33</v>
       </c>
       <c r="C1136" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D1136" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1136">
         <v>3</v>
@@ -33494,16 +33494,16 @@
         <v>49</v>
       </c>
       <c r="D1137" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1137">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F1137">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1137">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1137">
         <v>0</v>
@@ -33520,19 +33520,19 @@
         <v>33</v>
       </c>
       <c r="C1138" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D1138" t="s">
         <v>54</v>
       </c>
       <c r="E1138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1138">
         <v>0</v>
@@ -33549,25 +33549,25 @@
         <v>33</v>
       </c>
       <c r="C1139" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D1139" t="s">
         <v>54</v>
       </c>
       <c r="E1139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1139">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="I1139">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1140" spans="1:9">
@@ -33575,10 +33575,10 @@
         <v>24</v>
       </c>
       <c r="B1140" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C1140" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D1140" t="s">
         <v>54</v>
@@ -33593,10 +33593,10 @@
         <v>1</v>
       </c>
       <c r="H1140">
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="I1140">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1141" spans="1:9">
@@ -33607,19 +33607,19 @@
         <v>40</v>
       </c>
       <c r="C1141" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D1141" t="s">
         <v>54</v>
       </c>
       <c r="E1141">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F1141">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1141">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1141">
         <v>0</v>
@@ -33636,19 +33636,19 @@
         <v>40</v>
       </c>
       <c r="C1142" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D1142" t="s">
         <v>54</v>
       </c>
       <c r="E1142">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F1142">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1142">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1142">
         <v>0</v>
@@ -33665,7 +33665,7 @@
         <v>40</v>
       </c>
       <c r="C1143" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D1143" t="s">
         <v>54</v>
@@ -33694,7 +33694,7 @@
         <v>40</v>
       </c>
       <c r="C1144" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D1144" t="s">
         <v>54</v>
@@ -33720,22 +33720,22 @@
         <v>24</v>
       </c>
       <c r="B1145" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C1145" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D1145" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1145">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F1145">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G1145">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H1145">
         <v>0</v>
@@ -33755,16 +33755,16 @@
         <v>41</v>
       </c>
       <c r="D1146" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1146">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F1146">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1146">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1146">
         <v>0</v>
@@ -33781,19 +33781,19 @@
         <v>30</v>
       </c>
       <c r="C1147" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D1147" t="s">
         <v>54</v>
       </c>
       <c r="E1147">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F1147">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1147">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H1147">
         <v>0</v>
@@ -33810,25 +33810,25 @@
         <v>30</v>
       </c>
       <c r="C1148" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D1148" t="s">
         <v>53</v>
       </c>
       <c r="E1148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F1148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1148">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I1148">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1149" spans="1:9">
@@ -33839,19 +33839,19 @@
         <v>30</v>
       </c>
       <c r="C1149" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D1149" t="s">
         <v>54</v>
       </c>
       <c r="E1149">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F1149">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G1149">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H1149">
         <v>0</v>
@@ -33868,25 +33868,25 @@
         <v>30</v>
       </c>
       <c r="C1150" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D1150" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1150">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F1150">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1150">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1150">
-        <v>324</v>
+        <v>19</v>
       </c>
       <c r="I1150">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1151" spans="1:9">
@@ -33897,19 +33897,19 @@
         <v>30</v>
       </c>
       <c r="C1151" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D1151" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1151">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F1151">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="G1151">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H1151">
         <v>0</v>
@@ -33926,25 +33926,25 @@
         <v>30</v>
       </c>
       <c r="C1152" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D1152" t="s">
         <v>54</v>
       </c>
       <c r="E1152">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="F1152">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="G1152">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H1152">
-        <v>145</v>
+        <v>324</v>
       </c>
       <c r="I1152">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1153" spans="1:9">
@@ -33955,25 +33955,25 @@
         <v>30</v>
       </c>
       <c r="C1153" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D1153" t="s">
         <v>53</v>
       </c>
       <c r="E1153">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F1153">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G1153">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H1153">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I1153">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1154" spans="1:9">
@@ -33984,25 +33984,25 @@
         <v>30</v>
       </c>
       <c r="C1154" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D1154" t="s">
         <v>54</v>
       </c>
       <c r="E1154">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F1154">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G1154">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H1154">
-        <v>40</v>
+        <v>145</v>
       </c>
       <c r="I1154">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1155" spans="1:9">
@@ -34013,25 +34013,25 @@
         <v>30</v>
       </c>
       <c r="C1155" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1155" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1155">
         <v>47</v>
       </c>
-      <c r="D1155" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1155">
-        <v>1</v>
-      </c>
       <c r="F1155">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="G1155">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="H1155">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I1155">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1156" spans="1:9">
@@ -34042,25 +34042,25 @@
         <v>30</v>
       </c>
       <c r="C1156" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D1156" t="s">
         <v>54</v>
       </c>
       <c r="E1156">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F1156">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="G1156">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="H1156">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="I1156">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1157" spans="1:9">
@@ -34071,19 +34071,19 @@
         <v>30</v>
       </c>
       <c r="C1157" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D1157" t="s">
         <v>53</v>
       </c>
       <c r="E1157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1157">
         <v>0</v>
@@ -34100,25 +34100,25 @@
         <v>30</v>
       </c>
       <c r="C1158" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D1158" t="s">
         <v>54</v>
       </c>
       <c r="E1158">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F1158">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G1158">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H1158">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I1158">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1159" spans="1:9">
@@ -34129,25 +34129,25 @@
         <v>30</v>
       </c>
       <c r="C1159" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D1159" t="s">
         <v>53</v>
       </c>
       <c r="E1159">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="F1159">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G1159">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="H1159">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I1159">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1160" spans="1:9">
@@ -34158,25 +34158,25 @@
         <v>30</v>
       </c>
       <c r="C1160" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D1160" t="s">
         <v>54</v>
       </c>
       <c r="E1160">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="F1160">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G1160">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="H1160">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I1160">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1161" spans="1:9">
@@ -34187,25 +34187,25 @@
         <v>30</v>
       </c>
       <c r="C1161" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D1161" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1161">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F1161">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G1161">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H1161">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="I1161">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1162" spans="1:9">
@@ -34216,25 +34216,25 @@
         <v>30</v>
       </c>
       <c r="C1162" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D1162" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1162">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="F1162">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G1162">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="H1162">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I1162">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1163" spans="1:9">
@@ -34245,25 +34245,25 @@
         <v>30</v>
       </c>
       <c r="C1163" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D1163" t="s">
         <v>54</v>
       </c>
       <c r="E1163">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F1163">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G1163">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H1163">
-        <v>148</v>
+        <v>40</v>
       </c>
       <c r="I1163">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1164" spans="1:9">
@@ -34271,22 +34271,22 @@
         <v>24</v>
       </c>
       <c r="B1164" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C1164" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D1164" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E1164">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F1164">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1164">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H1164">
         <v>0</v>
@@ -34300,28 +34300,28 @@
         <v>24</v>
       </c>
       <c r="B1165" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C1165" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D1165" t="s">
         <v>54</v>
       </c>
       <c r="E1165">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F1165">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G1165">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H1165">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="I1165">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1166" spans="1:9">
@@ -34332,7 +34332,7 @@
         <v>27</v>
       </c>
       <c r="C1166" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D1166" t="s">
         <v>54</v>
@@ -34361,7 +34361,7 @@
         <v>27</v>
       </c>
       <c r="C1167" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D1167" t="s">
         <v>54</v>
@@ -34390,19 +34390,19 @@
         <v>27</v>
       </c>
       <c r="C1168" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D1168" t="s">
         <v>54</v>
       </c>
       <c r="E1168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1168">
         <v>0</v>
@@ -34419,24 +34419,82 @@
         <v>27</v>
       </c>
       <c r="C1169" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1169" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1169">
+        <v>1</v>
+      </c>
+      <c r="F1169">
+        <v>1</v>
+      </c>
+      <c r="G1169">
+        <v>1</v>
+      </c>
+      <c r="H1169">
+        <v>0</v>
+      </c>
+      <c r="I1169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:9">
+      <c r="A1170" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1170" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1170" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1170" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1170">
+        <v>1</v>
+      </c>
+      <c r="F1170">
+        <v>1</v>
+      </c>
+      <c r="G1170">
+        <v>1</v>
+      </c>
+      <c r="H1170">
+        <v>0</v>
+      </c>
+      <c r="I1170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:9">
+      <c r="A1171" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1171" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1171" t="s">
         <v>50</v>
       </c>
-      <c r="D1169" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1169">
-        <v>1</v>
-      </c>
-      <c r="F1169">
-        <v>1</v>
-      </c>
-      <c r="G1169">
-        <v>1</v>
-      </c>
-      <c r="H1169">
-        <v>0</v>
-      </c>
-      <c r="I1169">
+      <c r="D1171" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1171">
+        <v>1</v>
+      </c>
+      <c r="F1171">
+        <v>1</v>
+      </c>
+      <c r="G1171">
+        <v>1</v>
+      </c>
+      <c r="H1171">
+        <v>0</v>
+      </c>
+      <c r="I1171">
         <v>0</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4725" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4729" uniqueCount="55">
   <si>
     <t>Month</t>
   </si>
@@ -536,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1180"/>
+  <dimension ref="A1:I1181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -18803,10 +18803,10 @@
         <v>19</v>
       </c>
       <c r="H630">
-        <v>11722</v>
+        <v>12121</v>
       </c>
       <c r="I630">
-        <v>368</v>
+        <v>383</v>
       </c>
     </row>
     <row r="631" spans="1:9">
@@ -19296,10 +19296,10 @@
         <v>0</v>
       </c>
       <c r="H647">
-        <v>623</v>
+        <v>722</v>
       </c>
       <c r="I647">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="648" spans="1:9">
@@ -19557,10 +19557,10 @@
         <v>2</v>
       </c>
       <c r="H656">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="I656">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="657" spans="1:9">
@@ -21453,7 +21453,7 @@
         <v>22</v>
       </c>
       <c r="B722" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C722" t="s">
         <v>45</v>
@@ -21482,28 +21482,28 @@
         <v>22</v>
       </c>
       <c r="B723" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C723" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D723" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E723">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F723">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G723">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H723">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I723">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="724" spans="1:9">
@@ -21517,22 +21517,22 @@
         <v>41</v>
       </c>
       <c r="D724" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E724">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F724">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G724">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H724">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="I724">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="725" spans="1:9">
@@ -21543,25 +21543,25 @@
         <v>25</v>
       </c>
       <c r="C725" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D725" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E725">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F725">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G725">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H725">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="I725">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="726" spans="1:9">
@@ -21575,22 +21575,22 @@
         <v>42</v>
       </c>
       <c r="D726" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E726">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="F726">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="G726">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H726">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="I726">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="727" spans="1:9">
@@ -21601,25 +21601,25 @@
         <v>25</v>
       </c>
       <c r="C727" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D727" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E727">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="F727">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="G727">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="H727">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="I727">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="728" spans="1:9">
@@ -21633,22 +21633,22 @@
         <v>43</v>
       </c>
       <c r="D728" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E728">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F728">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G728">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H728">
-        <v>15</v>
+        <v>165</v>
       </c>
       <c r="I728">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="729" spans="1:9">
@@ -21659,25 +21659,25 @@
         <v>25</v>
       </c>
       <c r="C729" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D729" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E729">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F729">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G729">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H729">
-        <v>167</v>
+        <v>229</v>
       </c>
       <c r="I729">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="730" spans="1:9">
@@ -21691,22 +21691,22 @@
         <v>44</v>
       </c>
       <c r="D730" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E730">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F730">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G730">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="H730">
-        <v>229</v>
+        <v>30807</v>
       </c>
       <c r="I730">
-        <v>6</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="731" spans="1:9">
@@ -21717,25 +21717,25 @@
         <v>25</v>
       </c>
       <c r="C731" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D731" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E731">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="F731">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="G731">
-        <v>44</v>
+        <v>127</v>
       </c>
       <c r="H731">
-        <v>33702</v>
+        <v>1795</v>
       </c>
       <c r="I731">
-        <v>1312</v>
+        <v>74</v>
       </c>
     </row>
     <row r="732" spans="1:9">
@@ -21749,22 +21749,22 @@
         <v>45</v>
       </c>
       <c r="D732" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E732">
-        <v>119</v>
+        <v>221</v>
       </c>
       <c r="F732">
-        <v>127</v>
+        <v>258</v>
       </c>
       <c r="G732">
-        <v>127</v>
+        <v>259</v>
       </c>
       <c r="H732">
-        <v>2034</v>
+        <v>15446</v>
       </c>
       <c r="I732">
-        <v>80</v>
+        <v>688</v>
       </c>
     </row>
     <row r="733" spans="1:9">
@@ -21775,25 +21775,25 @@
         <v>25</v>
       </c>
       <c r="C733" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D733" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E733">
-        <v>221</v>
+        <v>75</v>
       </c>
       <c r="F733">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="G733">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="H733">
-        <v>17717</v>
+        <v>292</v>
       </c>
       <c r="I733">
-        <v>837</v>
+        <v>12</v>
       </c>
     </row>
     <row r="734" spans="1:9">
@@ -21807,22 +21807,22 @@
         <v>46</v>
       </c>
       <c r="D734" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E734">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F734">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G734">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H734">
-        <v>292</v>
+        <v>1087</v>
       </c>
       <c r="I734">
-        <v>11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="735" spans="1:9">
@@ -21833,25 +21833,25 @@
         <v>25</v>
       </c>
       <c r="C735" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D735" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E735">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="F735">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="G735">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="H735">
-        <v>1281</v>
+        <v>741</v>
       </c>
       <c r="I735">
-        <v>59</v>
+        <v>19</v>
       </c>
     </row>
     <row r="736" spans="1:9">
@@ -21865,22 +21865,22 @@
         <v>47</v>
       </c>
       <c r="D736" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E736">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F736">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G736">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H736">
-        <v>885</v>
+        <v>8589</v>
       </c>
       <c r="I736">
-        <v>24</v>
+        <v>331</v>
       </c>
     </row>
     <row r="737" spans="1:9">
@@ -21891,25 +21891,25 @@
         <v>25</v>
       </c>
       <c r="C737" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D737" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E737">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F737">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G737">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H737">
-        <v>10275</v>
+        <v>50</v>
       </c>
       <c r="I737">
-        <v>391</v>
+        <v>2</v>
       </c>
     </row>
     <row r="738" spans="1:9">
@@ -21923,22 +21923,22 @@
         <v>48</v>
       </c>
       <c r="D738" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E738">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F738">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G738">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H738">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I738">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="739" spans="1:9">
@@ -21949,25 +21949,25 @@
         <v>25</v>
       </c>
       <c r="C739" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D739" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E739">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="F739">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="G739">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="H739">
-        <v>0</v>
+        <v>965</v>
       </c>
       <c r="I739">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="740" spans="1:9">
@@ -21981,22 +21981,22 @@
         <v>49</v>
       </c>
       <c r="D740" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E740">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="F740">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="G740">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="H740">
-        <v>976</v>
+        <v>2668</v>
       </c>
       <c r="I740">
-        <v>36</v>
+        <v>95</v>
       </c>
     </row>
     <row r="741" spans="1:9">
@@ -22007,25 +22007,25 @@
         <v>25</v>
       </c>
       <c r="C741" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D741" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E741">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="F741">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="G741">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="H741">
-        <v>2730</v>
+        <v>0</v>
       </c>
       <c r="I741">
-        <v>94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="742" spans="1:9">
@@ -22039,22 +22039,22 @@
         <v>51</v>
       </c>
       <c r="D742" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E742">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F742">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G742">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H742">
-        <v>0</v>
+        <v>8475</v>
       </c>
       <c r="I742">
-        <v>0</v>
+        <v>308</v>
       </c>
     </row>
     <row r="743" spans="1:9">
@@ -22065,25 +22065,25 @@
         <v>25</v>
       </c>
       <c r="C743" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D743" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E743">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F743">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G743">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H743">
-        <v>9321</v>
+        <v>2627</v>
       </c>
       <c r="I743">
-        <v>341</v>
+        <v>90</v>
       </c>
     </row>
     <row r="744" spans="1:9">
@@ -22097,22 +22097,22 @@
         <v>50</v>
       </c>
       <c r="D744" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E744">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="F744">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="G744">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="H744">
-        <v>2808</v>
+        <v>6249</v>
       </c>
       <c r="I744">
-        <v>94</v>
+        <v>241</v>
       </c>
     </row>
     <row r="745" spans="1:9">
@@ -22120,28 +22120,28 @@
         <v>22</v>
       </c>
       <c r="B745" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C745" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D745" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E745">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="F745">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="G745">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="H745">
-        <v>6768</v>
+        <v>0</v>
       </c>
       <c r="I745">
-        <v>266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="746" spans="1:9">
@@ -22152,19 +22152,19 @@
         <v>26</v>
       </c>
       <c r="C746" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D746" t="s">
         <v>53</v>
       </c>
       <c r="E746">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F746">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G746">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H746">
         <v>0</v>
@@ -22184,16 +22184,16 @@
         <v>42</v>
       </c>
       <c r="D747" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E747">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F747">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G747">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H747">
         <v>0</v>
@@ -22210,25 +22210,25 @@
         <v>26</v>
       </c>
       <c r="C748" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D748" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E748">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F748">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G748">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H748">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I748">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="749" spans="1:9">
@@ -22242,22 +22242,22 @@
         <v>43</v>
       </c>
       <c r="D749" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E749">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F749">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G749">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H749">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I749">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="750" spans="1:9">
@@ -22268,25 +22268,25 @@
         <v>26</v>
       </c>
       <c r="C750" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D750" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E750">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F750">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G750">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H750">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I750">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="751" spans="1:9">
@@ -22300,22 +22300,22 @@
         <v>44</v>
       </c>
       <c r="D751" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E751">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F751">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G751">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H751">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="I751">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="752" spans="1:9">
@@ -22326,25 +22326,25 @@
         <v>26</v>
       </c>
       <c r="C752" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D752" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E752">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="F752">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="G752">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="H752">
-        <v>474</v>
+        <v>343</v>
       </c>
       <c r="I752">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="753" spans="1:9">
@@ -22358,22 +22358,22 @@
         <v>45</v>
       </c>
       <c r="D753" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E753">
-        <v>65</v>
+        <v>153</v>
       </c>
       <c r="F753">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="G753">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="H753">
-        <v>363</v>
+        <v>246</v>
       </c>
       <c r="I753">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="754" spans="1:9">
@@ -22384,25 +22384,25 @@
         <v>26</v>
       </c>
       <c r="C754" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D754" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E754">
-        <v>153</v>
+        <v>65</v>
       </c>
       <c r="F754">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="G754">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="H754">
-        <v>249</v>
+        <v>67</v>
       </c>
       <c r="I754">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="755" spans="1:9">
@@ -22416,22 +22416,22 @@
         <v>46</v>
       </c>
       <c r="D755" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E755">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F755">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G755">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="H755">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="I755">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="756" spans="1:9">
@@ -22442,25 +22442,25 @@
         <v>26</v>
       </c>
       <c r="C756" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D756" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E756">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="F756">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="G756">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="H756">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="I756">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="757" spans="1:9">
@@ -22474,22 +22474,22 @@
         <v>47</v>
       </c>
       <c r="D757" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E757">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F757">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G757">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H757">
-        <v>145</v>
+        <v>361</v>
       </c>
       <c r="I757">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="758" spans="1:9">
@@ -22500,25 +22500,25 @@
         <v>26</v>
       </c>
       <c r="C758" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D758" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E758">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F758">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G758">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H758">
-        <v>418</v>
+        <v>43</v>
       </c>
       <c r="I758">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="759" spans="1:9">
@@ -22532,7 +22532,7 @@
         <v>48</v>
       </c>
       <c r="D759" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E759">
         <v>7</v>
@@ -22544,10 +22544,10 @@
         <v>7</v>
       </c>
       <c r="H759">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="I759">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="760" spans="1:9">
@@ -22558,25 +22558,25 @@
         <v>26</v>
       </c>
       <c r="C760" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D760" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E760">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="F760">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="G760">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H760">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="I760">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="761" spans="1:9">
@@ -22590,22 +22590,22 @@
         <v>49</v>
       </c>
       <c r="D761" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E761">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F761">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G761">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H761">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="I761">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="762" spans="1:9">
@@ -22616,19 +22616,19 @@
         <v>26</v>
       </c>
       <c r="C762" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D762" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E762">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="F762">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="G762">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="H762">
         <v>0</v>
@@ -22648,16 +22648,16 @@
         <v>51</v>
       </c>
       <c r="D763" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E763">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F763">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G763">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H763">
         <v>0</v>
@@ -22674,25 +22674,25 @@
         <v>26</v>
       </c>
       <c r="C764" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D764" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E764">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F764">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G764">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H764">
-        <v>0</v>
+        <v>1683</v>
       </c>
       <c r="I764">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="765" spans="1:9">
@@ -22706,22 +22706,22 @@
         <v>50</v>
       </c>
       <c r="D765" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E765">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F765">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G765">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="H765">
-        <v>1756</v>
+        <v>483</v>
       </c>
       <c r="I765">
-        <v>70</v>
+        <v>21</v>
       </c>
     </row>
     <row r="766" spans="1:9">
@@ -22729,28 +22729,28 @@
         <v>22</v>
       </c>
       <c r="B766" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C766" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D766" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E766">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="F766">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G766">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="H766">
-        <v>483</v>
+        <v>68</v>
       </c>
       <c r="I766">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="767" spans="1:9">
@@ -22764,22 +22764,22 @@
         <v>41</v>
       </c>
       <c r="D767" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E767">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F767">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G767">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H767">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="I767">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="768" spans="1:9">
@@ -22790,19 +22790,19 @@
         <v>28</v>
       </c>
       <c r="C768" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D768" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E768">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F768">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="G768">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="H768">
         <v>0</v>
@@ -22822,22 +22822,22 @@
         <v>42</v>
       </c>
       <c r="D769" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E769">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F769">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G769">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H769">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I769">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="770" spans="1:9">
@@ -22848,25 +22848,25 @@
         <v>28</v>
       </c>
       <c r="C770" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D770" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E770">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F770">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G770">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H770">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I770">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="771" spans="1:9">
@@ -22880,22 +22880,22 @@
         <v>43</v>
       </c>
       <c r="D771" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E771">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F771">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G771">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H771">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I771">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="772" spans="1:9">
@@ -22906,25 +22906,25 @@
         <v>28</v>
       </c>
       <c r="C772" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D772" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E772">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F772">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G772">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H772">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I772">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="773" spans="1:9">
@@ -22938,16 +22938,16 @@
         <v>44</v>
       </c>
       <c r="D773" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E773">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F773">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G773">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H773">
         <v>0</v>
@@ -22964,25 +22964,25 @@
         <v>28</v>
       </c>
       <c r="C774" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D774" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E774">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="F774">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="G774">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="H774">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I774">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="775" spans="1:9">
@@ -22996,22 +22996,22 @@
         <v>45</v>
       </c>
       <c r="D775" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E775">
-        <v>41</v>
+        <v>120</v>
       </c>
       <c r="F775">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="G775">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="H775">
-        <v>67</v>
+        <v>663</v>
       </c>
       <c r="I775">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="776" spans="1:9">
@@ -23022,25 +23022,25 @@
         <v>28</v>
       </c>
       <c r="C776" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D776" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E776">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="F776">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="G776">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="H776">
-        <v>815</v>
+        <v>26</v>
       </c>
       <c r="I776">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="777" spans="1:9">
@@ -23054,22 +23054,22 @@
         <v>46</v>
       </c>
       <c r="D777" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E777">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F777">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G777">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H777">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I777">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="778" spans="1:9">
@@ -23080,19 +23080,19 @@
         <v>28</v>
       </c>
       <c r="C778" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D778" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E778">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="F778">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="G778">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="H778">
         <v>0</v>
@@ -23112,16 +23112,16 @@
         <v>47</v>
       </c>
       <c r="D779" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E779">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F779">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G779">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H779">
         <v>0</v>
@@ -23138,19 +23138,19 @@
         <v>28</v>
       </c>
       <c r="C780" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D780" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E780">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F780">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G780">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H780">
         <v>0</v>
@@ -23170,16 +23170,16 @@
         <v>48</v>
       </c>
       <c r="D781" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E781">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F781">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G781">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H781">
         <v>0</v>
@@ -23196,25 +23196,25 @@
         <v>28</v>
       </c>
       <c r="C782" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D782" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E782">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F782">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G782">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H782">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I782">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="783" spans="1:9">
@@ -23228,22 +23228,22 @@
         <v>49</v>
       </c>
       <c r="D783" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E783">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F783">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="G783">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="H783">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I783">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="784" spans="1:9">
@@ -23254,19 +23254,19 @@
         <v>28</v>
       </c>
       <c r="C784" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D784" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E784">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F784">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G784">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H784">
         <v>0</v>
@@ -23286,16 +23286,16 @@
         <v>51</v>
       </c>
       <c r="D785" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E785">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F785">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G785">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H785">
         <v>0</v>
@@ -23312,19 +23312,19 @@
         <v>28</v>
       </c>
       <c r="C786" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D786" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E786">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F786">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G786">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H786">
         <v>0</v>
@@ -23344,16 +23344,16 @@
         <v>50</v>
       </c>
       <c r="D787" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E787">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F787">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G787">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H787">
         <v>0</v>
@@ -23367,22 +23367,22 @@
         <v>22</v>
       </c>
       <c r="B788" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C788" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D788" t="s">
         <v>54</v>
       </c>
       <c r="E788">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F788">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G788">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H788">
         <v>0</v>
@@ -23399,25 +23399,25 @@
         <v>29</v>
       </c>
       <c r="C789" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D789" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E789">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F789">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G789">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H789">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="I789">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="790" spans="1:9">
@@ -23428,25 +23428,25 @@
         <v>29</v>
       </c>
       <c r="C790" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D790" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E790">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F790">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G790">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H790">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="I790">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="791" spans="1:9">
@@ -23457,25 +23457,25 @@
         <v>29</v>
       </c>
       <c r="C791" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D791" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E791">
+        <v>16</v>
+      </c>
+      <c r="F791">
+        <v>16</v>
+      </c>
+      <c r="G791">
+        <v>16</v>
+      </c>
+      <c r="H791">
+        <v>83</v>
+      </c>
+      <c r="I791">
         <v>8</v>
-      </c>
-      <c r="F791">
-        <v>8</v>
-      </c>
-      <c r="G791">
-        <v>8</v>
-      </c>
-      <c r="H791">
-        <v>0</v>
-      </c>
-      <c r="I791">
-        <v>0</v>
       </c>
     </row>
     <row r="792" spans="1:9">
@@ -23489,22 +23489,22 @@
         <v>45</v>
       </c>
       <c r="D792" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E792">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F792">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="G792">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="H792">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="I792">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="793" spans="1:9">
@@ -23515,25 +23515,25 @@
         <v>29</v>
       </c>
       <c r="C793" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D793" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E793">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="F793">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="G793">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="H793">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="I793">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="794" spans="1:9">
@@ -23547,16 +23547,16 @@
         <v>46</v>
       </c>
       <c r="D794" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E794">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F794">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G794">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H794">
         <v>0</v>
@@ -23573,19 +23573,19 @@
         <v>29</v>
       </c>
       <c r="C795" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D795" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E795">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F795">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G795">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H795">
         <v>0</v>
@@ -23605,22 +23605,22 @@
         <v>47</v>
       </c>
       <c r="D796" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E796">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F796">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G796">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H796">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="I796">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="797" spans="1:9">
@@ -23631,25 +23631,25 @@
         <v>29</v>
       </c>
       <c r="C797" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D797" t="s">
         <v>54</v>
       </c>
       <c r="E797">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F797">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G797">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H797">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="I797">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="798" spans="1:9">
@@ -23660,25 +23660,25 @@
         <v>29</v>
       </c>
       <c r="C798" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D798" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E798">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F798">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G798">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H798">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="I798">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="799" spans="1:9">
@@ -23692,22 +23692,22 @@
         <v>51</v>
       </c>
       <c r="D799" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E799">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F799">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G799">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H799">
-        <v>529</v>
+        <v>0</v>
       </c>
       <c r="I799">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="800" spans="1:9">
@@ -23718,19 +23718,19 @@
         <v>29</v>
       </c>
       <c r="C800" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D800" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E800">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F800">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G800">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H800">
         <v>0</v>
@@ -23750,22 +23750,22 @@
         <v>50</v>
       </c>
       <c r="D801" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E801">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F801">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G801">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H801">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I801">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="802" spans="1:9">
@@ -23773,28 +23773,28 @@
         <v>22</v>
       </c>
       <c r="B802" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C802" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D802" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E802">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F802">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G802">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H802">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I802">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="803" spans="1:9">
@@ -23802,7 +23802,7 @@
         <v>22</v>
       </c>
       <c r="B803" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C803" t="s">
         <v>45</v>
@@ -23811,13 +23811,13 @@
         <v>53</v>
       </c>
       <c r="E803">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F803">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G803">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H803">
         <v>0</v>
@@ -23837,7 +23837,7 @@
         <v>45</v>
       </c>
       <c r="D804" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E804">
         <v>1</v>
@@ -23863,10 +23863,10 @@
         <v>36</v>
       </c>
       <c r="C805" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D805" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E805">
         <v>1</v>
@@ -23889,13 +23889,13 @@
         <v>22</v>
       </c>
       <c r="B806" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C806" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D806" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E806">
         <v>1</v>
@@ -23921,19 +23921,19 @@
         <v>33</v>
       </c>
       <c r="C807" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D807" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E807">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F807">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G807">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H807">
         <v>0</v>
@@ -23953,16 +23953,16 @@
         <v>42</v>
       </c>
       <c r="D808" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E808">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F808">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G808">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H808">
         <v>0</v>
@@ -23979,19 +23979,19 @@
         <v>33</v>
       </c>
       <c r="C809" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D809" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E809">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F809">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G809">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H809">
         <v>0</v>
@@ -24011,16 +24011,16 @@
         <v>43</v>
       </c>
       <c r="D810" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E810">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F810">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G810">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H810">
         <v>0</v>
@@ -24037,10 +24037,10 @@
         <v>33</v>
       </c>
       <c r="C811" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D811" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E811">
         <v>3</v>
@@ -24069,16 +24069,16 @@
         <v>44</v>
       </c>
       <c r="D812" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E812">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F812">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G812">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H812">
         <v>0</v>
@@ -24095,25 +24095,25 @@
         <v>33</v>
       </c>
       <c r="C813" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D813" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E813">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F813">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G813">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H813">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="I813">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="814" spans="1:9">
@@ -24127,22 +24127,22 @@
         <v>45</v>
       </c>
       <c r="D814" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E814">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F814">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="G814">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="H814">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="I814">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="815" spans="1:9">
@@ -24153,25 +24153,25 @@
         <v>33</v>
       </c>
       <c r="C815" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D815" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E815">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="F815">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="G815">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="H815">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I815">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="816" spans="1:9">
@@ -24185,16 +24185,16 @@
         <v>46</v>
       </c>
       <c r="D816" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E816">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F816">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G816">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H816">
         <v>0</v>
@@ -24211,19 +24211,19 @@
         <v>33</v>
       </c>
       <c r="C817" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D817" t="s">
         <v>54</v>
       </c>
       <c r="E817">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F817">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G817">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H817">
         <v>0</v>
@@ -24240,10 +24240,10 @@
         <v>33</v>
       </c>
       <c r="C818" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D818" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E818">
         <v>5</v>
@@ -24255,10 +24255,10 @@
         <v>5</v>
       </c>
       <c r="H818">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I818">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="819" spans="1:9">
@@ -24272,16 +24272,16 @@
         <v>49</v>
       </c>
       <c r="D819" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E819">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F819">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G819">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H819">
         <v>10</v>
@@ -24298,25 +24298,25 @@
         <v>33</v>
       </c>
       <c r="C820" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D820" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E820">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F820">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G820">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H820">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I820">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="821" spans="1:9">
@@ -24330,16 +24330,16 @@
         <v>51</v>
       </c>
       <c r="D821" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E821">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F821">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G821">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H821">
         <v>0</v>
@@ -24356,19 +24356,19 @@
         <v>33</v>
       </c>
       <c r="C822" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D822" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E822">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F822">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G822">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H822">
         <v>0</v>
@@ -24388,22 +24388,22 @@
         <v>50</v>
       </c>
       <c r="D823" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E823">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F823">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G823">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H823">
-        <v>0</v>
+        <v>595</v>
       </c>
       <c r="I823">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="824" spans="1:9">
@@ -24411,28 +24411,28 @@
         <v>22</v>
       </c>
       <c r="B824" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C824" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D824" t="s">
         <v>54</v>
       </c>
       <c r="E824">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F824">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G824">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H824">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="I824">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="825" spans="1:9">
@@ -24443,25 +24443,25 @@
         <v>30</v>
       </c>
       <c r="C825" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D825" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E825">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F825">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G825">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H825">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="I825">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="826" spans="1:9">
@@ -24475,22 +24475,22 @@
         <v>44</v>
       </c>
       <c r="D826" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E826">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F826">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G826">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H826">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="I826">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="827" spans="1:9">
@@ -24501,19 +24501,19 @@
         <v>30</v>
       </c>
       <c r="C827" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D827" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E827">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F827">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G827">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H827">
         <v>0</v>
@@ -24533,22 +24533,22 @@
         <v>45</v>
       </c>
       <c r="D828" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E828">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F828">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G828">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H828">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I828">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="829" spans="1:9">
@@ -24559,25 +24559,25 @@
         <v>30</v>
       </c>
       <c r="C829" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D829" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E829">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F829">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G829">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H829">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I829">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="830" spans="1:9">
@@ -24591,7 +24591,7 @@
         <v>46</v>
       </c>
       <c r="D830" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E830">
         <v>2</v>
@@ -24617,19 +24617,19 @@
         <v>30</v>
       </c>
       <c r="C831" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D831" t="s">
         <v>54</v>
       </c>
       <c r="E831">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F831">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G831">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H831">
         <v>0</v>
@@ -24646,19 +24646,19 @@
         <v>30</v>
       </c>
       <c r="C832" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D832" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E832">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F832">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G832">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H832">
         <v>0</v>
@@ -24678,7 +24678,7 @@
         <v>49</v>
       </c>
       <c r="D833" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E833">
         <v>1</v>
@@ -24690,10 +24690,10 @@
         <v>1</v>
       </c>
       <c r="H833">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I833">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="834" spans="1:9">
@@ -24704,25 +24704,25 @@
         <v>30</v>
       </c>
       <c r="C834" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D834" t="s">
         <v>54</v>
       </c>
       <c r="E834">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F834">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G834">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H834">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="I834">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="835" spans="1:9">
@@ -24733,25 +24733,25 @@
         <v>30</v>
       </c>
       <c r="C835" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D835" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E835">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F835">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G835">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H835">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="I835">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="836" spans="1:9">
@@ -24765,22 +24765,22 @@
         <v>50</v>
       </c>
       <c r="D836" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E836">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F836">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G836">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H836">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I836">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="837" spans="1:9">
@@ -24788,28 +24788,28 @@
         <v>22</v>
       </c>
       <c r="B837" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C837" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D837" t="s">
         <v>54</v>
       </c>
       <c r="E837">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F837">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G837">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H837">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="I837">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="838" spans="1:9">
@@ -24820,7 +24820,7 @@
         <v>27</v>
       </c>
       <c r="C838" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D838" t="s">
         <v>54</v>
@@ -24849,7 +24849,7 @@
         <v>27</v>
       </c>
       <c r="C839" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D839" t="s">
         <v>54</v>
@@ -24872,13 +24872,13 @@
     </row>
     <row r="840" spans="1:9">
       <c r="A840" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B840" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C840" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D840" t="s">
         <v>54</v>
@@ -25096,10 +25096,10 @@
         <v>16</v>
       </c>
       <c r="H847">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="I847">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="848" spans="1:9">
@@ -25125,10 +25125,10 @@
         <v>12</v>
       </c>
       <c r="H848">
-        <v>45815</v>
+        <v>47852</v>
       </c>
       <c r="I848">
-        <v>1404</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="849" spans="1:9">
@@ -25183,10 +25183,10 @@
         <v>90</v>
       </c>
       <c r="H850">
-        <v>12285</v>
+        <v>13094</v>
       </c>
       <c r="I850">
-        <v>436</v>
+        <v>471</v>
       </c>
     </row>
     <row r="851" spans="1:9">
@@ -25241,10 +25241,10 @@
         <v>16</v>
       </c>
       <c r="H852">
-        <v>2694</v>
+        <v>2742</v>
       </c>
       <c r="I852">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="853" spans="1:9">
@@ -25299,10 +25299,10 @@
         <v>5</v>
       </c>
       <c r="H854">
-        <v>13395</v>
+        <v>14094</v>
       </c>
       <c r="I854">
-        <v>542</v>
+        <v>570</v>
       </c>
     </row>
     <row r="855" spans="1:9">
@@ -25386,10 +25386,10 @@
         <v>29</v>
       </c>
       <c r="H857">
-        <v>3397</v>
+        <v>3480</v>
       </c>
       <c r="I857">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="858" spans="1:9">
@@ -25444,10 +25444,10 @@
         <v>2</v>
       </c>
       <c r="H859">
-        <v>13109</v>
+        <v>14378</v>
       </c>
       <c r="I859">
-        <v>403</v>
+        <v>439</v>
       </c>
     </row>
     <row r="860" spans="1:9">
@@ -25473,10 +25473,10 @@
         <v>20</v>
       </c>
       <c r="H860">
-        <v>7028</v>
+        <v>7070</v>
       </c>
       <c r="I860">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="861" spans="1:9">
@@ -25502,10 +25502,10 @@
         <v>19</v>
       </c>
       <c r="H861">
-        <v>10523</v>
+        <v>10952</v>
       </c>
       <c r="I861">
-        <v>396</v>
+        <v>412</v>
       </c>
     </row>
     <row r="862" spans="1:9">
@@ -25937,10 +25937,10 @@
         <v>9</v>
       </c>
       <c r="H876">
-        <v>2707</v>
+        <v>2723</v>
       </c>
       <c r="I876">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="877" spans="1:9">
@@ -25995,10 +25995,10 @@
         <v>105</v>
       </c>
       <c r="H878">
-        <v>3289</v>
+        <v>3342</v>
       </c>
       <c r="I878">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="879" spans="1:9">
@@ -26053,10 +26053,10 @@
         <v>13</v>
       </c>
       <c r="H880">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="I880">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="881" spans="1:9">
@@ -26111,10 +26111,10 @@
         <v>6</v>
       </c>
       <c r="H882">
-        <v>2791</v>
+        <v>2861</v>
       </c>
       <c r="I882">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="883" spans="1:9">
@@ -26401,10 +26401,10 @@
         <v>1</v>
       </c>
       <c r="H892">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="I892">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="893" spans="1:9">
@@ -26546,10 +26546,10 @@
         <v>4</v>
       </c>
       <c r="H897">
-        <v>1087</v>
+        <v>1130</v>
       </c>
       <c r="I897">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="898" spans="1:9">
@@ -26894,10 +26894,10 @@
         <v>0</v>
       </c>
       <c r="H909">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="I909">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="910" spans="1:9">
@@ -28141,10 +28141,10 @@
         <v>2</v>
       </c>
       <c r="H952">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c r="I952">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="953" spans="1:9">
@@ -28199,10 +28199,10 @@
         <v>22</v>
       </c>
       <c r="H954">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="I954">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="955" spans="1:9">
@@ -28431,10 +28431,10 @@
         <v>0</v>
       </c>
       <c r="H962">
-        <v>1177</v>
+        <v>1219</v>
       </c>
       <c r="I962">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="963" spans="1:9">
@@ -28460,10 +28460,10 @@
         <v>6</v>
       </c>
       <c r="H963">
-        <v>761</v>
+        <v>791</v>
       </c>
       <c r="I963">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="964" spans="1:9">
@@ -28489,10 +28489,10 @@
         <v>8</v>
       </c>
       <c r="H964">
-        <v>1036</v>
+        <v>1129</v>
       </c>
       <c r="I964">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="965" spans="1:9">
@@ -28924,10 +28924,10 @@
         <v>11</v>
       </c>
       <c r="H979">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="I979">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="980" spans="1:9">
@@ -29176,13 +29176,13 @@
         <v>53</v>
       </c>
       <c r="E988">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F988">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G988">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H988">
         <v>0</v>
@@ -29388,10 +29388,10 @@
         <v>48</v>
       </c>
       <c r="H995">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="I995">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="996" spans="1:9">
@@ -29437,19 +29437,19 @@
         <v>53</v>
       </c>
       <c r="E997">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F997">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G997">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H997">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="I997">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="998" spans="1:9">
@@ -29794,10 +29794,10 @@
         <v>57</v>
       </c>
       <c r="H1009">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="I1009">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1010" spans="1:9">
@@ -29843,13 +29843,13 @@
         <v>53</v>
       </c>
       <c r="E1011">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F1011">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1011">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H1011">
         <v>0</v>
@@ -29910,10 +29910,10 @@
         <v>54</v>
       </c>
       <c r="H1013">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="I1013">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1014" spans="1:9">
@@ -29939,10 +29939,10 @@
         <v>15</v>
       </c>
       <c r="H1014">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I1014">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1015" spans="1:9">
@@ -30055,10 +30055,10 @@
         <v>17</v>
       </c>
       <c r="H1018">
-        <v>8520</v>
+        <v>10587</v>
       </c>
       <c r="I1018">
-        <v>272</v>
+        <v>328</v>
       </c>
     </row>
     <row r="1019" spans="1:9">
@@ -30084,10 +30084,10 @@
         <v>174</v>
       </c>
       <c r="H1019">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="I1019">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1020" spans="1:9">
@@ -30113,10 +30113,10 @@
         <v>168</v>
       </c>
       <c r="H1020">
-        <v>3640</v>
+        <v>4253</v>
       </c>
       <c r="I1020">
-        <v>131</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1021" spans="1:9">
@@ -30133,19 +30133,19 @@
         <v>53</v>
       </c>
       <c r="E1021">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F1021">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G1021">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H1021">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="I1021">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1022" spans="1:9">
@@ -30171,10 +30171,10 @@
         <v>51</v>
       </c>
       <c r="H1022">
-        <v>1083</v>
+        <v>1176</v>
       </c>
       <c r="I1022">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1023" spans="1:9">
@@ -30229,10 +30229,10 @@
         <v>6</v>
       </c>
       <c r="H1024">
-        <v>3289</v>
+        <v>4172</v>
       </c>
       <c r="I1024">
-        <v>119</v>
+        <v>150</v>
       </c>
     </row>
     <row r="1025" spans="1:9">
@@ -30316,10 +30316,10 @@
         <v>109</v>
       </c>
       <c r="H1027">
-        <v>182</v>
+        <v>305</v>
       </c>
       <c r="I1027">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1028" spans="1:9">
@@ -30345,10 +30345,10 @@
         <v>75</v>
       </c>
       <c r="H1028">
-        <v>710</v>
+        <v>891</v>
       </c>
       <c r="I1028">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1029" spans="1:9">
@@ -30374,10 +30374,10 @@
         <v>4</v>
       </c>
       <c r="H1029">
-        <v>2611</v>
+        <v>2995</v>
       </c>
       <c r="I1029">
-        <v>146</v>
+        <v>169</v>
       </c>
     </row>
     <row r="1030" spans="1:9">
@@ -30432,10 +30432,10 @@
         <v>40</v>
       </c>
       <c r="H1031">
-        <v>5064</v>
+        <v>6131</v>
       </c>
       <c r="I1031">
-        <v>193</v>
+        <v>224</v>
       </c>
     </row>
     <row r="1032" spans="1:9">
@@ -30577,10 +30577,10 @@
         <v>2</v>
       </c>
       <c r="H1036">
-        <v>262</v>
+        <v>296</v>
       </c>
       <c r="I1036">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1037" spans="1:9">
@@ -30693,10 +30693,10 @@
         <v>18</v>
       </c>
       <c r="H1040">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="I1040">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1041" spans="1:9">
@@ -30751,10 +30751,10 @@
         <v>10</v>
       </c>
       <c r="H1042">
-        <v>744</v>
+        <v>921</v>
       </c>
       <c r="I1042">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1043" spans="1:9">
@@ -30780,10 +30780,10 @@
         <v>43</v>
       </c>
       <c r="H1043">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I1043">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1044" spans="1:9">
@@ -30838,10 +30838,10 @@
         <v>62</v>
       </c>
       <c r="H1045">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="I1045">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1046" spans="1:9">
@@ -30867,10 +30867,10 @@
         <v>43</v>
       </c>
       <c r="H1046">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="I1046">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1047" spans="1:9">
@@ -30896,10 +30896,10 @@
         <v>4</v>
       </c>
       <c r="H1047">
-        <v>245</v>
+        <v>294</v>
       </c>
       <c r="I1047">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1048" spans="1:9">
@@ -31099,10 +31099,10 @@
         <v>15</v>
       </c>
       <c r="H1054">
-        <v>421</v>
+        <v>558</v>
       </c>
       <c r="I1054">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1055" spans="1:9">
@@ -31331,10 +31331,10 @@
         <v>6</v>
       </c>
       <c r="H1062">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I1062">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1063" spans="1:9">
@@ -31476,10 +31476,10 @@
         <v>1</v>
       </c>
       <c r="H1067">
-        <v>376</v>
+        <v>489</v>
       </c>
       <c r="I1067">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1068" spans="1:9">
@@ -31592,10 +31592,10 @@
         <v>28</v>
       </c>
       <c r="H1071">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I1071">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1072" spans="1:9">
@@ -31882,10 +31882,10 @@
         <v>6</v>
       </c>
       <c r="H1081">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I1081">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1082" spans="1:9">
@@ -31911,10 +31911,10 @@
         <v>10</v>
       </c>
       <c r="H1082">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="I1082">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1083" spans="1:9">
@@ -32955,10 +32955,10 @@
         <v>1</v>
       </c>
       <c r="H1118">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="I1118">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1119" spans="1:9">
@@ -33216,10 +33216,10 @@
         <v>48</v>
       </c>
       <c r="H1127">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="I1127">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1128" spans="1:9">
@@ -33622,10 +33622,10 @@
         <v>6</v>
       </c>
       <c r="H1141">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="I1141">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1142" spans="1:9">
@@ -33796,10 +33796,10 @@
         <v>1</v>
       </c>
       <c r="H1147">
-        <v>392</v>
+        <v>434</v>
       </c>
       <c r="I1147">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1148" spans="1:9">
@@ -33961,13 +33961,13 @@
         <v>53</v>
       </c>
       <c r="E1153">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1153">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1153">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1153">
         <v>0</v>
@@ -34173,10 +34173,10 @@
         <v>4</v>
       </c>
       <c r="H1160">
-        <v>324</v>
+        <v>481</v>
       </c>
       <c r="I1160">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1161" spans="1:9">
@@ -34251,13 +34251,13 @@
         <v>53</v>
       </c>
       <c r="E1163">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F1163">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G1163">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H1163">
         <v>45</v>
@@ -34463,10 +34463,10 @@
         <v>28</v>
       </c>
       <c r="H1170">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I1170">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1171" spans="1:9">
@@ -34564,7 +34564,7 @@
         <v>27</v>
       </c>
       <c r="C1174" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D1174" t="s">
         <v>54</v>
@@ -34593,19 +34593,19 @@
         <v>27</v>
       </c>
       <c r="C1175" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D1175" t="s">
         <v>54</v>
       </c>
       <c r="E1175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1175">
         <v>0</v>
@@ -34622,25 +34622,25 @@
         <v>27</v>
       </c>
       <c r="C1176" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D1176" t="s">
         <v>54</v>
       </c>
       <c r="E1176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1176">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I1176">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1177" spans="1:9">
@@ -34651,19 +34651,19 @@
         <v>27</v>
       </c>
       <c r="C1177" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D1177" t="s">
         <v>54</v>
       </c>
       <c r="E1177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1177">
         <v>0</v>
@@ -34680,19 +34680,19 @@
         <v>27</v>
       </c>
       <c r="C1178" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D1178" t="s">
         <v>54</v>
       </c>
       <c r="E1178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1178">
         <v>0</v>
@@ -34709,19 +34709,19 @@
         <v>27</v>
       </c>
       <c r="C1179" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D1179" t="s">
         <v>54</v>
       </c>
       <c r="E1179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1179">
         <v>0</v>
@@ -34738,24 +34738,53 @@
         <v>27</v>
       </c>
       <c r="C1180" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1180" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1180">
+        <v>1</v>
+      </c>
+      <c r="F1180">
+        <v>1</v>
+      </c>
+      <c r="G1180">
+        <v>1</v>
+      </c>
+      <c r="H1180">
+        <v>0</v>
+      </c>
+      <c r="I1180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:9">
+      <c r="A1181" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1181" t="s">
         <v>50</v>
       </c>
-      <c r="D1180" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1180">
-        <v>1</v>
-      </c>
-      <c r="F1180">
-        <v>1</v>
-      </c>
-      <c r="G1180">
-        <v>1</v>
-      </c>
-      <c r="H1180">
-        <v>0</v>
-      </c>
-      <c r="I1180">
+      <c r="D1181" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1181">
+        <v>1</v>
+      </c>
+      <c r="F1181">
+        <v>1</v>
+      </c>
+      <c r="G1181">
+        <v>1</v>
+      </c>
+      <c r="H1181">
+        <v>0</v>
+      </c>
+      <c r="I1181">
         <v>0</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -29814,13 +29814,13 @@
         <v>53</v>
       </c>
       <c r="E1010">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F1010">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G1010">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H1010">
         <v>0</v>
@@ -29872,13 +29872,13 @@
         <v>53</v>
       </c>
       <c r="E1012">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1012">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1012">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H1012">
         <v>64</v>
@@ -29930,13 +29930,13 @@
         <v>53</v>
       </c>
       <c r="E1014">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1014">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1014">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H1014">
         <v>0</v>
@@ -30046,13 +30046,13 @@
         <v>53</v>
       </c>
       <c r="E1018">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F1018">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G1018">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H1018">
         <v>199</v>
@@ -30278,13 +30278,13 @@
         <v>53</v>
       </c>
       <c r="E1026">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F1026">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G1026">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H1026">
         <v>247</v>
@@ -30510,13 +30510,13 @@
         <v>53</v>
       </c>
       <c r="E1034">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1034">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1034">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1034">
         <v>0</v>
@@ -30568,13 +30568,13 @@
         <v>53</v>
       </c>
       <c r="E1036">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F1036">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G1036">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H1036">
         <v>0</v>
@@ -31090,13 +31090,13 @@
         <v>53</v>
       </c>
       <c r="E1054">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1054">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1054">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1054">
         <v>0</v>
@@ -31148,13 +31148,13 @@
         <v>53</v>
       </c>
       <c r="E1056">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1056">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1056">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1056">
         <v>0</v>
@@ -32801,13 +32801,13 @@
         <v>53</v>
       </c>
       <c r="E1113">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1113">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1113">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H1113">
         <v>0</v>
@@ -32830,13 +32830,13 @@
         <v>53</v>
       </c>
       <c r="E1114">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F1114">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1114">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H1114">
         <v>0</v>
@@ -33004,13 +33004,13 @@
         <v>53</v>
       </c>
       <c r="E1120">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F1120">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1120">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H1120">
         <v>0</v>
@@ -33990,13 +33990,13 @@
         <v>53</v>
       </c>
       <c r="E1154">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1154">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1154">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1154">
         <v>0</v>
@@ -34048,13 +34048,13 @@
         <v>53</v>
       </c>
       <c r="E1156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1156">
         <v>0</v>
